--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,25 +481,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>86.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>93.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>95.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>70.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>258.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>896.3</v>
+        <v>945</v>
       </c>
       <c r="J2" t="n">
         <v>945</v>
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>johnson5</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>85.8</v>
+        <v>83.5</v>
       </c>
       <c r="E3" t="n">
-        <v>85.8</v>
+        <v>83.5</v>
       </c>
       <c r="F3" t="n">
-        <v>85.8</v>
+        <v>83.5</v>
       </c>
       <c r="G3" t="n">
-        <v>85.8</v>
+        <v>83.5</v>
       </c>
       <c r="H3" t="n">
-        <v>85.8</v>
+        <v>83.5</v>
       </c>
       <c r="I3" t="n">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="J3" t="n">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="4">
@@ -549,25 +549,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>82.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="E4" t="n">
-        <v>83.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>94.3</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>69.5</v>
+        <v>75</v>
       </c>
       <c r="H4" t="n">
-        <v>247.2</v>
+        <v>75</v>
       </c>
       <c r="I4" t="n">
-        <v>891.3</v>
+        <v>926</v>
       </c>
       <c r="J4" t="n">
         <v>926</v>
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pparril</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>64.59999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="E5" t="n">
-        <v>64.59999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="F5" t="n">
-        <v>90.59999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="G5" t="n">
-        <v>38.6</v>
+        <v>55.5</v>
       </c>
       <c r="H5" t="n">
-        <v>129.2</v>
+        <v>55.5</v>
       </c>
       <c r="I5" t="n">
-        <v>825.5</v>
+        <v>894</v>
       </c>
       <c r="J5" t="n">
-        <v>959</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>54.4</v>
+        <v>50.8</v>
       </c>
       <c r="E6" t="n">
-        <v>42.3</v>
+        <v>50.8</v>
       </c>
       <c r="F6" t="n">
-        <v>92.7</v>
+        <v>50.8</v>
       </c>
       <c r="G6" t="n">
-        <v>28.1</v>
+        <v>50.8</v>
       </c>
       <c r="H6" t="n">
-        <v>163.1</v>
+        <v>50.8</v>
       </c>
       <c r="I6" t="n">
-        <v>859.7</v>
+        <v>887</v>
       </c>
       <c r="J6" t="n">
-        <v>894</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>52.2</v>
+        <v>44.2</v>
       </c>
       <c r="E7" t="n">
-        <v>52.2</v>
+        <v>44.2</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>44.2</v>
       </c>
       <c r="G7" t="n">
-        <v>36.5</v>
+        <v>44.2</v>
       </c>
       <c r="H7" t="n">
-        <v>104.5</v>
+        <v>44.2</v>
       </c>
       <c r="I7" t="n">
-        <v>802.5</v>
+        <v>877</v>
       </c>
       <c r="J7" t="n">
-        <v>917</v>
+        <v>877</v>
       </c>
     </row>
     <row r="8">
@@ -685,28 +685,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>47.6</v>
+        <v>37.7</v>
       </c>
       <c r="E8" t="n">
-        <v>65.09999999999999</v>
+        <v>37.7</v>
       </c>
       <c r="F8" t="n">
-        <v>65.7</v>
+        <v>37.7</v>
       </c>
       <c r="G8" t="n">
-        <v>11.9</v>
+        <v>37.7</v>
       </c>
       <c r="H8" t="n">
-        <v>142.7</v>
+        <v>37.7</v>
       </c>
       <c r="I8" t="n">
-        <v>841</v>
+        <v>867</v>
       </c>
       <c r="J8" t="n">
-        <v>913</v>
+        <v>867</v>
       </c>
     </row>
     <row r="9">
@@ -715,270 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>djeckma</t>
+          <t>johnson7</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>42.3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>42.3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>42.3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>42.3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>699</v>
+        <v>746</v>
       </c>
       <c r="J9" t="n">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Jules</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="E10" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>774</v>
-      </c>
-      <c r="J10" t="n">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JonahL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="F11" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>817.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>cartert</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>756.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>jbarn11</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="G13" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H13" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>817.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Meghan</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>657</v>
-      </c>
-      <c r="J14" t="n">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>andrewf3</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="G15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>621</v>
-      </c>
-      <c r="J15" t="n">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>andrewf2</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>784</v>
-      </c>
-      <c r="J16" t="n">
-        <v>784</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,16 +765,6 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>8/31/26</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>9/1/26</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>9/2/26</t>
         </is>
       </c>
@@ -1020,214 +772,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>750</v>
-      </c>
-      <c r="C2" t="n">
-        <v>815</v>
-      </c>
-      <c r="D2" t="n">
-        <v>887</v>
+        <v>945</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>642</v>
-      </c>
-      <c r="C3" t="n">
-        <v>906</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>944</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>688</v>
-      </c>
-      <c r="C4" t="n">
-        <v>917</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>926</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>829</v>
-      </c>
-      <c r="C5" t="n">
-        <v>919</v>
-      </c>
-      <c r="D5" t="n">
-        <v>926</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>743</v>
-      </c>
-      <c r="C6" t="n">
-        <v>913</v>
-      </c>
-      <c r="D6" t="n">
-        <v>867</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>andrewf3</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>621</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+        <v>877</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>601</v>
-      </c>
-      <c r="C8" t="n">
-        <v>912</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>867</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>djeckma</t>
+          <t>johnson7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>699</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>jbarn11</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>707</v>
-      </c>
-      <c r="C10" t="n">
-        <v>868</v>
-      </c>
-      <c r="D10" t="n">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>kadrids</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>820</v>
-      </c>
-      <c r="C11" t="n">
-        <v>865</v>
-      </c>
-      <c r="D11" t="n">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>kunalrs</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>824</v>
-      </c>
-      <c r="C12" t="n">
-        <v>920</v>
-      </c>
-      <c r="D12" t="n">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pparril</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>692</v>
-      </c>
-      <c r="C13" t="n">
-        <v>959</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Meghan</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>657</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>johnson5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>947</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>andrewf2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>784</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>746</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1240,7 +860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,16 +871,6 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>8/31/26</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>9/1/26</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>9/2/26</t>
         </is>
       </c>
@@ -1268,214 +878,82 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32.7</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>83.5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>68</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>75</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>83.40000000000001</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="C6" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11.9</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>andrewf3</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+        <v>44.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>37.7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>djeckma</t>
+          <t>johnson7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>jbarn11</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="C10" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>kadrids</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>92.7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>42.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>kunalrs</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="C12" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="D12" t="n">
-        <v>95.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pparril</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="C13" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Meghan</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>johnson5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>andrewf2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1488,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1531,76 +1009,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8/31/26</t>
+          <t>9/2/26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>713.3</v>
+        <v>885.75</v>
       </c>
       <c r="D2" t="n">
-        <v>73.40000000000001</v>
+        <v>59.74058503228773</v>
       </c>
       <c r="E2" t="n">
-        <v>699</v>
+        <v>890.5</v>
       </c>
       <c r="F2" t="n">
-        <v>829</v>
+        <v>945</v>
       </c>
       <c r="G2" t="n">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>9/1/26</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C3" t="n">
-        <v>893.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>912.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>959</v>
-      </c>
-      <c r="G3" t="n">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9/2/26</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>899.3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>890.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>945</v>
-      </c>
-      <c r="G4" t="n">
-        <v>867</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,19 +484,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>83.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>83.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="F2" t="n">
-        <v>83.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
-        <v>83.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="H2" t="n">
-        <v>83.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="I2" t="n">
         <v>945</v>
@@ -518,19 +518,19 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>83.5</v>
+        <v>86.7</v>
       </c>
       <c r="E3" t="n">
-        <v>83.5</v>
+        <v>86.7</v>
       </c>
       <c r="F3" t="n">
-        <v>83.5</v>
+        <v>86.7</v>
       </c>
       <c r="G3" t="n">
-        <v>83.5</v>
+        <v>86.7</v>
       </c>
       <c r="H3" t="n">
-        <v>83.5</v>
+        <v>86.7</v>
       </c>
       <c r="I3" t="n">
         <v>944</v>
@@ -552,19 +552,19 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>75</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>926</v>
@@ -586,19 +586,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>55.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>55.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>55.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>55.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>55.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>894</v>
@@ -620,19 +620,19 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>50.8</v>
+        <v>61.9</v>
       </c>
       <c r="E6" t="n">
-        <v>50.8</v>
+        <v>61.9</v>
       </c>
       <c r="F6" t="n">
-        <v>50.8</v>
+        <v>61.9</v>
       </c>
       <c r="G6" t="n">
-        <v>50.8</v>
+        <v>61.9</v>
       </c>
       <c r="H6" t="n">
-        <v>50.8</v>
+        <v>61.9</v>
       </c>
       <c r="I6" t="n">
         <v>887</v>
@@ -654,19 +654,19 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>44.2</v>
+        <v>56.3</v>
       </c>
       <c r="E7" t="n">
-        <v>44.2</v>
+        <v>56.3</v>
       </c>
       <c r="F7" t="n">
-        <v>44.2</v>
+        <v>56.3</v>
       </c>
       <c r="G7" t="n">
-        <v>44.2</v>
+        <v>56.3</v>
       </c>
       <c r="H7" t="n">
-        <v>44.2</v>
+        <v>56.3</v>
       </c>
       <c r="I7" t="n">
         <v>877</v>
@@ -688,19 +688,19 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>37.7</v>
+        <v>50.7</v>
       </c>
       <c r="E8" t="n">
-        <v>37.7</v>
+        <v>50.7</v>
       </c>
       <c r="F8" t="n">
-        <v>37.7</v>
+        <v>50.7</v>
       </c>
       <c r="G8" t="n">
-        <v>37.7</v>
+        <v>50.7</v>
       </c>
       <c r="H8" t="n">
-        <v>37.7</v>
+        <v>50.7</v>
       </c>
       <c r="I8" t="n">
         <v>867</v>
@@ -715,32 +715,100 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
+        <v>33</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33</v>
+      </c>
+      <c r="H9" t="n">
+        <v>33</v>
+      </c>
+      <c r="I9" t="n">
+        <v>835</v>
+      </c>
+      <c r="J9" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>johnson7</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="D10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>746</v>
+      </c>
+      <c r="J10" t="n">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cartert</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>746</v>
-      </c>
-      <c r="J9" t="n">
-        <v>746</v>
+      <c r="D11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>737</v>
+      </c>
+      <c r="J11" t="n">
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -754,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -847,6 +915,26 @@
       </c>
       <c r="B9" t="n">
         <v>746</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cartert</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,7 +970,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.90000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -892,7 +980,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83.5</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="4">
@@ -902,7 +990,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -912,7 +1000,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.5</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -922,7 +1010,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.8</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="7">
@@ -932,7 +1020,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44.2</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="8">
@@ -942,7 +1030,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37.7</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="9">
@@ -952,7 +1040,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Jules</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cartert</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1013,22 +1121,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>885.75</v>
+        <v>865.8</v>
       </c>
       <c r="D2" t="n">
-        <v>59.74058503228773</v>
+        <v>70.2</v>
       </c>
       <c r="E2" t="n">
-        <v>890.5</v>
+        <v>882</v>
       </c>
       <c r="F2" t="n">
         <v>945</v>
       </c>
       <c r="G2" t="n">
-        <v>746</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -685,28 +685,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="E8" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F8" t="n">
         <v>50.7</v>
       </c>
       <c r="G8" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>50.7</v>
+        <v>100.7</v>
       </c>
       <c r="I8" t="n">
-        <v>867</v>
+        <v>876.5</v>
       </c>
       <c r="J8" t="n">
-        <v>867</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9">
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,6 +836,11 @@
           <t>9/2/26</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>9/3/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -846,6 +851,7 @@
       <c r="B2" t="n">
         <v>945</v>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -856,6 +862,7 @@
       <c r="B3" t="n">
         <v>944</v>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -866,6 +873,7 @@
       <c r="B4" t="n">
         <v>926</v>
       </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -876,6 +884,7 @@
       <c r="B5" t="n">
         <v>894</v>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -886,6 +895,7 @@
       <c r="B6" t="n">
         <v>887</v>
       </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -896,6 +906,7 @@
       <c r="B7" t="n">
         <v>877</v>
       </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -906,6 +917,9 @@
       <c r="B8" t="n">
         <v>867</v>
       </c>
+      <c r="C8" t="n">
+        <v>886</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -916,6 +930,7 @@
       <c r="B9" t="n">
         <v>746</v>
       </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -926,6 +941,7 @@
       <c r="B10" t="n">
         <v>835</v>
       </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -936,6 +952,7 @@
       <c r="B11" t="n">
         <v>737</v>
       </c>
+      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -948,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -962,6 +979,11 @@
           <t>9/2/26</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>9/3/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -972,6 +994,7 @@
       <c r="B2" t="n">
         <v>87</v>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -982,6 +1005,7 @@
       <c r="B3" t="n">
         <v>86.7</v>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -992,6 +1016,7 @@
       <c r="B4" t="n">
         <v>80.40000000000001</v>
       </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1002,6 +1027,7 @@
       <c r="B5" t="n">
         <v>65.59999999999999</v>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1012,6 +1038,7 @@
       <c r="B6" t="n">
         <v>61.9</v>
       </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1022,6 +1049,7 @@
       <c r="B7" t="n">
         <v>56.3</v>
       </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1032,6 +1060,9 @@
       <c r="B8" t="n">
         <v>50.7</v>
       </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1042,6 +1073,7 @@
       <c r="B9" t="n">
         <v>4.4</v>
       </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1052,6 +1084,7 @@
       <c r="B10" t="n">
         <v>33</v>
       </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1062,6 +1095,7 @@
       <c r="B11" t="n">
         <v>3.3</v>
       </c>
+      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1074,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1173,31 @@
         <v>737</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9/3/26</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>886</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>886</v>
+      </c>
+      <c r="F3" t="n">
+        <v>886</v>
+      </c>
+      <c r="G3" t="n">
+        <v>886</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,32 +477,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="F2" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="G2" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="H2" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="I2" t="n">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J2" t="n">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="3">
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pparril</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>86.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>86.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>86.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>86.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>86.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>944</v>
+        <v>926</v>
       </c>
       <c r="J3" t="n">
-        <v>944</v>
+        <v>926</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>80.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="E4" t="n">
-        <v>80.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F4" t="n">
-        <v>80.40000000000001</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>80.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="H4" t="n">
-        <v>80.40000000000001</v>
+        <v>141.7</v>
       </c>
       <c r="I4" t="n">
-        <v>926</v>
+        <v>876.5</v>
       </c>
       <c r="J4" t="n">
-        <v>926</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="E8" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F8" t="n">
-        <v>50.7</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>14.6</v>
       </c>
       <c r="H8" t="n">
-        <v>100.7</v>
+        <v>101.6</v>
       </c>
       <c r="I8" t="n">
-        <v>876.5</v>
+        <v>839</v>
       </c>
       <c r="J8" t="n">
-        <v>886</v>
+        <v>945</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="F9" t="n">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="H9" t="n">
-        <v>33</v>
+        <v>38.7</v>
       </c>
       <c r="I9" t="n">
-        <v>835</v>
+        <v>782</v>
       </c>
       <c r="J9" t="n">
-        <v>835</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>4.4</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>4.4</v>
+        <v>33</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>33</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>33</v>
       </c>
       <c r="I10" t="n">
-        <v>746</v>
+        <v>835</v>
       </c>
       <c r="J10" t="n">
-        <v>746</v>
+        <v>835</v>
       </c>
     </row>
     <row r="11">
@@ -783,31 +783,65 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>johnson7</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>746</v>
+      </c>
+      <c r="J11" t="n">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cartert</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
         <v>3.3</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>3.3</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>3.3</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>3.3</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>3.3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>737</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>737</v>
       </c>
     </row>
@@ -822,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,7 +885,9 @@
       <c r="B2" t="n">
         <v>945</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>733</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -953,6 +989,17 @@
         <v>737</v>
       </c>
       <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>johnson6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>782</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -965,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,7 +1041,9 @@
       <c r="B2" t="n">
         <v>87</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>14.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1061,7 +1110,7 @@
         <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -1096,6 +1145,17 @@
         <v>3.3</v>
       </c>
       <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>johnson6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>38.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1180,22 +1240,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>886</v>
+        <v>800.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="E3" t="n">
-        <v>886</v>
+        <v>782</v>
       </c>
       <c r="F3" t="n">
         <v>886</v>
       </c>
       <c r="G3" t="n">
-        <v>886</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>80.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="E3" t="n">
-        <v>80.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="F3" t="n">
-        <v>80.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>80.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="H3" t="n">
-        <v>80.40000000000001</v>
+        <v>147.6</v>
       </c>
       <c r="I3" t="n">
-        <v>926</v>
+        <v>876.5</v>
       </c>
       <c r="J3" t="n">
-        <v>926</v>
+        <v>886</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>70.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>70.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>50.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>141.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>876.5</v>
+        <v>894</v>
       </c>
       <c r="J4" t="n">
-        <v>886</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>65.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="E5" t="n">
-        <v>65.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="F5" t="n">
-        <v>65.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="G5" t="n">
-        <v>65.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="H5" t="n">
-        <v>65.59999999999999</v>
+        <v>61.9</v>
       </c>
       <c r="I5" t="n">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="J5" t="n">
-        <v>894</v>
+        <v>887</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>61.9</v>
+        <v>56.9</v>
       </c>
       <c r="E6" t="n">
-        <v>61.9</v>
+        <v>56.9</v>
       </c>
       <c r="F6" t="n">
-        <v>61.9</v>
+        <v>56.9</v>
       </c>
       <c r="G6" t="n">
-        <v>61.9</v>
+        <v>56.9</v>
       </c>
       <c r="H6" t="n">
-        <v>61.9</v>
+        <v>56.9</v>
       </c>
       <c r="I6" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
       <c r="J6" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="E7" t="n">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="F7" t="n">
-        <v>56.3</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>56.3</v>
+        <v>26.6</v>
       </c>
       <c r="H7" t="n">
-        <v>56.3</v>
+        <v>113.6</v>
       </c>
       <c r="I7" t="n">
-        <v>877</v>
+        <v>839</v>
       </c>
       <c r="J7" t="n">
-        <v>877</v>
+        <v>945</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>50.8</v>
+        <v>56.3</v>
       </c>
       <c r="E8" t="n">
-        <v>50.8</v>
+        <v>56.3</v>
       </c>
       <c r="F8" t="n">
-        <v>87</v>
+        <v>56.3</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6</v>
+        <v>56.3</v>
       </c>
       <c r="H8" t="n">
-        <v>101.6</v>
+        <v>56.3</v>
       </c>
       <c r="I8" t="n">
-        <v>839</v>
+        <v>877</v>
       </c>
       <c r="J8" t="n">
-        <v>945</v>
+        <v>877</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>38.7</v>
+        <v>55.7</v>
       </c>
       <c r="E9" t="n">
-        <v>38.7</v>
+        <v>55.7</v>
       </c>
       <c r="F9" t="n">
-        <v>38.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>38.7</v>
+        <v>31</v>
       </c>
       <c r="H9" t="n">
-        <v>38.7</v>
+        <v>111.4</v>
       </c>
       <c r="I9" t="n">
-        <v>782</v>
+        <v>833.5</v>
       </c>
       <c r="J9" t="n">
-        <v>782</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10">
@@ -753,25 +753,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>25.4</v>
       </c>
       <c r="E10" t="n">
-        <v>33</v>
+        <v>25.4</v>
       </c>
       <c r="F10" t="n">
         <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>17.9</v>
       </c>
       <c r="H10" t="n">
-        <v>33</v>
+        <v>50.9</v>
       </c>
       <c r="I10" t="n">
-        <v>835</v>
+        <v>775</v>
       </c>
       <c r="J10" t="n">
         <v>835</v>
@@ -909,7 +909,9 @@
       <c r="B4" t="n">
         <v>926</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>741</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -977,7 +979,9 @@
       <c r="B10" t="n">
         <v>835</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>715</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1042,7 +1046,7 @@
         <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>14.6</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="3">
@@ -1065,7 +1069,9 @@
       <c r="B4" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1110,7 +1116,7 @@
         <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>91</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1133,7 +1139,9 @@
       <c r="B10" t="n">
         <v>33</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>17.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1154,7 +1162,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>38.7</v>
+        <v>56.9</v>
       </c>
     </row>
   </sheetData>
@@ -1240,22 +1248,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>800.3</v>
+        <v>771.4</v>
       </c>
       <c r="D3" t="n">
-        <v>63.8</v>
+        <v>61.4</v>
       </c>
       <c r="E3" t="n">
-        <v>782</v>
+        <v>741</v>
       </c>
       <c r="F3" t="n">
         <v>886</v>
       </c>
       <c r="G3" t="n">
-        <v>733</v>
+        <v>715</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -518,19 +518,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>73.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>96.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>50.7</v>
       </c>
       <c r="H3" t="n">
-        <v>147.6</v>
+        <v>141.8</v>
       </c>
       <c r="I3" t="n">
         <v>876.5</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>65.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>65.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="F4" t="n">
-        <v>65.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>65.59999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="H4" t="n">
-        <v>65.59999999999999</v>
+        <v>140.1</v>
       </c>
       <c r="I4" t="n">
-        <v>894</v>
+        <v>839</v>
       </c>
       <c r="J4" t="n">
-        <v>894</v>
+        <v>945</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>61.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>61.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>61.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>61.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>61.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
       <c r="J5" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>56.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>56.9</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>56.9</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>56.9</v>
+        <v>55.7</v>
       </c>
       <c r="H6" t="n">
-        <v>56.9</v>
+        <v>136.1</v>
       </c>
       <c r="I6" t="n">
-        <v>782</v>
+        <v>833.5</v>
       </c>
       <c r="J6" t="n">
-        <v>782</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>56.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>56.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>87</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>26.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>113.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>839</v>
+        <v>894</v>
       </c>
       <c r="J7" t="n">
-        <v>945</v>
+        <v>894</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="E8" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="F8" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="G8" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="H8" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="I8" t="n">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="J8" t="n">
-        <v>877</v>
+        <v>887</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>55.7</v>
+        <v>56.3</v>
       </c>
       <c r="E9" t="n">
-        <v>55.7</v>
+        <v>56.3</v>
       </c>
       <c r="F9" t="n">
-        <v>80.40000000000001</v>
+        <v>56.3</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>56.3</v>
       </c>
       <c r="H9" t="n">
-        <v>111.4</v>
+        <v>56.3</v>
       </c>
       <c r="I9" t="n">
-        <v>833.5</v>
+        <v>877</v>
       </c>
       <c r="J9" t="n">
-        <v>926</v>
+        <v>877</v>
       </c>
     </row>
     <row r="10">
@@ -756,19 +756,19 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>25.4</v>
+        <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>25.4</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G10" t="n">
         <v>33</v>
       </c>
-      <c r="G10" t="n">
-        <v>17.9</v>
-      </c>
       <c r="H10" t="n">
-        <v>50.9</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>775</v>
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="F12" t="n">
         <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>737</v>
+        <v>611</v>
       </c>
       <c r="J12" t="n">
         <v>737</v>
@@ -992,7 +992,9 @@
       <c r="B11" t="n">
         <v>737</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>485</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1046,7 +1048,7 @@
         <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>26.6</v>
+        <v>53.1</v>
       </c>
     </row>
     <row r="3">
@@ -1070,7 +1072,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="5">
@@ -1116,7 +1118,7 @@
         <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>96.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1140,7 +1142,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>17.9</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="11">
@@ -1152,7 +1154,9 @@
       <c r="B11" t="n">
         <v>3.3</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="n">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1162,7 +1166,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>56.9</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1248,22 +1252,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>771.4</v>
+        <v>723.7</v>
       </c>
       <c r="D3" t="n">
-        <v>61.4</v>
+        <v>120.5</v>
       </c>
       <c r="E3" t="n">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="F3" t="n">
         <v>886</v>
       </c>
       <c r="G3" t="n">
-        <v>715</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,25 +481,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>86.7</v>
+        <v>84.2</v>
       </c>
       <c r="E2" t="n">
-        <v>86.7</v>
+        <v>84.2</v>
       </c>
       <c r="F2" t="n">
         <v>86.7</v>
       </c>
       <c r="G2" t="n">
-        <v>86.7</v>
+        <v>81.7</v>
       </c>
       <c r="H2" t="n">
-        <v>86.7</v>
+        <v>168.4</v>
       </c>
       <c r="I2" t="n">
-        <v>944</v>
+        <v>886.5</v>
       </c>
       <c r="J2" t="n">
         <v>944</v>
@@ -518,19 +518,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E3" t="n">
-        <v>70.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="F3" t="n">
-        <v>91.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="G3" t="n">
         <v>50.7</v>
       </c>
       <c r="H3" t="n">
-        <v>141.8</v>
+        <v>142.4</v>
       </c>
       <c r="I3" t="n">
         <v>876.5</v>
@@ -552,19 +552,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>53.1</v>
+        <v>53.8</v>
       </c>
       <c r="H4" t="n">
-        <v>140.1</v>
+        <v>140.8</v>
       </c>
       <c r="I4" t="n">
         <v>839</v>
@@ -586,19 +586,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>782</v>
@@ -620,19 +620,19 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>68.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>68.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>55.7</v>
+        <v>56.4</v>
       </c>
       <c r="H6" t="n">
-        <v>136.1</v>
+        <v>136.8</v>
       </c>
       <c r="I6" t="n">
         <v>833.5</v>
@@ -756,19 +756,19 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>40.4</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>40.4</v>
       </c>
       <c r="F10" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="G10" t="n">
         <v>33</v>
       </c>
       <c r="H10" t="n">
-        <v>80.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="I10" t="n">
         <v>775</v>
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.4</v>
+        <v>15.9</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4</v>
+        <v>15.9</v>
       </c>
       <c r="F11" t="n">
-        <v>4.4</v>
+        <v>15.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.4</v>
+        <v>15.9</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>15.9</v>
       </c>
       <c r="I11" t="n">
-        <v>746</v>
+        <v>603</v>
       </c>
       <c r="J11" t="n">
-        <v>746</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12">
@@ -817,31 +817,65 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>johnson7</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>746</v>
+      </c>
+      <c r="J12" t="n">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>cartert</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C13" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" t="n">
         <v>2.8</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>2.8</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>3.3</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="G13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I13" t="n">
         <v>611</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>737</v>
       </c>
     </row>
@@ -856,7 +890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,7 +932,9 @@
       <c r="B3" t="n">
         <v>944</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>829</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1005,6 +1041,17 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>782</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Spy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>603</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,7 +1095,7 @@
         <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>53.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="3">
@@ -1060,7 +1107,9 @@
       <c r="B3" t="n">
         <v>86.7</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>81.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1072,7 +1121,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>55.7</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="5">
@@ -1118,7 +1167,7 @@
         <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>91.09999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="9">
@@ -1142,7 +1191,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="11">
@@ -1155,7 +1204,7 @@
         <v>3.3</v>
       </c>
       <c r="C11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -1166,7 +1215,18 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>68.59999999999999</v>
+        <v>69.40000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Spy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="n">
+        <v>15.9</v>
       </c>
     </row>
   </sheetData>
@@ -1252,13 +1312,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>723.7</v>
+        <v>721.8</v>
       </c>
       <c r="D3" t="n">
-        <v>120.5</v>
+        <v>118.7</v>
       </c>
       <c r="E3" t="n">
         <v>737</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,19 +484,19 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>84.2</v>
+        <v>81.8</v>
       </c>
       <c r="E2" t="n">
-        <v>84.2</v>
+        <v>81.8</v>
       </c>
       <c r="F2" t="n">
         <v>86.7</v>
       </c>
       <c r="G2" t="n">
-        <v>81.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>168.4</v>
+        <v>163.6</v>
       </c>
       <c r="I2" t="n">
         <v>886.5</v>
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="E3" t="n">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="F3" t="n">
-        <v>91.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>50.7</v>
+        <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>142.4</v>
+        <v>143.4</v>
       </c>
       <c r="I3" t="n">
-        <v>876.5</v>
+        <v>877</v>
       </c>
       <c r="J3" t="n">
-        <v>886</v>
+        <v>877</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>70.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>70.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>53.8</v>
+        <v>50.7</v>
       </c>
       <c r="H4" t="n">
-        <v>140.8</v>
+        <v>139.3</v>
       </c>
       <c r="I4" t="n">
-        <v>839</v>
+        <v>876.5</v>
       </c>
       <c r="J4" t="n">
-        <v>945</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>69.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="E5" t="n">
-        <v>69.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="F5" t="n">
-        <v>69.40000000000001</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>69.40000000000001</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>69.40000000000001</v>
+        <v>135</v>
       </c>
       <c r="I5" t="n">
-        <v>782</v>
+        <v>839</v>
       </c>
       <c r="J5" t="n">
-        <v>782</v>
+        <v>945</v>
       </c>
     </row>
     <row r="6">
@@ -620,19 +620,19 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>68.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>68.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F6" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>56.4</v>
+        <v>50.7</v>
       </c>
       <c r="H6" t="n">
-        <v>136.8</v>
+        <v>131.1</v>
       </c>
       <c r="I6" t="n">
         <v>833.5</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>61.9</v>
+        <v>63.8</v>
       </c>
       <c r="E8" t="n">
-        <v>61.9</v>
+        <v>63.8</v>
       </c>
       <c r="F8" t="n">
-        <v>61.9</v>
+        <v>63.8</v>
       </c>
       <c r="G8" t="n">
-        <v>61.9</v>
+        <v>63.8</v>
       </c>
       <c r="H8" t="n">
-        <v>61.9</v>
+        <v>63.8</v>
       </c>
       <c r="I8" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
       <c r="J8" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="E9" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="F9" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="G9" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="H9" t="n">
-        <v>56.3</v>
+        <v>61.9</v>
       </c>
       <c r="I9" t="n">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="J9" t="n">
-        <v>877</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10">
@@ -756,19 +756,19 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>40.4</v>
+        <v>37.6</v>
       </c>
       <c r="E10" t="n">
-        <v>40.4</v>
+        <v>37.6</v>
       </c>
       <c r="F10" t="n">
-        <v>47.7</v>
+        <v>42.2</v>
       </c>
       <c r="G10" t="n">
         <v>33</v>
       </c>
       <c r="H10" t="n">
-        <v>80.7</v>
+        <v>75.2</v>
       </c>
       <c r="I10" t="n">
         <v>775</v>
@@ -790,19 +790,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
       <c r="F11" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
       <c r="G11" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
       <c r="H11" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
       <c r="I11" t="n">
         <v>603</v>
@@ -858,19 +858,19 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="F13" t="n">
         <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
         <v>611</v>
@@ -980,7 +980,9 @@
       <c r="B7" t="n">
         <v>877</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>877</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,7 +1097,7 @@
         <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>53.8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -1108,7 +1110,7 @@
         <v>86.7</v>
       </c>
       <c r="C3" t="n">
-        <v>81.7</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1121,7 +1123,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>56.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="5">
@@ -1155,7 +1157,9 @@
       <c r="B7" t="n">
         <v>56.3</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>87.09999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1167,7 +1171,7 @@
         <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1191,7 +1195,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>47.7</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="11">
@@ -1204,7 +1208,7 @@
         <v>3.3</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12">
@@ -1215,7 +1219,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>69.40000000000001</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="13">
@@ -1226,7 +1230,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
     </row>
   </sheetData>
@@ -1312,16 +1316,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>721.8</v>
+        <v>739</v>
       </c>
       <c r="D3" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="E3" t="n">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="F3" t="n">
         <v>886</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,19 +484,19 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="E2" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="F2" t="n">
         <v>86.7</v>
       </c>
       <c r="G2" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="H2" t="n">
-        <v>163.6</v>
+        <v>163.4</v>
       </c>
       <c r="I2" t="n">
         <v>886.5</v>
@@ -518,19 +518,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="E3" t="n">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="F3" t="n">
-        <v>87.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="G3" t="n">
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>143.4</v>
+        <v>143.6</v>
       </c>
       <c r="I3" t="n">
         <v>877</v>
@@ -552,19 +552,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="E4" t="n">
-        <v>69.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="F4" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="G4" t="n">
         <v>50.7</v>
       </c>
       <c r="H4" t="n">
-        <v>139.3</v>
+        <v>139.5</v>
       </c>
       <c r="I4" t="n">
         <v>876.5</v>
@@ -586,19 +586,19 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>67.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>67.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F5" t="n">
         <v>87</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>46.3</v>
       </c>
       <c r="H5" t="n">
-        <v>135</v>
+        <v>133.3</v>
       </c>
       <c r="I5" t="n">
         <v>839</v>
@@ -613,11 +613,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>65.59999999999999</v>
@@ -626,19 +626,19 @@
         <v>65.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>50.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>131.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>833.5</v>
+        <v>894</v>
       </c>
       <c r="J6" t="n">
-        <v>926</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="E7" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="F7" t="n">
-        <v>65.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>65.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>65.59999999999999</v>
+        <v>129.4</v>
       </c>
       <c r="I7" t="n">
-        <v>894</v>
+        <v>833.5</v>
       </c>
       <c r="J7" t="n">
-        <v>894</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>63.8</v>
+        <v>64.7</v>
       </c>
       <c r="E8" t="n">
-        <v>63.8</v>
+        <v>64.7</v>
       </c>
       <c r="F8" t="n">
-        <v>63.8</v>
+        <v>64.7</v>
       </c>
       <c r="G8" t="n">
-        <v>63.8</v>
+        <v>64.7</v>
       </c>
       <c r="H8" t="n">
-        <v>63.8</v>
+        <v>64.7</v>
       </c>
       <c r="I8" t="n">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="J8" t="n">
-        <v>782</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="E9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="F9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="G9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="H9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="I9" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
       <c r="J9" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>37.6</v>
+        <v>61.9</v>
       </c>
       <c r="E10" t="n">
-        <v>37.6</v>
+        <v>61.9</v>
       </c>
       <c r="F10" t="n">
-        <v>42.2</v>
+        <v>61.9</v>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>61.9</v>
       </c>
       <c r="H10" t="n">
-        <v>75.2</v>
+        <v>61.9</v>
       </c>
       <c r="I10" t="n">
-        <v>775</v>
+        <v>887</v>
       </c>
       <c r="J10" t="n">
-        <v>835</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>36.6</v>
       </c>
       <c r="E11" t="n">
-        <v>13.3</v>
+        <v>36.6</v>
       </c>
       <c r="F11" t="n">
-        <v>13.3</v>
+        <v>40.2</v>
       </c>
       <c r="G11" t="n">
-        <v>13.3</v>
+        <v>33</v>
       </c>
       <c r="H11" t="n">
-        <v>13.3</v>
+        <v>73.2</v>
       </c>
       <c r="I11" t="n">
-        <v>603</v>
+        <v>775</v>
       </c>
       <c r="J11" t="n">
-        <v>603</v>
+        <v>835</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="G12" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="I12" t="n">
-        <v>746</v>
+        <v>603</v>
       </c>
       <c r="J12" t="n">
-        <v>746</v>
+        <v>603</v>
       </c>
     </row>
     <row r="13">
@@ -851,31 +851,65 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>johnson7</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>746</v>
+      </c>
+      <c r="J13" t="n">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>cartert</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C14" t="n">
         <v>2</v>
       </c>
-      <c r="D13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="D14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F14" t="n">
         <v>3.3</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="G14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I14" t="n">
         <v>611</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>737</v>
       </c>
     </row>
@@ -890,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1088,17 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>603</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meghan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,7 +1142,7 @@
         <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="3">
@@ -1110,7 +1155,7 @@
         <v>86.7</v>
       </c>
       <c r="C3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="4">
@@ -1123,7 +1168,7 @@
         <v>80.40000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>50.7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
@@ -1158,7 +1203,7 @@
         <v>56.3</v>
       </c>
       <c r="C7" t="n">
-        <v>87.09999999999999</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="8">
@@ -1171,7 +1216,7 @@
         <v>50.7</v>
       </c>
       <c r="C8" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="9">
@@ -1195,7 +1240,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="11">
@@ -1208,7 +1253,7 @@
         <v>3.3</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12">
@@ -1219,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>63.8</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="13">
@@ -1230,7 +1275,18 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>13.3</v>
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Meghan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="n">
+        <v>64.7</v>
       </c>
     </row>
   </sheetData>
@@ -1316,16 +1372,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>739</v>
+        <v>743.9</v>
       </c>
       <c r="D3" t="n">
-        <v>122.1</v>
+        <v>116.8</v>
       </c>
       <c r="E3" t="n">
-        <v>741</v>
+        <v>761.5</v>
       </c>
       <c r="F3" t="n">
         <v>886</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>69.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>69.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>88.8</v>
+        <v>87</v>
       </c>
       <c r="G4" t="n">
-        <v>50.7</v>
+        <v>46.3</v>
       </c>
       <c r="H4" t="n">
-        <v>139.5</v>
+        <v>133.3</v>
       </c>
       <c r="I4" t="n">
-        <v>876.5</v>
+        <v>839</v>
       </c>
       <c r="J4" t="n">
-        <v>886</v>
+        <v>945</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>66.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>66.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>87</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>46.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>133.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>839</v>
+        <v>894</v>
       </c>
       <c r="J5" t="n">
-        <v>945</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="E6" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>65.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>65.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>65.59999999999999</v>
+        <v>129.4</v>
       </c>
       <c r="I6" t="n">
-        <v>894</v>
+        <v>833.5</v>
       </c>
       <c r="J6" t="n">
-        <v>894</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -647,11 +647,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>64.7</v>
@@ -660,19 +660,19 @@
         <v>64.7</v>
       </c>
       <c r="F7" t="n">
-        <v>80.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G7" t="n">
-        <v>49</v>
+        <v>64.7</v>
       </c>
       <c r="H7" t="n">
-        <v>129.4</v>
+        <v>64.7</v>
       </c>
       <c r="I7" t="n">
-        <v>833.5</v>
+        <v>788</v>
       </c>
       <c r="J7" t="n">
-        <v>926</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>64.7</v>
+        <v>63.2</v>
       </c>
       <c r="E8" t="n">
-        <v>64.7</v>
+        <v>50.7</v>
       </c>
       <c r="F8" t="n">
-        <v>64.7</v>
+        <v>88.8</v>
       </c>
       <c r="G8" t="n">
-        <v>64.7</v>
+        <v>50</v>
       </c>
       <c r="H8" t="n">
-        <v>64.7</v>
+        <v>189.5</v>
       </c>
       <c r="I8" t="n">
-        <v>788</v>
+        <v>809.7</v>
       </c>
       <c r="J8" t="n">
-        <v>788</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9">
@@ -924,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,6 +943,11 @@
           <t>9/3/26</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>9/4/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -956,6 +961,7 @@
       <c r="C2" t="n">
         <v>733</v>
       </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -969,6 +975,7 @@
       <c r="C3" t="n">
         <v>829</v>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -982,6 +989,7 @@
       <c r="C4" t="n">
         <v>741</v>
       </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -993,6 +1001,7 @@
         <v>894</v>
       </c>
       <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1004,6 +1013,7 @@
         <v>887</v>
       </c>
       <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1027,7 @@
       <c r="C7" t="n">
         <v>877</v>
       </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1030,6 +1041,9 @@
       <c r="C8" t="n">
         <v>886</v>
       </c>
+      <c r="D8" t="n">
+        <v>676</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1041,6 +1055,7 @@
         <v>746</v>
       </c>
       <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1054,6 +1069,7 @@
       <c r="C10" t="n">
         <v>715</v>
       </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1067,6 +1083,7 @@
       <c r="C11" t="n">
         <v>485</v>
       </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1078,6 +1095,7 @@
       <c r="C12" t="n">
         <v>782</v>
       </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1089,6 +1107,7 @@
       <c r="C13" t="n">
         <v>603</v>
       </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1100,6 +1119,7 @@
       <c r="C14" t="n">
         <v>788</v>
       </c>
+      <c r="D14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1112,7 +1132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,6 +1151,11 @@
           <t>9/3/26</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>9/4/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1144,6 +1169,7 @@
       <c r="C2" t="n">
         <v>46.3</v>
       </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1157,6 +1183,7 @@
       <c r="C3" t="n">
         <v>76.7</v>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1170,6 +1197,7 @@
       <c r="C4" t="n">
         <v>49</v>
       </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1181,6 +1209,7 @@
         <v>65.59999999999999</v>
       </c>
       <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1192,6 +1221,7 @@
         <v>61.9</v>
       </c>
       <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1205,6 +1235,7 @@
       <c r="C7" t="n">
         <v>87.3</v>
       </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1218,6 +1249,9 @@
       <c r="C8" t="n">
         <v>88.8</v>
       </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1229,6 +1263,7 @@
         <v>4.4</v>
       </c>
       <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1242,6 +1277,7 @@
       <c r="C10" t="n">
         <v>40.2</v>
       </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1255,6 +1291,7 @@
       <c r="C11" t="n">
         <v>1.3</v>
       </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1266,6 +1303,7 @@
       <c r="C12" t="n">
         <v>62.8</v>
       </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1277,6 +1315,7 @@
       <c r="C13" t="n">
         <v>11.4</v>
       </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1288,6 +1327,7 @@
       <c r="C14" t="n">
         <v>64.7</v>
       </c>
+      <c r="D14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1300,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1390,6 +1430,31 @@
         <v>485</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9/4/26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>676</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>676</v>
+      </c>
+      <c r="F4" t="n">
+        <v>676</v>
+      </c>
+      <c r="G4" t="n">
+        <v>676</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,25 +481,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>81.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>81.7</v>
+        <v>86.7</v>
       </c>
       <c r="F2" t="n">
-        <v>86.7</v>
+        <v>91.8</v>
       </c>
       <c r="G2" t="n">
         <v>76.7</v>
       </c>
       <c r="H2" t="n">
-        <v>163.4</v>
+        <v>255.2</v>
       </c>
       <c r="I2" t="n">
-        <v>886.5</v>
+        <v>884.7</v>
       </c>
       <c r="J2" t="n">
         <v>944</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>63.2</v>
+        <v>62.8</v>
       </c>
       <c r="E8" t="n">
-        <v>50.7</v>
+        <v>62.8</v>
       </c>
       <c r="F8" t="n">
-        <v>88.8</v>
+        <v>62.8</v>
       </c>
       <c r="G8" t="n">
-        <v>50</v>
+        <v>62.8</v>
       </c>
       <c r="H8" t="n">
-        <v>189.5</v>
+        <v>62.8</v>
       </c>
       <c r="I8" t="n">
-        <v>809.7</v>
+        <v>782</v>
       </c>
       <c r="J8" t="n">
-        <v>886</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
       <c r="E9" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
       <c r="F9" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
       <c r="G9" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
       <c r="H9" t="n">
-        <v>62.8</v>
+        <v>61.9</v>
       </c>
       <c r="I9" t="n">
-        <v>782</v>
+        <v>887</v>
       </c>
       <c r="J9" t="n">
-        <v>782</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>61.9</v>
+        <v>57.2</v>
       </c>
       <c r="E10" t="n">
-        <v>61.9</v>
+        <v>50.7</v>
       </c>
       <c r="F10" t="n">
-        <v>61.9</v>
+        <v>88.8</v>
       </c>
       <c r="G10" t="n">
-        <v>61.9</v>
+        <v>32</v>
       </c>
       <c r="H10" t="n">
-        <v>61.9</v>
+        <v>171.5</v>
       </c>
       <c r="I10" t="n">
-        <v>887</v>
+        <v>809.7</v>
       </c>
       <c r="J10" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="11">
@@ -787,25 +787,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>36.6</v>
+        <v>30.3</v>
       </c>
       <c r="E11" t="n">
-        <v>36.6</v>
+        <v>33</v>
       </c>
       <c r="F11" t="n">
         <v>40.2</v>
       </c>
       <c r="G11" t="n">
-        <v>33</v>
+        <v>17.8</v>
       </c>
       <c r="H11" t="n">
-        <v>73.2</v>
+        <v>91</v>
       </c>
       <c r="I11" t="n">
-        <v>775</v>
+        <v>725.3</v>
       </c>
       <c r="J11" t="n">
         <v>835</v>
@@ -975,7 +975,9 @@
       <c r="C3" t="n">
         <v>829</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>881</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1069,7 +1071,9 @@
       <c r="C10" t="n">
         <v>715</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>626</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1183,7 +1187,9 @@
       <c r="C3" t="n">
         <v>76.7</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>91.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1250,7 +1256,7 @@
         <v>88.8</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -1277,7 +1283,9 @@
       <c r="C10" t="n">
         <v>40.2</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>17.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1437,22 +1445,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>676</v>
+        <v>727.7</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>110.3</v>
       </c>
       <c r="E4" t="n">
         <v>676</v>
       </c>
       <c r="F4" t="n">
-        <v>676</v>
+        <v>881</v>
       </c>
       <c r="G4" t="n">
-        <v>676</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,19 +484,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>85.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
       </c>
       <c r="F2" t="n">
-        <v>91.8</v>
+        <v>96.7</v>
       </c>
       <c r="G2" t="n">
         <v>76.7</v>
       </c>
       <c r="H2" t="n">
-        <v>255.2</v>
+        <v>260.1</v>
       </c>
       <c r="I2" t="n">
         <v>884.7</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>64.7</v>
       </c>
       <c r="E6" t="n">
-        <v>64.7</v>
+        <v>54.7</v>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>50.7</v>
       </c>
       <c r="H6" t="n">
-        <v>129.4</v>
+        <v>194.2</v>
       </c>
       <c r="I6" t="n">
-        <v>833.5</v>
+        <v>809.7</v>
       </c>
       <c r="J6" t="n">
-        <v>926</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7">
@@ -647,11 +647,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>64.7</v>
@@ -660,19 +660,19 @@
         <v>64.7</v>
       </c>
       <c r="F7" t="n">
-        <v>64.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>64.7</v>
+        <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>64.7</v>
+        <v>129.4</v>
       </c>
       <c r="I7" t="n">
-        <v>788</v>
+        <v>833.5</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="E8" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="F8" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="G8" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="H8" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="I8" t="n">
-        <v>782</v>
+        <v>788</v>
       </c>
       <c r="J8" t="n">
-        <v>782</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="E9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="F9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="G9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="H9" t="n">
-        <v>61.9</v>
+        <v>62.8</v>
       </c>
       <c r="I9" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
       <c r="J9" t="n">
-        <v>887</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>57.2</v>
+        <v>45</v>
       </c>
       <c r="E10" t="n">
-        <v>50.7</v>
+        <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>88.8</v>
+        <v>61.9</v>
       </c>
       <c r="G10" t="n">
-        <v>32</v>
+        <v>28.2</v>
       </c>
       <c r="H10" t="n">
-        <v>171.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>809.7</v>
+        <v>740</v>
       </c>
       <c r="J10" t="n">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11">
@@ -790,19 +790,19 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>30.3</v>
+        <v>37.1</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>38.2</v>
       </c>
       <c r="F11" t="n">
         <v>40.2</v>
       </c>
       <c r="G11" t="n">
-        <v>17.8</v>
+        <v>33</v>
       </c>
       <c r="H11" t="n">
-        <v>91</v>
+        <v>111.4</v>
       </c>
       <c r="I11" t="n">
         <v>725.3</v>
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.4</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>11.4</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>11.4</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>11.4</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>603</v>
+        <v>533</v>
       </c>
       <c r="J12" t="n">
-        <v>603</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="F13" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>11.4</v>
       </c>
       <c r="I13" t="n">
-        <v>746</v>
+        <v>603</v>
       </c>
       <c r="J13" t="n">
-        <v>746</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14">
@@ -885,31 +885,65 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>johnson7</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>746</v>
+      </c>
+      <c r="J14" t="n">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>cartert</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C15" t="n">
         <v>2</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>2.3</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>2.3</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>3.3</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G15" t="n">
         <v>1.3</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>4.6</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>611</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>737</v>
       </c>
     </row>
@@ -924,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,7 +1049,9 @@
         <v>887</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>593</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1124,6 +1160,18 @@
         <v>788</v>
       </c>
       <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>brhunt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>533</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1136,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,7 +1236,7 @@
         <v>76.7</v>
       </c>
       <c r="D3" t="n">
-        <v>91.8</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="4">
@@ -1227,7 +1275,9 @@
         <v>61.9</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>28.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1256,7 +1306,7 @@
         <v>88.8</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="9">
@@ -1284,7 +1334,7 @@
         <v>40.2</v>
       </c>
       <c r="D10" t="n">
-        <v>17.8</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="11">
@@ -1336,6 +1386,18 @@
         <v>64.7</v>
       </c>
       <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>brhunt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1445,22 +1507,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>727.7</v>
+        <v>661.8</v>
       </c>
       <c r="D4" t="n">
-        <v>110.3</v>
+        <v>119</v>
       </c>
       <c r="E4" t="n">
-        <v>676</v>
+        <v>626</v>
       </c>
       <c r="F4" t="n">
         <v>881</v>
       </c>
       <c r="G4" t="n">
-        <v>626</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,19 +484,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>86.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
       </c>
       <c r="F2" t="n">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="G2" t="n">
         <v>76.7</v>
       </c>
       <c r="H2" t="n">
-        <v>260.1</v>
+        <v>258.4</v>
       </c>
       <c r="I2" t="n">
         <v>884.7</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>66.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
-        <v>66.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="F4" t="n">
         <v>87</v>
@@ -564,10 +564,10 @@
         <v>46.3</v>
       </c>
       <c r="H4" t="n">
-        <v>133.3</v>
+        <v>198.1</v>
       </c>
       <c r="I4" t="n">
-        <v>839</v>
+        <v>805</v>
       </c>
       <c r="J4" t="n">
         <v>945</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>64.7</v>
       </c>
       <c r="E6" t="n">
-        <v>54.7</v>
+        <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>88.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>50.7</v>
+        <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>194.2</v>
+        <v>129.4</v>
       </c>
       <c r="I6" t="n">
-        <v>809.7</v>
+        <v>833.5</v>
       </c>
       <c r="J6" t="n">
-        <v>886</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -647,11 +647,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>64.7</v>
@@ -660,19 +660,19 @@
         <v>64.7</v>
       </c>
       <c r="F7" t="n">
-        <v>80.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G7" t="n">
-        <v>49</v>
+        <v>64.7</v>
       </c>
       <c r="H7" t="n">
-        <v>129.4</v>
+        <v>64.7</v>
       </c>
       <c r="I7" t="n">
-        <v>833.5</v>
+        <v>788</v>
       </c>
       <c r="J7" t="n">
-        <v>926</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>64.7</v>
+        <v>62.8</v>
       </c>
       <c r="E8" t="n">
-        <v>64.7</v>
+        <v>62.8</v>
       </c>
       <c r="F8" t="n">
-        <v>64.7</v>
+        <v>62.8</v>
       </c>
       <c r="G8" t="n">
-        <v>64.7</v>
+        <v>62.8</v>
       </c>
       <c r="H8" t="n">
-        <v>64.7</v>
+        <v>62.8</v>
       </c>
       <c r="I8" t="n">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="J8" t="n">
-        <v>788</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>62.8</v>
+        <v>61.1</v>
       </c>
       <c r="E9" t="n">
-        <v>62.8</v>
+        <v>50.7</v>
       </c>
       <c r="F9" t="n">
-        <v>62.8</v>
+        <v>88.8</v>
       </c>
       <c r="G9" t="n">
-        <v>62.8</v>
+        <v>43.9</v>
       </c>
       <c r="H9" t="n">
-        <v>62.8</v>
+        <v>183.4</v>
       </c>
       <c r="I9" t="n">
-        <v>782</v>
+        <v>809.7</v>
       </c>
       <c r="J9" t="n">
-        <v>782</v>
+        <v>886</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>47.9</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>47.9</v>
       </c>
       <c r="F10" t="n">
-        <v>61.9</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>28.2</v>
+        <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>90.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="I10" t="n">
-        <v>740</v>
+        <v>706</v>
       </c>
       <c r="J10" t="n">
-        <v>887</v>
+        <v>809</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>37.1</v>
+        <v>40.4</v>
       </c>
       <c r="E11" t="n">
-        <v>38.2</v>
+        <v>40.4</v>
       </c>
       <c r="F11" t="n">
-        <v>40.2</v>
+        <v>61.9</v>
       </c>
       <c r="G11" t="n">
-        <v>33</v>
+        <v>18.9</v>
       </c>
       <c r="H11" t="n">
-        <v>111.4</v>
+        <v>80.8</v>
       </c>
       <c r="I11" t="n">
-        <v>725.3</v>
+        <v>740</v>
       </c>
       <c r="J11" t="n">
-        <v>835</v>
+        <v>887</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>33.6</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>27.7</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>100.9</v>
       </c>
       <c r="I12" t="n">
-        <v>533</v>
+        <v>725.3</v>
       </c>
       <c r="J12" t="n">
-        <v>533</v>
+        <v>835</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>11.4</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
-        <v>603</v>
+        <v>533</v>
       </c>
       <c r="J13" t="n">
-        <v>603</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14">
@@ -995,7 +995,9 @@
       <c r="C2" t="n">
         <v>733</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>737</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1147,7 +1149,9 @@
       <c r="C13" t="n">
         <v>603</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>809</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1221,7 +1225,9 @@
       <c r="C2" t="n">
         <v>46.3</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>64.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1236,7 +1242,7 @@
         <v>76.7</v>
       </c>
       <c r="D3" t="n">
-        <v>96.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4">
@@ -1276,7 +1282,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>28.2</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="7">
@@ -1306,7 +1312,7 @@
         <v>88.8</v>
       </c>
       <c r="D8" t="n">
-        <v>54.7</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="9">
@@ -1334,7 +1340,7 @@
         <v>40.2</v>
       </c>
       <c r="D10" t="n">
-        <v>38.2</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="11">
@@ -1373,7 +1379,9 @@
       <c r="C13" t="n">
         <v>11.4</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>84.40000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1396,7 +1404,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1507,16 +1515,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>661.8</v>
+        <v>693.6</v>
       </c>
       <c r="D4" t="n">
-        <v>119</v>
+        <v>114.1</v>
       </c>
       <c r="E4" t="n">
-        <v>626</v>
+        <v>676</v>
       </c>
       <c r="F4" t="n">
         <v>881</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,19 +484,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>86.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
       </c>
       <c r="F2" t="n">
-        <v>95</v>
+        <v>93.7</v>
       </c>
       <c r="G2" t="n">
         <v>76.7</v>
       </c>
       <c r="H2" t="n">
-        <v>258.4</v>
+        <v>257.1</v>
       </c>
       <c r="I2" t="n">
         <v>884.7</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>71.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>71.8</v>
+        <v>81.2</v>
       </c>
       <c r="F3" t="n">
         <v>87.3</v>
@@ -530,10 +530,10 @@
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>143.6</v>
+        <v>224.8</v>
       </c>
       <c r="I3" t="n">
-        <v>877</v>
+        <v>854</v>
       </c>
       <c r="J3" t="n">
         <v>877</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>64.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>87</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>46.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>198.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>805</v>
+        <v>894</v>
       </c>
       <c r="J4" t="n">
-        <v>945</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="E5" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="F5" t="n">
-        <v>65.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>65.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>65.59999999999999</v>
+        <v>129.4</v>
       </c>
       <c r="I5" t="n">
-        <v>894</v>
+        <v>833.5</v>
       </c>
       <c r="J5" t="n">
-        <v>894</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6">
@@ -613,11 +613,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>64.7</v>
@@ -626,19 +626,19 @@
         <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>64.7</v>
       </c>
       <c r="H6" t="n">
-        <v>129.4</v>
+        <v>64.7</v>
       </c>
       <c r="I6" t="n">
-        <v>833.5</v>
+        <v>788</v>
       </c>
       <c r="J6" t="n">
-        <v>926</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>64.7</v>
+        <v>64.5</v>
       </c>
       <c r="E7" t="n">
-        <v>64.7</v>
+        <v>60.1</v>
       </c>
       <c r="F7" t="n">
-        <v>64.7</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>64.7</v>
+        <v>46.3</v>
       </c>
       <c r="H7" t="n">
-        <v>64.7</v>
+        <v>193.4</v>
       </c>
       <c r="I7" t="n">
-        <v>788</v>
+        <v>805</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>945</v>
       </c>
     </row>
     <row r="8">
@@ -722,7 +722,7 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>61.1</v>
+        <v>59.5</v>
       </c>
       <c r="E9" t="n">
         <v>50.7</v>
@@ -731,10 +731,10 @@
         <v>88.8</v>
       </c>
       <c r="G9" t="n">
-        <v>43.9</v>
+        <v>38.9</v>
       </c>
       <c r="H9" t="n">
-        <v>183.4</v>
+        <v>178.4</v>
       </c>
       <c r="I9" t="n">
         <v>809.7</v>
@@ -756,19 +756,19 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>47.9</v>
+        <v>46.4</v>
       </c>
       <c r="E10" t="n">
-        <v>47.9</v>
+        <v>46.4</v>
       </c>
       <c r="F10" t="n">
-        <v>84.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>95.8</v>
+        <v>92.8</v>
       </c>
       <c r="I10" t="n">
         <v>706</v>
@@ -790,19 +790,19 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>40.4</v>
+        <v>38.7</v>
       </c>
       <c r="E11" t="n">
-        <v>40.4</v>
+        <v>38.7</v>
       </c>
       <c r="F11" t="n">
         <v>61.9</v>
       </c>
       <c r="G11" t="n">
-        <v>18.9</v>
+        <v>15.5</v>
       </c>
       <c r="H11" t="n">
-        <v>80.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>740</v>
@@ -824,7 +824,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>33.6</v>
+        <v>32.2</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
@@ -833,10 +833,10 @@
         <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>27.7</v>
+        <v>23.5</v>
       </c>
       <c r="H12" t="n">
-        <v>100.9</v>
+        <v>96.7</v>
       </c>
       <c r="I12" t="n">
         <v>725.3</v>
@@ -858,19 +858,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="I13" t="n">
         <v>533</v>
@@ -1067,7 +1067,9 @@
       <c r="C7" t="n">
         <v>877</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>808</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1226,7 +1228,7 @@
         <v>46.3</v>
       </c>
       <c r="D2" t="n">
-        <v>64.8</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="3">
@@ -1242,7 +1244,7 @@
         <v>76.7</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="4">
@@ -1282,7 +1284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="7">
@@ -1297,7 +1299,9 @@
       <c r="C7" t="n">
         <v>87.3</v>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1312,7 +1316,7 @@
         <v>88.8</v>
       </c>
       <c r="D8" t="n">
-        <v>43.9</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="9">
@@ -1340,7 +1344,7 @@
         <v>40.2</v>
       </c>
       <c r="D10" t="n">
-        <v>27.7</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="11">
@@ -1380,7 +1384,7 @@
         <v>11.4</v>
       </c>
       <c r="D13" t="n">
-        <v>84.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1404,7 +1408,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1515,16 +1519,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>693.6</v>
+        <v>707.9</v>
       </c>
       <c r="D4" t="n">
-        <v>114.1</v>
+        <v>113.2</v>
       </c>
       <c r="E4" t="n">
-        <v>676</v>
+        <v>706.5</v>
       </c>
       <c r="F4" t="n">
         <v>881</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>38.7</v>
+        <v>42.5</v>
       </c>
       <c r="E11" t="n">
-        <v>38.7</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
         <v>61.9</v>
@@ -802,10 +802,10 @@
         <v>15.5</v>
       </c>
       <c r="H11" t="n">
-        <v>77.40000000000001</v>
+        <v>127.4</v>
       </c>
       <c r="I11" t="n">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="J11" t="n">
         <v>887</v>
@@ -958,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,6 +982,11 @@
           <t>9/4/26</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>9/5/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -998,6 +1003,7 @@
       <c r="D2" t="n">
         <v>737</v>
       </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1014,6 +1020,7 @@
       <c r="D3" t="n">
         <v>881</v>
       </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1028,6 +1035,7 @@
         <v>741</v>
       </c>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1040,6 +1048,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1054,6 +1063,9 @@
       <c r="D6" t="n">
         <v>593</v>
       </c>
+      <c r="E6" t="n">
+        <v>857</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1070,6 +1082,7 @@
       <c r="D7" t="n">
         <v>808</v>
       </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1086,6 +1099,7 @@
       <c r="D8" t="n">
         <v>676</v>
       </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1098,6 +1112,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1114,6 +1129,7 @@
       <c r="D10" t="n">
         <v>626</v>
       </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1128,6 +1144,7 @@
         <v>485</v>
       </c>
       <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1140,6 +1157,7 @@
         <v>782</v>
       </c>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1154,6 +1172,7 @@
       <c r="D13" t="n">
         <v>809</v>
       </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1166,6 +1185,7 @@
         <v>788</v>
       </c>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1178,6 +1198,7 @@
       <c r="D15" t="n">
         <v>533</v>
       </c>
+      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1190,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1214,6 +1235,11 @@
           <t>9/4/26</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>9/5/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1230,6 +1256,7 @@
       <c r="D2" t="n">
         <v>60.1</v>
       </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1246,6 +1273,7 @@
       <c r="D3" t="n">
         <v>93.7</v>
       </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1260,6 +1288,7 @@
         <v>49</v>
       </c>
       <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1272,6 +1301,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1286,6 +1316,9 @@
       <c r="D6" t="n">
         <v>15.5</v>
       </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1302,6 +1335,7 @@
       <c r="D7" t="n">
         <v>81.2</v>
       </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1318,6 +1352,7 @@
       <c r="D8" t="n">
         <v>38.9</v>
       </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1330,6 +1365,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1346,6 +1382,7 @@
       <c r="D10" t="n">
         <v>23.5</v>
       </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1360,6 +1397,7 @@
         <v>1.3</v>
       </c>
       <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1372,6 +1410,7 @@
         <v>62.8</v>
       </c>
       <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1386,6 +1425,7 @@
       <c r="D13" t="n">
         <v>81.40000000000001</v>
       </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1398,6 +1438,7 @@
         <v>64.7</v>
       </c>
       <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1410,6 +1451,7 @@
       <c r="D15" t="n">
         <v>6.1</v>
       </c>
+      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1422,7 +1464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,6 +1579,31 @@
         <v>533</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9/5/26</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>857</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>857</v>
+      </c>
+      <c r="F5" t="n">
+        <v>857</v>
+      </c>
+      <c r="G5" t="n">
+        <v>857</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>46.4</v>
+        <v>53.8</v>
       </c>
       <c r="E10" t="n">
-        <v>46.4</v>
+        <v>61.9</v>
       </c>
       <c r="F10" t="n">
-        <v>81.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>92.8</v>
+        <v>161.5</v>
       </c>
       <c r="I10" t="n">
-        <v>706</v>
+        <v>779</v>
       </c>
       <c r="J10" t="n">
-        <v>809</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>42.5</v>
+        <v>46.4</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
       <c r="F11" t="n">
-        <v>61.9</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="H11" t="n">
-        <v>127.4</v>
+        <v>92.8</v>
       </c>
       <c r="I11" t="n">
-        <v>779</v>
+        <v>706</v>
       </c>
       <c r="J11" t="n">
-        <v>887</v>
+        <v>809</v>
       </c>
     </row>
     <row r="12">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>32.2</v>
+        <v>28.2</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>28.2</v>
       </c>
       <c r="F12" t="n">
         <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>23.5</v>
+        <v>15.9</v>
       </c>
       <c r="H12" t="n">
-        <v>96.7</v>
+        <v>112.6</v>
       </c>
       <c r="I12" t="n">
-        <v>725.3</v>
+        <v>723.2</v>
       </c>
       <c r="J12" t="n">
         <v>835</v>
@@ -1129,7 +1129,9 @@
       <c r="D10" t="n">
         <v>626</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>717</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1317,7 +1319,7 @@
         <v>15.5</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1382,7 +1384,9 @@
       <c r="D10" t="n">
         <v>23.5</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1586,22 +1590,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>857</v>
+        <v>787</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E5" t="n">
-        <v>857</v>
+        <v>787</v>
       </c>
       <c r="F5" t="n">
         <v>857</v>
       </c>
       <c r="G5" t="n">
-        <v>857</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>85.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>86.7</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
         <v>93.7</v>
@@ -496,10 +496,10 @@
         <v>76.7</v>
       </c>
       <c r="H2" t="n">
-        <v>257.1</v>
+        <v>338.3</v>
       </c>
       <c r="I2" t="n">
-        <v>884.7</v>
+        <v>884.5</v>
       </c>
       <c r="J2" t="n">
         <v>944</v>
@@ -756,19 +756,19 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>53.8</v>
+        <v>49</v>
       </c>
       <c r="E10" t="n">
         <v>61.9</v>
       </c>
       <c r="F10" t="n">
-        <v>84.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="G10" t="n">
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>161.5</v>
+        <v>147.1</v>
       </c>
       <c r="I10" t="n">
         <v>779</v>
@@ -824,7 +824,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>28.2</v>
+        <v>26.2</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -833,10 +833,10 @@
         <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>15.9</v>
+        <v>8.1</v>
       </c>
       <c r="H12" t="n">
-        <v>112.6</v>
+        <v>104.8</v>
       </c>
       <c r="I12" t="n">
         <v>723.2</v>
@@ -1020,7 +1020,9 @@
       <c r="D3" t="n">
         <v>881</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>884</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1275,7 +1277,9 @@
       <c r="D3" t="n">
         <v>93.7</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>81.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1319,7 +1323,7 @@
         <v>15.5</v>
       </c>
       <c r="E6" t="n">
-        <v>84.09999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="7">
@@ -1385,7 +1389,7 @@
         <v>23.5</v>
       </c>
       <c r="E10" t="n">
-        <v>15.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="11">
@@ -1590,19 +1594,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>787</v>
+        <v>819.3</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>73.2</v>
       </c>
       <c r="E5" t="n">
-        <v>787</v>
+        <v>857</v>
       </c>
       <c r="F5" t="n">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="G5" t="n">
         <v>717</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>84.59999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>87.2</v>
       </c>
       <c r="F2" t="n">
         <v>93.7</v>
@@ -496,7 +496,7 @@
         <v>76.7</v>
       </c>
       <c r="H2" t="n">
-        <v>338.3</v>
+        <v>344.7</v>
       </c>
       <c r="I2" t="n">
         <v>884.5</v>
@@ -756,19 +756,19 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>52.3</v>
       </c>
       <c r="E10" t="n">
         <v>61.9</v>
       </c>
       <c r="F10" t="n">
-        <v>69.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>147.1</v>
+        <v>157</v>
       </c>
       <c r="I10" t="n">
         <v>779</v>
@@ -824,7 +824,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>26.2</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -833,10 +833,10 @@
         <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>8.1</v>
+        <v>19.1</v>
       </c>
       <c r="H12" t="n">
-        <v>104.8</v>
+        <v>115.8</v>
       </c>
       <c r="I12" t="n">
         <v>723.2</v>
@@ -855,28 +855,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>6.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1</v>
+        <v>13.5</v>
       </c>
       <c r="G13" t="n">
         <v>6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>6.1</v>
+        <v>19.6</v>
       </c>
       <c r="I13" t="n">
-        <v>533</v>
+        <v>615.5</v>
       </c>
       <c r="J13" t="n">
-        <v>533</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14">
@@ -1202,7 +1202,9 @@
       <c r="D15" t="n">
         <v>533</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>698</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1278,7 +1280,7 @@
         <v>93.7</v>
       </c>
       <c r="E3" t="n">
-        <v>81.2</v>
+        <v>87.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1323,7 +1325,7 @@
         <v>15.5</v>
       </c>
       <c r="E6" t="n">
-        <v>69.7</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1389,7 +1391,7 @@
         <v>23.5</v>
       </c>
       <c r="E10" t="n">
-        <v>8.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="11">
@@ -1459,7 +1461,9 @@
       <c r="D15" t="n">
         <v>6.1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>13.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1594,22 +1598,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>819.3</v>
+        <v>789</v>
       </c>
       <c r="D5" t="n">
-        <v>73.2</v>
+        <v>82.3</v>
       </c>
       <c r="E5" t="n">
-        <v>857</v>
+        <v>787</v>
       </c>
       <c r="F5" t="n">
         <v>884</v>
       </c>
       <c r="G5" t="n">
-        <v>717</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,19 +484,19 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>86.2</v>
+        <v>82.2</v>
       </c>
       <c r="E2" t="n">
-        <v>87.2</v>
+        <v>81.7</v>
       </c>
       <c r="F2" t="n">
         <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>76.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>344.7</v>
+        <v>329</v>
       </c>
       <c r="I2" t="n">
         <v>884.5</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>65.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="E4" t="n">
-        <v>65.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>65.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="G4" t="n">
-        <v>65.59999999999999</v>
+        <v>46.3</v>
       </c>
       <c r="H4" t="n">
-        <v>65.59999999999999</v>
+        <v>285.2</v>
       </c>
       <c r="I4" t="n">
-        <v>894</v>
+        <v>845.5</v>
       </c>
       <c r="J4" t="n">
-        <v>894</v>
+        <v>967</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>80.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>129.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>833.5</v>
+        <v>894</v>
       </c>
       <c r="J5" t="n">
-        <v>926</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6">
@@ -613,11 +613,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>64.7</v>
@@ -626,19 +626,19 @@
         <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>64.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>64.7</v>
+        <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>64.7</v>
+        <v>129.4</v>
       </c>
       <c r="I6" t="n">
-        <v>788</v>
+        <v>833.5</v>
       </c>
       <c r="J6" t="n">
-        <v>788</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>64.5</v>
+        <v>64.7</v>
       </c>
       <c r="E7" t="n">
-        <v>60.1</v>
+        <v>64.7</v>
       </c>
       <c r="F7" t="n">
-        <v>87</v>
+        <v>64.7</v>
       </c>
       <c r="G7" t="n">
-        <v>46.3</v>
+        <v>64.7</v>
       </c>
       <c r="H7" t="n">
-        <v>193.4</v>
+        <v>64.7</v>
       </c>
       <c r="I7" t="n">
-        <v>805</v>
+        <v>788</v>
       </c>
       <c r="J7" t="n">
-        <v>945</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -756,19 +756,19 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>52.3</v>
+        <v>46.6</v>
       </c>
       <c r="E10" t="n">
         <v>61.9</v>
       </c>
       <c r="F10" t="n">
-        <v>79.59999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="G10" t="n">
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>157</v>
+        <v>139.8</v>
       </c>
       <c r="I10" t="n">
         <v>779</v>
@@ -824,7 +824,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>27.8</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -833,10 +833,10 @@
         <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>19.1</v>
+        <v>14.7</v>
       </c>
       <c r="H12" t="n">
-        <v>115.8</v>
+        <v>111.4</v>
       </c>
       <c r="I12" t="n">
         <v>723.2</v>
@@ -858,19 +858,19 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="E13" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="F13" t="n">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
       <c r="G13" t="n">
         <v>6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>19.6</v>
+        <v>16.9</v>
       </c>
       <c r="I13" t="n">
         <v>615.5</v>
@@ -1003,7 +1003,9 @@
       <c r="D2" t="n">
         <v>737</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>967</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1262,7 +1264,9 @@
       <c r="D2" t="n">
         <v>60.1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>91.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1280,7 +1284,7 @@
         <v>93.7</v>
       </c>
       <c r="E3" t="n">
-        <v>87.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1325,7 +1329,7 @@
         <v>15.5</v>
       </c>
       <c r="E6" t="n">
-        <v>79.59999999999999</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="7">
@@ -1391,7 +1395,7 @@
         <v>23.5</v>
       </c>
       <c r="E10" t="n">
-        <v>19.1</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="11">
@@ -1462,7 +1466,7 @@
         <v>6.1</v>
       </c>
       <c r="E15" t="n">
-        <v>13.5</v>
+        <v>10.8</v>
       </c>
     </row>
   </sheetData>
@@ -1598,19 +1602,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>789</v>
+        <v>824.6</v>
       </c>
       <c r="D5" t="n">
-        <v>82.3</v>
+        <v>102.4</v>
       </c>
       <c r="E5" t="n">
-        <v>787</v>
+        <v>857</v>
       </c>
       <c r="F5" t="n">
-        <v>884</v>
+        <v>967</v>
       </c>
       <c r="G5" t="n">
         <v>698</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>82.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>81.7</v>
@@ -493,10 +493,10 @@
         <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>71.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="H2" t="n">
-        <v>329</v>
+        <v>325.8</v>
       </c>
       <c r="I2" t="n">
         <v>884.5</v>
@@ -552,19 +552,19 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
       <c r="G4" t="n">
         <v>46.3</v>
       </c>
       <c r="H4" t="n">
-        <v>285.2</v>
+        <v>284.4</v>
       </c>
       <c r="I4" t="n">
         <v>845.5</v>
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>46.6</v>
+        <v>55.3</v>
       </c>
       <c r="E10" t="n">
-        <v>61.9</v>
+        <v>73.2</v>
       </c>
       <c r="F10" t="n">
-        <v>62.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>139.8</v>
+        <v>166</v>
       </c>
       <c r="I10" t="n">
-        <v>779</v>
+        <v>769.7</v>
       </c>
       <c r="J10" t="n">
-        <v>887</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>46.4</v>
+        <v>45.2</v>
       </c>
       <c r="E11" t="n">
-        <v>46.4</v>
+        <v>58.3</v>
       </c>
       <c r="F11" t="n">
-        <v>81.40000000000001</v>
+        <v>61.9</v>
       </c>
       <c r="G11" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="H11" t="n">
-        <v>92.8</v>
+        <v>135.7</v>
       </c>
       <c r="I11" t="n">
-        <v>706</v>
+        <v>779</v>
       </c>
       <c r="J11" t="n">
-        <v>809</v>
+        <v>887</v>
       </c>
     </row>
     <row r="12">
@@ -824,7 +824,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>27.8</v>
+        <v>26.9</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -833,10 +833,10 @@
         <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
       <c r="H12" t="n">
-        <v>111.4</v>
+        <v>107.6</v>
       </c>
       <c r="I12" t="n">
         <v>723.2</v>
@@ -858,19 +858,19 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="E13" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="n">
-        <v>10.8</v>
+        <v>7.7</v>
       </c>
       <c r="G13" t="n">
         <v>6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>16.9</v>
+        <v>13.8</v>
       </c>
       <c r="I13" t="n">
         <v>615.5</v>
@@ -1178,7 +1178,9 @@
       <c r="D13" t="n">
         <v>809</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>897</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1265,7 +1267,7 @@
         <v>60.1</v>
       </c>
       <c r="E2" t="n">
-        <v>91.8</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -1284,7 +1286,7 @@
         <v>93.7</v>
       </c>
       <c r="E3" t="n">
-        <v>71.90000000000001</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="4">
@@ -1329,7 +1331,7 @@
         <v>15.5</v>
       </c>
       <c r="E6" t="n">
-        <v>62.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="7">
@@ -1395,7 +1397,7 @@
         <v>23.5</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="11">
@@ -1439,7 +1441,9 @@
       <c r="D13" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>73.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1466,7 +1470,7 @@
         <v>6.1</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1602,16 +1606,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>824.6</v>
+        <v>836.7</v>
       </c>
       <c r="D5" t="n">
-        <v>102.4</v>
+        <v>97.3</v>
       </c>
       <c r="E5" t="n">
-        <v>857</v>
+        <v>870.5</v>
       </c>
       <c r="F5" t="n">
         <v>967</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>81.40000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>81.7</v>
@@ -493,10 +493,10 @@
         <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>68.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>325.8</v>
+        <v>324.5</v>
       </c>
       <c r="I2" t="n">
         <v>884.5</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>74.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>81.2</v>
+        <v>73.3</v>
       </c>
       <c r="F3" t="n">
         <v>87.3</v>
@@ -530,13 +530,13 @@
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>224.8</v>
+        <v>290.2</v>
       </c>
       <c r="I3" t="n">
-        <v>854</v>
+        <v>860.2</v>
       </c>
       <c r="J3" t="n">
-        <v>877</v>
+        <v>879</v>
       </c>
     </row>
     <row r="4">
@@ -552,19 +552,19 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="E4" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>91</v>
+        <v>91.3</v>
       </c>
       <c r="G4" t="n">
         <v>46.3</v>
       </c>
       <c r="H4" t="n">
-        <v>284.4</v>
+        <v>284.7</v>
       </c>
       <c r="I4" t="n">
         <v>845.5</v>
@@ -756,10 +756,10 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>55.3</v>
+        <v>55.1</v>
       </c>
       <c r="E10" t="n">
-        <v>73.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F10" t="n">
         <v>81.40000000000001</v>
@@ -768,7 +768,7 @@
         <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>166</v>
+        <v>165.2</v>
       </c>
       <c r="I10" t="n">
         <v>769.7</v>
@@ -790,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>45.2</v>
+        <v>44.5</v>
       </c>
       <c r="E11" t="n">
-        <v>58.3</v>
+        <v>56.2</v>
       </c>
       <c r="F11" t="n">
         <v>61.9</v>
@@ -802,7 +802,7 @@
         <v>15.5</v>
       </c>
       <c r="H11" t="n">
-        <v>135.7</v>
+        <v>133.6</v>
       </c>
       <c r="I11" t="n">
         <v>779</v>
@@ -824,7 +824,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>26.9</v>
+        <v>26.3</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -833,10 +833,10 @@
         <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>10.9</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>107.6</v>
+        <v>105.1</v>
       </c>
       <c r="I12" t="n">
         <v>723.2</v>
@@ -858,19 +858,19 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="F13" t="n">
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="I13" t="n">
         <v>615.5</v>
@@ -1086,7 +1086,9 @@
       <c r="D7" t="n">
         <v>808</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>879</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1267,7 +1269,7 @@
         <v>60.1</v>
       </c>
       <c r="E2" t="n">
-        <v>91</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="3">
@@ -1286,7 +1288,7 @@
         <v>93.7</v>
       </c>
       <c r="E3" t="n">
-        <v>68.7</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1331,7 +1333,7 @@
         <v>15.5</v>
       </c>
       <c r="E6" t="n">
-        <v>58.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="7">
@@ -1349,7 +1351,9 @@
       <c r="D7" t="n">
         <v>81.2</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>65.40000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1397,7 +1401,7 @@
         <v>23.5</v>
       </c>
       <c r="E10" t="n">
-        <v>10.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="11">
@@ -1442,7 +1446,7 @@
         <v>81.40000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>73.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1470,7 +1474,7 @@
         <v>6.1</v>
       </c>
       <c r="E15" t="n">
-        <v>7.7</v>
+        <v>5.7</v>
       </c>
     </row>
   </sheetData>
@@ -1606,16 +1610,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>836.7</v>
+        <v>842.7</v>
       </c>
       <c r="D5" t="n">
-        <v>97.3</v>
+        <v>91.3</v>
       </c>
       <c r="E5" t="n">
-        <v>870.5</v>
+        <v>879</v>
       </c>
       <c r="F5" t="n">
         <v>967</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -855,25 +855,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9</v>
+        <v>20.6</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
         <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>11.8</v>
+        <v>61.8</v>
       </c>
       <c r="I13" t="n">
-        <v>615.5</v>
+        <v>587.7</v>
       </c>
       <c r="J13" t="n">
         <v>698</v>
@@ -958,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,11 @@
           <t>9/5/26</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>9/6/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1006,6 +1011,7 @@
       <c r="E2" t="n">
         <v>967</v>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1025,6 +1031,7 @@
       <c r="E3" t="n">
         <v>884</v>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1040,6 +1047,7 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1053,6 +1061,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1070,6 +1079,7 @@
       <c r="E6" t="n">
         <v>857</v>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1089,6 +1099,7 @@
       <c r="E7" t="n">
         <v>879</v>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1106,6 +1117,7 @@
         <v>676</v>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1119,6 +1131,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1138,6 +1151,7 @@
       <c r="E10" t="n">
         <v>717</v>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1153,6 +1167,7 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1166,6 +1181,7 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1183,6 +1199,7 @@
       <c r="E13" t="n">
         <v>897</v>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1196,6 +1213,7 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1210,6 +1228,9 @@
       </c>
       <c r="E15" t="n">
         <v>698</v>
+      </c>
+      <c r="F15" t="n">
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -1223,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,6 +1273,11 @@
           <t>9/5/26</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>9/6/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1271,6 +1297,7 @@
       <c r="E2" t="n">
         <v>91.3</v>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1290,6 +1317,7 @@
       <c r="E3" t="n">
         <v>67.40000000000001</v>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1305,6 +1333,7 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1318,6 +1347,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1335,6 +1365,7 @@
       <c r="E6" t="n">
         <v>56.2</v>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1354,6 +1385,7 @@
       <c r="E7" t="n">
         <v>65.40000000000001</v>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1371,6 +1403,7 @@
         <v>38.9</v>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1384,6 +1417,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1403,6 +1437,7 @@
       <c r="E10" t="n">
         <v>8.4</v>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1418,6 +1453,7 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1431,6 +1467,7 @@
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1448,6 +1485,7 @@
       <c r="E13" t="n">
         <v>72.40000000000001</v>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1461,6 +1499,7 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1475,6 +1514,9 @@
       </c>
       <c r="E15" t="n">
         <v>5.7</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1628,6 +1670,31 @@
         <v>698</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>9/6/26</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>532</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>532</v>
+      </c>
+      <c r="F6" t="n">
+        <v>532</v>
+      </c>
+      <c r="G6" t="n">
+        <v>532</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>59.5</v>
+        <v>62.3</v>
       </c>
       <c r="E9" t="n">
-        <v>50.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>88.8</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>38.9</v>
+        <v>11.4</v>
       </c>
       <c r="H9" t="n">
-        <v>178.4</v>
+        <v>249.3</v>
       </c>
       <c r="I9" t="n">
-        <v>809.7</v>
+        <v>764</v>
       </c>
       <c r="J9" t="n">
-        <v>886</v>
+        <v>897</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>55.1</v>
+        <v>59.5</v>
       </c>
       <c r="E10" t="n">
-        <v>72.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="F10" t="n">
-        <v>81.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4</v>
+        <v>38.9</v>
       </c>
       <c r="H10" t="n">
-        <v>165.2</v>
+        <v>178.4</v>
       </c>
       <c r="I10" t="n">
-        <v>769.7</v>
+        <v>809.7</v>
       </c>
       <c r="J10" t="n">
-        <v>897</v>
+        <v>886</v>
       </c>
     </row>
     <row r="11">
@@ -858,19 +858,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>20.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E13" t="n">
         <v>6.1</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
       <c r="G13" t="n">
         <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>61.8</v>
+        <v>27.7</v>
       </c>
       <c r="I13" t="n">
         <v>587.7</v>
@@ -1199,7 +1199,9 @@
       <c r="E13" t="n">
         <v>897</v>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>747</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1485,7 +1487,9 @@
       <c r="E13" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1516,7 +1520,7 @@
         <v>5.7</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
   </sheetData>
@@ -1677,19 +1681,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>532</v>
+        <v>639.5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>107.5</v>
       </c>
       <c r="E6" t="n">
-        <v>532</v>
+        <v>639.5</v>
       </c>
       <c r="F6" t="n">
-        <v>532</v>
+        <v>747</v>
       </c>
       <c r="G6" t="n">
         <v>532</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>72.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>73.3</v>
+        <v>81.2</v>
       </c>
       <c r="F3" t="n">
         <v>87.3</v>
@@ -530,10 +530,10 @@
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>290.2</v>
+        <v>372.8</v>
       </c>
       <c r="I3" t="n">
-        <v>860.2</v>
+        <v>849.2</v>
       </c>
       <c r="J3" t="n">
         <v>879</v>
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>62.3</v>
+        <v>59.5</v>
       </c>
       <c r="E9" t="n">
-        <v>76.90000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="F9" t="n">
-        <v>84.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="G9" t="n">
-        <v>11.4</v>
+        <v>38.9</v>
       </c>
       <c r="H9" t="n">
-        <v>249.3</v>
+        <v>178.4</v>
       </c>
       <c r="I9" t="n">
-        <v>764</v>
+        <v>809.7</v>
       </c>
       <c r="J9" t="n">
-        <v>897</v>
+        <v>886</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>59.5</v>
+        <v>58.1</v>
       </c>
       <c r="E10" t="n">
-        <v>50.7</v>
+        <v>69.8</v>
       </c>
       <c r="F10" t="n">
-        <v>88.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>38.9</v>
+        <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>178.4</v>
+        <v>232.4</v>
       </c>
       <c r="I10" t="n">
-        <v>809.7</v>
+        <v>764</v>
       </c>
       <c r="J10" t="n">
-        <v>886</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11">
@@ -858,19 +858,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="E13" t="n">
         <v>6.1</v>
       </c>
       <c r="F13" t="n">
-        <v>15.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>5.7</v>
       </c>
       <c r="H13" t="n">
-        <v>27.7</v>
+        <v>20.1</v>
       </c>
       <c r="I13" t="n">
         <v>587.7</v>
@@ -1099,7 +1099,9 @@
       <c r="E7" t="n">
         <v>879</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>805</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1387,7 +1389,9 @@
       <c r="E7" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>82.59999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1488,7 +1492,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>84.09999999999999</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -1520,7 +1524,7 @@
         <v>5.7</v>
       </c>
       <c r="F15" t="n">
-        <v>15.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1681,19 +1685,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>639.5</v>
+        <v>694.7</v>
       </c>
       <c r="D6" t="n">
-        <v>107.5</v>
+        <v>117.4</v>
       </c>
       <c r="E6" t="n">
-        <v>639.5</v>
+        <v>747</v>
       </c>
       <c r="F6" t="n">
-        <v>747</v>
+        <v>805</v>
       </c>
       <c r="G6" t="n">
         <v>532</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,25 +481,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>81.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="E2" t="n">
-        <v>81.7</v>
+        <v>76.7</v>
       </c>
       <c r="F2" t="n">
         <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>67.40000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H2" t="n">
-        <v>324.5</v>
+        <v>386.3</v>
       </c>
       <c r="I2" t="n">
-        <v>884.5</v>
+        <v>853.8</v>
       </c>
       <c r="J2" t="n">
         <v>944</v>
@@ -518,7 +518,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>74.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E3" t="n">
         <v>81.2</v>
@@ -530,7 +530,7 @@
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>372.8</v>
+        <v>376.7</v>
       </c>
       <c r="I3" t="n">
         <v>849.2</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>71.2</v>
+        <v>66.8</v>
       </c>
       <c r="E4" t="n">
-        <v>73.59999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="F4" t="n">
         <v>91.3</v>
@@ -564,10 +564,10 @@
         <v>46.3</v>
       </c>
       <c r="H4" t="n">
-        <v>284.7</v>
+        <v>334.1</v>
       </c>
       <c r="I4" t="n">
-        <v>845.5</v>
+        <v>816.8</v>
       </c>
       <c r="J4" t="n">
         <v>967</v>
@@ -756,10 +756,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>58.1</v>
+        <v>58.4</v>
       </c>
       <c r="E10" t="n">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="F10" t="n">
         <v>81.40000000000001</v>
@@ -768,7 +768,7 @@
         <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>232.4</v>
+        <v>233.4</v>
       </c>
       <c r="I10" t="n">
         <v>764</v>
@@ -858,19 +858,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F13" t="n">
         <v>6.1</v>
       </c>
-      <c r="F13" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="G13" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>20.1</v>
+        <v>14.9</v>
       </c>
       <c r="I13" t="n">
         <v>587.7</v>
@@ -1011,7 +1011,9 @@
       <c r="E2" t="n">
         <v>967</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>702</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1031,7 +1033,9 @@
       <c r="E3" t="n">
         <v>884</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>731</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1301,7 +1305,9 @@
       <c r="E2" t="n">
         <v>91.3</v>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>49.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1321,7 +1327,9 @@
       <c r="E3" t="n">
         <v>67.40000000000001</v>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>61.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1390,7 +1398,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>82.59999999999999</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="8">
@@ -1492,7 +1500,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>67.2</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="14">
@@ -1524,7 +1532,7 @@
         <v>5.7</v>
       </c>
       <c r="F15" t="n">
-        <v>8.300000000000001</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -1685,16 +1693,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>694.7</v>
+        <v>703.4</v>
       </c>
       <c r="D6" t="n">
-        <v>117.4</v>
+        <v>92</v>
       </c>
       <c r="E6" t="n">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="F6" t="n">
         <v>805</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>77.3</v>
+        <v>74.7</v>
       </c>
       <c r="E2" t="n">
         <v>76.7</v>
@@ -493,10 +493,10 @@
         <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>61.8</v>
+        <v>49.1</v>
       </c>
       <c r="H2" t="n">
-        <v>386.3</v>
+        <v>373.6</v>
       </c>
       <c r="I2" t="n">
         <v>853.8</v>
@@ -518,10 +518,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>75.3</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>81.2</v>
+        <v>74.7</v>
       </c>
       <c r="F3" t="n">
         <v>87.3</v>
@@ -530,7 +530,7 @@
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>376.7</v>
+        <v>364.9</v>
       </c>
       <c r="I3" t="n">
         <v>849.2</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>66.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>60.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>91.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>46.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>334.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>816.8</v>
+        <v>894</v>
       </c>
       <c r="J4" t="n">
-        <v>967</v>
+        <v>894</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="E5" t="n">
-        <v>65.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="F5" t="n">
-        <v>65.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>65.59999999999999</v>
+        <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>65.59999999999999</v>
+        <v>129.4</v>
       </c>
       <c r="I5" t="n">
-        <v>894</v>
+        <v>833.5</v>
       </c>
       <c r="J5" t="n">
-        <v>894</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6">
@@ -613,11 +613,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>64.7</v>
@@ -626,19 +626,19 @@
         <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>64.7</v>
       </c>
       <c r="H6" t="n">
-        <v>129.4</v>
+        <v>64.7</v>
       </c>
       <c r="I6" t="n">
-        <v>833.5</v>
+        <v>788</v>
       </c>
       <c r="J6" t="n">
-        <v>926</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>64.7</v>
+        <v>60.1</v>
       </c>
       <c r="F7" t="n">
-        <v>64.7</v>
+        <v>91.3</v>
       </c>
       <c r="G7" t="n">
-        <v>64.7</v>
+        <v>38.5</v>
       </c>
       <c r="H7" t="n">
-        <v>64.7</v>
+        <v>323.2</v>
       </c>
       <c r="I7" t="n">
-        <v>788</v>
+        <v>816.8</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>58.4</v>
+        <v>56.4</v>
       </c>
       <c r="E10" t="n">
-        <v>70.3</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>81.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>233.4</v>
+        <v>225.5</v>
       </c>
       <c r="I10" t="n">
-        <v>764</v>
+        <v>805.2</v>
       </c>
       <c r="J10" t="n">
-        <v>897</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>44.5</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
-        <v>56.2</v>
+        <v>63.7</v>
       </c>
       <c r="F11" t="n">
-        <v>61.9</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="H11" t="n">
-        <v>133.6</v>
+        <v>220.2</v>
       </c>
       <c r="I11" t="n">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="J11" t="n">
-        <v>887</v>
+        <v>897</v>
       </c>
     </row>
     <row r="12">
@@ -1083,7 +1083,9 @@
       <c r="E6" t="n">
         <v>857</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>884</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1306,7 +1308,7 @@
         <v>91.3</v>
       </c>
       <c r="F2" t="n">
-        <v>49.4</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="3">
@@ -1328,7 +1330,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>61.8</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="4">
@@ -1377,7 +1379,9 @@
       <c r="E6" t="n">
         <v>56.2</v>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>91.90000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1398,7 +1402,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>86.5</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="8">
@@ -1500,7 +1504,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>68.2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1693,19 +1697,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>703.4</v>
+        <v>733.5</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>107.7</v>
       </c>
       <c r="E6" t="n">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="F6" t="n">
-        <v>805</v>
+        <v>884</v>
       </c>
       <c r="G6" t="n">
         <v>532</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>74.7</v>
+        <v>74.5</v>
       </c>
       <c r="E2" t="n">
         <v>76.7</v>
@@ -493,10 +493,10 @@
         <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>49.1</v>
+        <v>47.8</v>
       </c>
       <c r="H2" t="n">
-        <v>373.6</v>
+        <v>372.3</v>
       </c>
       <c r="I2" t="n">
         <v>853.8</v>
@@ -518,10 +518,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>74.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>87.3</v>
@@ -530,7 +530,7 @@
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>364.9</v>
+        <v>365.6</v>
       </c>
       <c r="I3" t="n">
         <v>849.2</v>
@@ -654,7 +654,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>64.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="E7" t="n">
         <v>60.1</v>
@@ -663,10 +663,10 @@
         <v>91.3</v>
       </c>
       <c r="G7" t="n">
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
       <c r="H7" t="n">
-        <v>323.2</v>
+        <v>321.2</v>
       </c>
       <c r="I7" t="n">
         <v>816.8</v>
@@ -756,19 +756,19 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="E10" t="n">
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>91.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="G10" t="n">
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>225.5</v>
+        <v>226.6</v>
       </c>
       <c r="I10" t="n">
         <v>805.2</v>
@@ -790,10 +790,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="E11" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="F11" t="n">
         <v>81.40000000000001</v>
@@ -802,7 +802,7 @@
         <v>11.4</v>
       </c>
       <c r="H11" t="n">
-        <v>220.2</v>
+        <v>219.4</v>
       </c>
       <c r="I11" t="n">
         <v>764</v>
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>26.3</v>
+        <v>32.4</v>
       </c>
       <c r="E12" t="n">
-        <v>28.2</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>40.2</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>105.1</v>
+        <v>162.1</v>
       </c>
       <c r="I12" t="n">
-        <v>723.2</v>
+        <v>729.4</v>
       </c>
       <c r="J12" t="n">
         <v>835</v>
@@ -858,7 +858,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="E13" t="n">
         <v>5.7</v>
@@ -867,10 +867,10 @@
         <v>6.1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>14.9</v>
+        <v>13.8</v>
       </c>
       <c r="I13" t="n">
         <v>587.7</v>
@@ -1159,7 +1159,9 @@
       <c r="E10" t="n">
         <v>717</v>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>754</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1308,7 +1310,7 @@
         <v>91.3</v>
       </c>
       <c r="F2" t="n">
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="3">
@@ -1330,7 +1332,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>49.1</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="4">
@@ -1380,7 +1382,7 @@
         <v>56.2</v>
       </c>
       <c r="F6" t="n">
-        <v>91.90000000000001</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1402,7 +1404,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>74.7</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1455,7 +1457,9 @@
       <c r="E10" t="n">
         <v>8.4</v>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1504,7 +1508,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="14">
@@ -1536,7 +1540,7 @@
         <v>5.7</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1697,16 +1701,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>733.5</v>
+        <v>736.4</v>
       </c>
       <c r="D6" t="n">
-        <v>107.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="F6" t="n">
         <v>884</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>74.5</v>
+        <v>73</v>
       </c>
       <c r="E2" t="n">
         <v>76.7</v>
@@ -493,10 +493,10 @@
         <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>47.8</v>
+        <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>372.3</v>
+        <v>365</v>
       </c>
       <c r="I2" t="n">
         <v>853.8</v>
@@ -518,10 +518,10 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>73.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="E3" t="n">
-        <v>75.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>87.3</v>
@@ -530,7 +530,7 @@
         <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>365.6</v>
+        <v>357.3</v>
       </c>
       <c r="I3" t="n">
         <v>849.2</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>65.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="E4" t="n">
-        <v>65.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="F4" t="n">
-        <v>65.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>65.59999999999999</v>
+        <v>38.9</v>
       </c>
       <c r="H4" t="n">
-        <v>65.59999999999999</v>
+        <v>269.3</v>
       </c>
       <c r="I4" t="n">
-        <v>894</v>
+        <v>832.8</v>
       </c>
       <c r="J4" t="n">
-        <v>894</v>
+        <v>902</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>80.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>129.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>833.5</v>
+        <v>894</v>
       </c>
       <c r="J5" t="n">
-        <v>926</v>
+        <v>894</v>
       </c>
     </row>
     <row r="6">
@@ -613,11 +613,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>64.7</v>
@@ -626,19 +626,19 @@
         <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>64.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>64.7</v>
+        <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>64.7</v>
+        <v>129.4</v>
       </c>
       <c r="I6" t="n">
-        <v>788</v>
+        <v>833.5</v>
       </c>
       <c r="J6" t="n">
-        <v>788</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>64.2</v>
+        <v>64.7</v>
       </c>
       <c r="E7" t="n">
-        <v>60.1</v>
+        <v>64.7</v>
       </c>
       <c r="F7" t="n">
-        <v>91.3</v>
+        <v>64.7</v>
       </c>
       <c r="G7" t="n">
-        <v>36.5</v>
+        <v>64.7</v>
       </c>
       <c r="H7" t="n">
-        <v>321.2</v>
+        <v>64.7</v>
       </c>
       <c r="I7" t="n">
-        <v>816.8</v>
+        <v>788</v>
       </c>
       <c r="J7" t="n">
-        <v>967</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
-        <v>62.8</v>
+        <v>60.1</v>
       </c>
       <c r="F8" t="n">
-        <v>62.8</v>
+        <v>91.3</v>
       </c>
       <c r="G8" t="n">
-        <v>62.8</v>
+        <v>30.5</v>
       </c>
       <c r="H8" t="n">
-        <v>62.8</v>
+        <v>315.2</v>
       </c>
       <c r="I8" t="n">
-        <v>782</v>
+        <v>816.8</v>
       </c>
       <c r="J8" t="n">
-        <v>782</v>
+        <v>967</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>59.5</v>
+        <v>62.8</v>
       </c>
       <c r="E9" t="n">
-        <v>50.7</v>
+        <v>62.8</v>
       </c>
       <c r="F9" t="n">
-        <v>88.8</v>
+        <v>62.8</v>
       </c>
       <c r="G9" t="n">
-        <v>38.9</v>
+        <v>62.8</v>
       </c>
       <c r="H9" t="n">
-        <v>178.4</v>
+        <v>62.8</v>
       </c>
       <c r="I9" t="n">
-        <v>809.7</v>
+        <v>782</v>
       </c>
       <c r="J9" t="n">
-        <v>886</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10">
@@ -756,19 +756,19 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>56.6</v>
+        <v>55.4</v>
       </c>
       <c r="E10" t="n">
         <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>93</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>226.6</v>
+        <v>221.5</v>
       </c>
       <c r="I10" t="n">
         <v>805.2</v>
@@ -790,10 +790,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>54.9</v>
+        <v>52.9</v>
       </c>
       <c r="E11" t="n">
-        <v>63.3</v>
+        <v>59.4</v>
       </c>
       <c r="F11" t="n">
         <v>81.40000000000001</v>
@@ -802,7 +802,7 @@
         <v>11.4</v>
       </c>
       <c r="H11" t="n">
-        <v>219.4</v>
+        <v>211.5</v>
       </c>
       <c r="I11" t="n">
         <v>764</v>
@@ -824,19 +824,19 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>32.4</v>
+        <v>30.8</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>48.8</v>
       </c>
       <c r="G12" t="n">
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>162.1</v>
+        <v>153.9</v>
       </c>
       <c r="I12" t="n">
         <v>729.4</v>
@@ -867,10 +867,10 @@
         <v>6.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="I13" t="n">
         <v>587.7</v>
@@ -1125,7 +1125,9 @@
         <v>676</v>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>902</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1310,7 +1312,7 @@
         <v>91.3</v>
       </c>
       <c r="F2" t="n">
-        <v>36.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="3">
@@ -1332,7 +1334,7 @@
         <v>67.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>47.8</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="4">
@@ -1382,7 +1384,7 @@
         <v>56.2</v>
       </c>
       <c r="F6" t="n">
-        <v>93</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1404,7 +1406,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>75.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1423,7 +1425,9 @@
         <v>38.9</v>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>90.90000000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1458,7 +1462,7 @@
         <v>8.4</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="11">
@@ -1508,7 +1512,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>54.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="14">
@@ -1540,7 +1544,7 @@
         <v>5.7</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -1701,19 +1705,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>736.4</v>
+        <v>757.1</v>
       </c>
       <c r="D6" t="n">
-        <v>99.90000000000001</v>
+        <v>108.3</v>
       </c>
       <c r="E6" t="n">
-        <v>747</v>
+        <v>750.5</v>
       </c>
       <c r="F6" t="n">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="G6" t="n">
         <v>532</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -613,11 +613,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>64.7</v>
@@ -626,19 +626,19 @@
         <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>64.7</v>
       </c>
       <c r="H6" t="n">
-        <v>129.4</v>
+        <v>64.7</v>
       </c>
       <c r="I6" t="n">
-        <v>833.5</v>
+        <v>788</v>
       </c>
       <c r="J6" t="n">
-        <v>926</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>64.7</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>64.7</v>
+        <v>60.1</v>
       </c>
       <c r="F7" t="n">
-        <v>64.7</v>
+        <v>91.3</v>
       </c>
       <c r="G7" t="n">
-        <v>64.7</v>
+        <v>30.5</v>
       </c>
       <c r="H7" t="n">
-        <v>64.7</v>
+        <v>315.2</v>
       </c>
       <c r="I7" t="n">
-        <v>788</v>
+        <v>816.8</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>62.8</v>
       </c>
       <c r="E8" t="n">
-        <v>60.1</v>
+        <v>62.8</v>
       </c>
       <c r="F8" t="n">
-        <v>91.3</v>
+        <v>62.8</v>
       </c>
       <c r="G8" t="n">
-        <v>30.5</v>
+        <v>62.8</v>
       </c>
       <c r="H8" t="n">
-        <v>315.2</v>
+        <v>62.8</v>
       </c>
       <c r="I8" t="n">
-        <v>816.8</v>
+        <v>782</v>
       </c>
       <c r="J8" t="n">
-        <v>967</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>62.8</v>
+        <v>59.8</v>
       </c>
       <c r="E9" t="n">
-        <v>62.8</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>62.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>62.8</v>
+        <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>62.8</v>
+        <v>179.4</v>
       </c>
       <c r="I9" t="n">
-        <v>782</v>
+        <v>817.7</v>
       </c>
       <c r="J9" t="n">
-        <v>782</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10">
@@ -958,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,6 +992,11 @@
           <t>9/6/26</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>9/7/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1014,6 +1019,7 @@
       <c r="F2" t="n">
         <v>702</v>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1036,6 +1042,7 @@
       <c r="F3" t="n">
         <v>731</v>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1052,6 +1059,9 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>786</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1066,6 +1076,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1086,6 +1097,7 @@
       <c r="F6" t="n">
         <v>884</v>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1108,6 +1120,7 @@
       <c r="F7" t="n">
         <v>805</v>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1128,6 +1141,7 @@
       <c r="F8" t="n">
         <v>902</v>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1142,6 +1156,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1164,6 +1179,7 @@
       <c r="F10" t="n">
         <v>754</v>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1180,6 +1196,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1194,6 +1211,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1214,6 +1232,7 @@
       <c r="F13" t="n">
         <v>747</v>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1228,6 +1247,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1246,6 +1266,7 @@
       <c r="F15" t="n">
         <v>532</v>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1258,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1292,6 +1313,11 @@
           <t>9/6/26</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>9/7/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1314,6 +1340,7 @@
       <c r="F2" t="n">
         <v>30.5</v>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1336,6 +1363,7 @@
       <c r="F3" t="n">
         <v>40.5</v>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1352,6 +1380,9 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1366,6 +1397,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1386,6 +1418,7 @@
       <c r="F6" t="n">
         <v>87.90000000000001</v>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1408,6 +1441,7 @@
       <c r="F7" t="n">
         <v>67.09999999999999</v>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1428,6 +1462,7 @@
       <c r="F8" t="n">
         <v>90.90000000000001</v>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1442,6 +1477,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1464,6 +1500,7 @@
       <c r="F10" t="n">
         <v>48.8</v>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1480,6 +1517,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1494,6 +1532,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1514,6 +1553,7 @@
       <c r="F13" t="n">
         <v>46.3</v>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1528,6 +1568,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1546,6 +1587,7 @@
       <c r="F15" t="n">
         <v>1.9</v>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1558,7 +1600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1723,6 +1765,31 @@
         <v>532</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>9/7/26</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>786</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>786</v>
+      </c>
+      <c r="F7" t="n">
+        <v>786</v>
+      </c>
+      <c r="G7" t="n">
+        <v>786</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -477,32 +477,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pparril</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>76.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>93.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>40.5</v>
+        <v>62.8</v>
       </c>
       <c r="H2" t="n">
-        <v>365</v>
+        <v>146.9</v>
       </c>
       <c r="I2" t="n">
-        <v>853.8</v>
+        <v>786</v>
       </c>
       <c r="J2" t="n">
-        <v>944</v>
+        <v>790</v>
       </c>
     </row>
     <row r="3">
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>67.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F3" t="n">
-        <v>87.3</v>
+        <v>93.7</v>
       </c>
       <c r="G3" t="n">
-        <v>56.3</v>
+        <v>40.5</v>
       </c>
       <c r="H3" t="n">
-        <v>357.3</v>
+        <v>365</v>
       </c>
       <c r="I3" t="n">
-        <v>849.2</v>
+        <v>853.8</v>
       </c>
       <c r="J3" t="n">
-        <v>879</v>
+        <v>944</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>67.3</v>
+        <v>71.5</v>
       </c>
       <c r="E4" t="n">
-        <v>69.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>90.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9</v>
+        <v>56.3</v>
       </c>
       <c r="H4" t="n">
-        <v>269.3</v>
+        <v>357.3</v>
       </c>
       <c r="I4" t="n">
-        <v>832.8</v>
+        <v>849.2</v>
       </c>
       <c r="J4" t="n">
-        <v>902</v>
+        <v>879</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>65.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="E5" t="n">
-        <v>65.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="F5" t="n">
-        <v>65.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>65.59999999999999</v>
+        <v>38.9</v>
       </c>
       <c r="H5" t="n">
-        <v>65.59999999999999</v>
+        <v>269.3</v>
       </c>
       <c r="I5" t="n">
-        <v>894</v>
+        <v>832.8</v>
       </c>
       <c r="J5" t="n">
-        <v>894</v>
+        <v>902</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>788</v>
+        <v>894</v>
       </c>
       <c r="J6" t="n">
-        <v>788</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>64.7</v>
       </c>
       <c r="E7" t="n">
-        <v>60.1</v>
+        <v>64.7</v>
       </c>
       <c r="F7" t="n">
-        <v>91.3</v>
+        <v>64.7</v>
       </c>
       <c r="G7" t="n">
-        <v>30.5</v>
+        <v>64.7</v>
       </c>
       <c r="H7" t="n">
-        <v>315.2</v>
+        <v>64.7</v>
       </c>
       <c r="I7" t="n">
-        <v>816.8</v>
+        <v>788</v>
       </c>
       <c r="J7" t="n">
-        <v>967</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
-        <v>62.8</v>
+        <v>60.1</v>
       </c>
       <c r="F8" t="n">
-        <v>62.8</v>
+        <v>91.3</v>
       </c>
       <c r="G8" t="n">
-        <v>62.8</v>
+        <v>30.5</v>
       </c>
       <c r="H8" t="n">
-        <v>62.8</v>
+        <v>315.2</v>
       </c>
       <c r="I8" t="n">
-        <v>782</v>
+        <v>816.8</v>
       </c>
       <c r="J8" t="n">
-        <v>782</v>
+        <v>967</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>59.8</v>
+        <v>55.4</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>80.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>179.4</v>
+        <v>221.5</v>
       </c>
       <c r="I9" t="n">
-        <v>817.7</v>
+        <v>805.2</v>
       </c>
       <c r="J9" t="n">
-        <v>926</v>
+        <v>887</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>55.4</v>
+        <v>52.9</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="F10" t="n">
-        <v>87.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>221.5</v>
+        <v>211.5</v>
       </c>
       <c r="I10" t="n">
-        <v>805.2</v>
+        <v>764</v>
       </c>
       <c r="J10" t="n">
-        <v>887</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>52.9</v>
+        <v>48.4</v>
       </c>
       <c r="E11" t="n">
-        <v>59.4</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>81.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
       <c r="H11" t="n">
-        <v>211.5</v>
+        <v>145.3</v>
       </c>
       <c r="I11" t="n">
-        <v>764</v>
+        <v>817.7</v>
       </c>
       <c r="J11" t="n">
-        <v>897</v>
+        <v>926</v>
       </c>
     </row>
     <row r="12">
@@ -1211,7 +1211,9 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>790</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1381,7 +1383,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="5">
@@ -1532,7 +1534,9 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1772,19 +1776,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="F7" t="n">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="G7" t="n">
         <v>786</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -477,32 +477,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>pparril</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>73.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E2" t="n">
-        <v>73.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="F2" t="n">
-        <v>84.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="G2" t="n">
-        <v>62.8</v>
+        <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>146.9</v>
+        <v>365</v>
       </c>
       <c r="I2" t="n">
-        <v>786</v>
+        <v>853.8</v>
       </c>
       <c r="J2" t="n">
-        <v>790</v>
+        <v>944</v>
       </c>
     </row>
     <row r="3">
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pparril</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>71.5</v>
       </c>
       <c r="E3" t="n">
-        <v>76.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>93.7</v>
+        <v>87.3</v>
       </c>
       <c r="G3" t="n">
-        <v>40.5</v>
+        <v>56.3</v>
       </c>
       <c r="H3" t="n">
-        <v>365</v>
+        <v>357.3</v>
       </c>
       <c r="I3" t="n">
-        <v>853.8</v>
+        <v>849.2</v>
       </c>
       <c r="J3" t="n">
-        <v>944</v>
+        <v>879</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>71.5</v>
+        <v>68</v>
       </c>
       <c r="E4" t="n">
-        <v>67.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>87.3</v>
+        <v>93</v>
       </c>
       <c r="G4" t="n">
-        <v>56.3</v>
+        <v>30.5</v>
       </c>
       <c r="H4" t="n">
-        <v>357.3</v>
+        <v>408.2</v>
       </c>
       <c r="I4" t="n">
-        <v>849.2</v>
+        <v>835.2</v>
       </c>
       <c r="J4" t="n">
-        <v>879</v>
+        <v>967</v>
       </c>
     </row>
     <row r="5">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>58.7</v>
       </c>
       <c r="E8" t="n">
-        <v>60.1</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>91.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>30.5</v>
+        <v>46.7</v>
       </c>
       <c r="H8" t="n">
-        <v>315.2</v>
+        <v>176.1</v>
       </c>
       <c r="I8" t="n">
-        <v>816.8</v>
+        <v>817.7</v>
       </c>
       <c r="J8" t="n">
-        <v>967</v>
+        <v>926</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>55.4</v>
+        <v>55.6</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>55.6</v>
       </c>
       <c r="F9" t="n">
-        <v>87.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="G9" t="n">
-        <v>15.5</v>
+        <v>48.5</v>
       </c>
       <c r="H9" t="n">
-        <v>221.5</v>
+        <v>111.3</v>
       </c>
       <c r="I9" t="n">
-        <v>805.2</v>
+        <v>786</v>
       </c>
       <c r="J9" t="n">
-        <v>887</v>
+        <v>790</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>52.9</v>
+        <v>55.4</v>
       </c>
       <c r="E10" t="n">
-        <v>59.4</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>81.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>211.5</v>
+        <v>221.5</v>
       </c>
       <c r="I10" t="n">
-        <v>764</v>
+        <v>805.2</v>
       </c>
       <c r="J10" t="n">
-        <v>897</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>48.4</v>
+        <v>52.9</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>59.4</v>
       </c>
       <c r="F11" t="n">
-        <v>80.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>15.9</v>
+        <v>11.4</v>
       </c>
       <c r="H11" t="n">
-        <v>145.3</v>
+        <v>211.5</v>
       </c>
       <c r="I11" t="n">
-        <v>817.7</v>
+        <v>764</v>
       </c>
       <c r="J11" t="n">
-        <v>926</v>
+        <v>897</v>
       </c>
     </row>
     <row r="12">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>30.8</v>
+        <v>27.1</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>28.2</v>
       </c>
       <c r="F12" t="n">
         <v>48.8</v>
@@ -836,10 +836,10 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>153.9</v>
+        <v>162.7</v>
       </c>
       <c r="I12" t="n">
-        <v>729.4</v>
+        <v>719.7</v>
       </c>
       <c r="J12" t="n">
         <v>835</v>
@@ -1019,7 +1019,9 @@
       <c r="F2" t="n">
         <v>702</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>927</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1179,7 +1181,9 @@
       <c r="F10" t="n">
         <v>754</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>671</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1342,7 +1346,9 @@
       <c r="F2" t="n">
         <v>30.5</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1383,7 +1389,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>15.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="5">
@@ -1502,7 +1508,9 @@
       <c r="F10" t="n">
         <v>48.8</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>8.800000000000001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1535,7 +1543,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>84.09999999999999</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="13">
@@ -1776,22 +1784,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>788</v>
+        <v>793.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>90.7</v>
       </c>
       <c r="E7" t="n">
         <v>788</v>
       </c>
       <c r="F7" t="n">
-        <v>790</v>
+        <v>927</v>
       </c>
       <c r="G7" t="n">
-        <v>786</v>
+        <v>671</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -552,19 +552,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>68</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E4" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>95.5</v>
       </c>
       <c r="G4" t="n">
         <v>30.5</v>
       </c>
       <c r="H4" t="n">
-        <v>408.2</v>
+        <v>410.7</v>
       </c>
       <c r="I4" t="n">
         <v>835.2</v>
@@ -688,19 +688,19 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>58.7</v>
+        <v>61.6</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>55.5</v>
       </c>
       <c r="F8" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>46.7</v>
+        <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>176.1</v>
+        <v>184.9</v>
       </c>
       <c r="I8" t="n">
         <v>817.7</v>
@@ -722,19 +722,19 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
         <v>62.8</v>
       </c>
       <c r="G9" t="n">
-        <v>48.5</v>
+        <v>57.3</v>
       </c>
       <c r="H9" t="n">
-        <v>111.3</v>
+        <v>120.1</v>
       </c>
       <c r="I9" t="n">
         <v>786</v>
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>55.4</v>
+        <v>52.9</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>59.4</v>
       </c>
       <c r="F10" t="n">
-        <v>87.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>15.5</v>
+        <v>11.4</v>
       </c>
       <c r="H10" t="n">
-        <v>221.5</v>
+        <v>211.5</v>
       </c>
       <c r="I10" t="n">
-        <v>805.2</v>
+        <v>764</v>
       </c>
       <c r="J10" t="n">
-        <v>887</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>52.9</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>59.4</v>
+        <v>56.2</v>
       </c>
       <c r="F11" t="n">
-        <v>81.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="H11" t="n">
-        <v>211.5</v>
+        <v>240.2</v>
       </c>
       <c r="I11" t="n">
-        <v>764</v>
+        <v>782.8</v>
       </c>
       <c r="J11" t="n">
-        <v>897</v>
+        <v>887</v>
       </c>
     </row>
     <row r="12">
@@ -824,7 +824,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -836,7 +836,7 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>162.7</v>
+        <v>166.8</v>
       </c>
       <c r="I12" t="n">
         <v>719.7</v>
@@ -1099,7 +1099,9 @@
       <c r="F6" t="n">
         <v>884</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>693</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1347,7 +1349,7 @@
         <v>30.5</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="3">
@@ -1389,7 +1391,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>46.7</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="5">
@@ -1426,7 +1428,9 @@
       <c r="F6" t="n">
         <v>87.90000000000001</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>18.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1509,7 +1513,7 @@
         <v>48.8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.800000000000001</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="11">
@@ -1543,7 +1547,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>48.5</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="13">
@@ -1784,16 +1788,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>793.5</v>
+        <v>773.4</v>
       </c>
       <c r="D7" t="n">
-        <v>90.7</v>
+        <v>90.5</v>
       </c>
       <c r="E7" t="n">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="F7" t="n">
         <v>927</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>76.7</v>
+        <v>81.7</v>
       </c>
       <c r="F2" t="n">
         <v>93.7</v>
@@ -496,10 +496,10 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>365</v>
+        <v>455.4</v>
       </c>
       <c r="I2" t="n">
-        <v>853.8</v>
+        <v>864.3</v>
       </c>
       <c r="J2" t="n">
         <v>944</v>
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>71.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>67.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>87.3</v>
+        <v>92</v>
       </c>
       <c r="G3" t="n">
-        <v>56.3</v>
+        <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>357.3</v>
+        <v>407.2</v>
       </c>
       <c r="I3" t="n">
-        <v>849.2</v>
+        <v>835.2</v>
       </c>
       <c r="J3" t="n">
-        <v>879</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>68.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="E4" t="n">
-        <v>73.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="F4" t="n">
-        <v>95.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>30.5</v>
+        <v>38.9</v>
       </c>
       <c r="H4" t="n">
-        <v>410.7</v>
+        <v>269.3</v>
       </c>
       <c r="I4" t="n">
-        <v>835.2</v>
+        <v>832.8</v>
       </c>
       <c r="J4" t="n">
-        <v>967</v>
+        <v>902</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>67.3</v>
+        <v>66.2</v>
       </c>
       <c r="E5" t="n">
-        <v>69.8</v>
+        <v>66.2</v>
       </c>
       <c r="F5" t="n">
-        <v>90.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="G5" t="n">
-        <v>38.9</v>
+        <v>39.9</v>
       </c>
       <c r="H5" t="n">
-        <v>269.3</v>
+        <v>397.2</v>
       </c>
       <c r="I5" t="n">
-        <v>832.8</v>
+        <v>834.7</v>
       </c>
       <c r="J5" t="n">
-        <v>902</v>
+        <v>879</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>65.59999999999999</v>
+        <v>60.2</v>
       </c>
       <c r="E6" t="n">
-        <v>65.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>65.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="G6" t="n">
-        <v>65.59999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="H6" t="n">
-        <v>65.59999999999999</v>
+        <v>301.2</v>
       </c>
       <c r="I6" t="n">
-        <v>894</v>
+        <v>793.8</v>
       </c>
       <c r="J6" t="n">
-        <v>894</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>64.7</v>
+        <v>59.6</v>
       </c>
       <c r="E7" t="n">
-        <v>64.7</v>
+        <v>49.4</v>
       </c>
       <c r="F7" t="n">
-        <v>64.7</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>64.7</v>
+        <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>64.7</v>
+        <v>178.8</v>
       </c>
       <c r="I7" t="n">
-        <v>788</v>
+        <v>817.7</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>61.6</v>
+        <v>56.9</v>
       </c>
       <c r="E8" t="n">
-        <v>55.5</v>
+        <v>56.9</v>
       </c>
       <c r="F8" t="n">
-        <v>80.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H8" t="n">
-        <v>184.9</v>
+        <v>113.8</v>
       </c>
       <c r="I8" t="n">
-        <v>817.7</v>
+        <v>786</v>
       </c>
       <c r="J8" t="n">
-        <v>926</v>
+        <v>790</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="G9" t="n">
-        <v>57.3</v>
+        <v>47.4</v>
       </c>
       <c r="H9" t="n">
-        <v>120.1</v>
+        <v>112.1</v>
       </c>
       <c r="I9" t="n">
-        <v>786</v>
+        <v>784.5</v>
       </c>
       <c r="J9" t="n">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>52.9</v>
+        <v>47.7</v>
       </c>
       <c r="E10" t="n">
-        <v>59.4</v>
+        <v>56.2</v>
       </c>
       <c r="F10" t="n">
-        <v>81.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4</v>
+        <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>211.5</v>
+        <v>238.6</v>
       </c>
       <c r="I10" t="n">
-        <v>764</v>
+        <v>782.8</v>
       </c>
       <c r="J10" t="n">
-        <v>897</v>
+        <v>887</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>35.8</v>
       </c>
       <c r="E11" t="n">
-        <v>56.2</v>
+        <v>35.8</v>
       </c>
       <c r="F11" t="n">
-        <v>87.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>15.5</v>
+        <v>6.1</v>
       </c>
       <c r="H11" t="n">
-        <v>240.2</v>
+        <v>71.7</v>
       </c>
       <c r="I11" t="n">
-        <v>782.8</v>
+        <v>764</v>
       </c>
       <c r="J11" t="n">
-        <v>887</v>
+        <v>894</v>
       </c>
     </row>
     <row r="12">
@@ -824,7 +824,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -836,7 +836,7 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>166.8</v>
+        <v>166</v>
       </c>
       <c r="I12" t="n">
         <v>719.7</v>
@@ -1044,7 +1044,9 @@
       <c r="F3" t="n">
         <v>731</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>917</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1078,7 +1080,9 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>634</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1124,7 +1128,9 @@
       <c r="F7" t="n">
         <v>805</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>762</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1240,7 +1246,9 @@
       <c r="F13" t="n">
         <v>747</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>913</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1255,7 +1263,9 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>781</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1349,7 +1359,7 @@
         <v>30.5</v>
       </c>
       <c r="G2" t="n">
-        <v>95.5</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3">
@@ -1373,7 +1383,9 @@
       <c r="F3" t="n">
         <v>40.5</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>90.40000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1391,7 +1403,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>55.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="5">
@@ -1407,7 +1419,9 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1429,7 +1443,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="7">
@@ -1453,7 +1467,9 @@
       <c r="F7" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>39.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1513,7 +1529,7 @@
         <v>48.8</v>
       </c>
       <c r="G10" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="11">
@@ -1547,7 +1563,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>57.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -1569,7 +1585,9 @@
       <c r="F13" t="n">
         <v>46.3</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>89.7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1584,7 +1602,9 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>47.4</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1788,22 +1808,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>773.4</v>
+        <v>787.4</v>
       </c>
       <c r="D7" t="n">
-        <v>90.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>786</v>
+        <v>783.5</v>
       </c>
       <c r="F7" t="n">
         <v>927</v>
       </c>
       <c r="G7" t="n">
-        <v>671</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>81.7</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>455.4</v>
+        <v>456.8</v>
       </c>
       <c r="I2" t="n">
         <v>864.3</v>
@@ -518,19 +518,19 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>67.90000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>92</v>
+        <v>93.3</v>
       </c>
       <c r="G3" t="n">
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>407.2</v>
+        <v>408.5</v>
       </c>
       <c r="I3" t="n">
         <v>835.2</v>
@@ -586,7 +586,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -595,10 +595,10 @@
         <v>87.3</v>
       </c>
       <c r="G5" t="n">
-        <v>39.9</v>
+        <v>40.7</v>
       </c>
       <c r="H5" t="n">
-        <v>397.2</v>
+        <v>398</v>
       </c>
       <c r="I5" t="n">
         <v>834.7</v>
@@ -620,19 +620,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>60.2</v>
+        <v>60.5</v>
       </c>
       <c r="E6" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>89.7</v>
+        <v>91.2</v>
       </c>
       <c r="G6" t="n">
         <v>11.4</v>
       </c>
       <c r="H6" t="n">
-        <v>301.2</v>
+        <v>302.7</v>
       </c>
       <c r="I6" t="n">
         <v>793.8</v>
@@ -654,10 +654,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>59.6</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>49.4</v>
+        <v>50.7</v>
       </c>
       <c r="F7" t="n">
         <v>80.40000000000001</v>
@@ -666,7 +666,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>178.8</v>
+        <v>180.1</v>
       </c>
       <c r="I7" t="n">
         <v>817.7</v>
@@ -688,19 +688,19 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>56.9</v>
+        <v>57.6</v>
       </c>
       <c r="E8" t="n">
-        <v>56.9</v>
+        <v>57.6</v>
       </c>
       <c r="F8" t="n">
         <v>62.8</v>
       </c>
       <c r="G8" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
       <c r="H8" t="n">
-        <v>113.8</v>
+        <v>115.2</v>
       </c>
       <c r="I8" t="n">
         <v>786</v>
@@ -722,19 +722,19 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>56.6</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>56.6</v>
       </c>
       <c r="F9" t="n">
         <v>64.7</v>
       </c>
       <c r="G9" t="n">
-        <v>47.4</v>
+        <v>48.6</v>
       </c>
       <c r="H9" t="n">
-        <v>112.1</v>
+        <v>113.3</v>
       </c>
       <c r="I9" t="n">
         <v>784.5</v>
@@ -768,7 +768,7 @@
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>238.6</v>
+        <v>238.4</v>
       </c>
       <c r="I10" t="n">
         <v>782.8</v>
@@ -790,19 +790,19 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="E11" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="F11" t="n">
         <v>65.59999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>71.7</v>
+        <v>71.3</v>
       </c>
       <c r="I11" t="n">
         <v>764</v>
@@ -824,7 +824,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>27.7</v>
+        <v>27.6</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -836,7 +836,7 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>166</v>
+        <v>165.6</v>
       </c>
       <c r="I12" t="n">
         <v>719.7</v>
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1</v>
+        <v>37.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>13.7</v>
+        <v>42.1</v>
       </c>
       <c r="I13" t="n">
-        <v>587.7</v>
+        <v>658.7</v>
       </c>
       <c r="J13" t="n">
-        <v>698</v>
+        <v>754</v>
       </c>
     </row>
     <row r="14">
@@ -885,32 +885,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>13.7</v>
       </c>
       <c r="I14" t="n">
-        <v>746</v>
+        <v>587.7</v>
       </c>
       <c r="J14" t="n">
-        <v>746</v>
+        <v>698</v>
       </c>
     </row>
     <row r="15">
@@ -919,32 +919,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>johnson7</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>611</v>
+        <v>746</v>
       </c>
       <c r="J15" t="n">
-        <v>737</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +1208,9 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>754</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1359,7 +1361,7 @@
         <v>30.5</v>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="3">
@@ -1384,7 +1386,7 @@
         <v>40.5</v>
       </c>
       <c r="G3" t="n">
-        <v>90.40000000000001</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="4">
@@ -1403,7 +1405,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>49.4</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="5">
@@ -1420,7 +1422,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6">
@@ -1443,7 +1445,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="7">
@@ -1468,7 +1470,7 @@
         <v>67.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>39.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="8">
@@ -1529,7 +1531,7 @@
         <v>48.8</v>
       </c>
       <c r="G10" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="11">
@@ -1547,7 +1549,9 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1563,7 +1567,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="13">
@@ -1586,7 +1590,7 @@
         <v>46.3</v>
       </c>
       <c r="G13" t="n">
-        <v>89.7</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="14">
@@ -1603,7 +1607,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>47.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="15">
@@ -1808,16 +1812,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>787.4</v>
+        <v>784.4</v>
       </c>
       <c r="D7" t="n">
-        <v>99.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="E7" t="n">
-        <v>783.5</v>
+        <v>781</v>
       </c>
       <c r="F7" t="n">
         <v>927</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>76.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>81.7</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>456.8</v>
+        <v>458.1</v>
       </c>
       <c r="I2" t="n">
         <v>864.3</v>
@@ -518,19 +518,19 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="E3" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>408.5</v>
+        <v>409.6</v>
       </c>
       <c r="I3" t="n">
         <v>835.2</v>
@@ -586,7 +586,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -595,10 +595,10 @@
         <v>87.3</v>
       </c>
       <c r="G5" t="n">
-        <v>40.7</v>
+        <v>41.8</v>
       </c>
       <c r="H5" t="n">
-        <v>398</v>
+        <v>399.1</v>
       </c>
       <c r="I5" t="n">
         <v>834.7</v>
@@ -620,19 +620,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="E6" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>91.2</v>
+        <v>92.5</v>
       </c>
       <c r="G6" t="n">
         <v>11.4</v>
       </c>
       <c r="H6" t="n">
-        <v>302.7</v>
+        <v>304</v>
       </c>
       <c r="I6" t="n">
         <v>793.8</v>
@@ -654,10 +654,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="E7" t="n">
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
       <c r="F7" t="n">
         <v>80.40000000000001</v>
@@ -666,7 +666,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>180.1</v>
+        <v>181.6</v>
       </c>
       <c r="I7" t="n">
         <v>817.7</v>
@@ -688,19 +688,19 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>57.6</v>
+        <v>58.4</v>
       </c>
       <c r="E8" t="n">
-        <v>57.6</v>
+        <v>58.4</v>
       </c>
       <c r="F8" t="n">
         <v>62.8</v>
       </c>
       <c r="G8" t="n">
-        <v>52.4</v>
+        <v>53.9</v>
       </c>
       <c r="H8" t="n">
-        <v>115.2</v>
+        <v>116.7</v>
       </c>
       <c r="I8" t="n">
         <v>786</v>
@@ -722,19 +722,19 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>56.6</v>
+        <v>57.4</v>
       </c>
       <c r="E9" t="n">
-        <v>56.6</v>
+        <v>57.4</v>
       </c>
       <c r="F9" t="n">
         <v>64.7</v>
       </c>
       <c r="G9" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
-        <v>113.3</v>
+        <v>114.7</v>
       </c>
       <c r="I9" t="n">
         <v>784.5</v>
@@ -799,10 +799,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>764</v>
@@ -836,7 +836,7 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>165.6</v>
+        <v>165.5</v>
       </c>
       <c r="I12" t="n">
         <v>719.7</v>
@@ -858,19 +858,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="n">
         <v>3.3</v>
       </c>
       <c r="F13" t="n">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="G13" t="n">
         <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>42.1</v>
+        <v>43.1</v>
       </c>
       <c r="I13" t="n">
         <v>658.7</v>
@@ -889,28 +889,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6</v>
+        <v>11.9</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="F14" t="n">
-        <v>6.1</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>13.7</v>
+        <v>47.7</v>
       </c>
       <c r="I14" t="n">
-        <v>587.7</v>
+        <v>626.5</v>
       </c>
       <c r="J14" t="n">
-        <v>698</v>
+        <v>743</v>
       </c>
     </row>
     <row r="15">
@@ -1286,7 +1286,9 @@
       <c r="F15" t="n">
         <v>532</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>743</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1361,7 +1363,7 @@
         <v>30.5</v>
       </c>
       <c r="G2" t="n">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1386,7 +1388,7 @@
         <v>40.5</v>
       </c>
       <c r="G3" t="n">
-        <v>91.8</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1405,7 +1407,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="5">
@@ -1422,7 +1424,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
@@ -1470,7 +1472,7 @@
         <v>67.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>40.7</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="8">
@@ -1531,7 +1533,7 @@
         <v>48.8</v>
       </c>
       <c r="G10" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="11">
@@ -1550,7 +1552,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="12">
@@ -1567,7 +1569,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>52.4</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="13">
@@ -1590,7 +1592,7 @@
         <v>46.3</v>
       </c>
       <c r="G13" t="n">
-        <v>91.2</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="14">
@@ -1607,7 +1609,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -1627,7 +1629,9 @@
       <c r="F15" t="n">
         <v>1.9</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1812,16 +1816,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>784.4</v>
+        <v>780.9</v>
       </c>
       <c r="D7" t="n">
-        <v>95.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>781</v>
+        <v>771.5</v>
       </c>
       <c r="F7" t="n">
         <v>927</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,19 +484,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="E2" t="n">
         <v>81.7</v>
       </c>
       <c r="F2" t="n">
-        <v>93.7</v>
+        <v>94.2</v>
       </c>
       <c r="G2" t="n">
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>458.1</v>
+        <v>459.2</v>
       </c>
       <c r="I2" t="n">
         <v>864.3</v>
@@ -518,19 +518,19 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>73.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>94.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="G3" t="n">
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>409.6</v>
+        <v>410.5</v>
       </c>
       <c r="I3" t="n">
         <v>835.2</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>67.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>69.8</v>
+        <v>66.2</v>
       </c>
       <c r="F4" t="n">
-        <v>90.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="G4" t="n">
-        <v>38.9</v>
+        <v>43.9</v>
       </c>
       <c r="H4" t="n">
-        <v>269.3</v>
+        <v>401.2</v>
       </c>
       <c r="I4" t="n">
-        <v>832.8</v>
+        <v>834.7</v>
       </c>
       <c r="J4" t="n">
-        <v>902</v>
+        <v>879</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>66.5</v>
+        <v>61.3</v>
       </c>
       <c r="E5" t="n">
-        <v>66.2</v>
+        <v>54.5</v>
       </c>
       <c r="F5" t="n">
-        <v>87.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>41.8</v>
+        <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>399.1</v>
+        <v>183.9</v>
       </c>
       <c r="I5" t="n">
-        <v>834.7</v>
+        <v>817.7</v>
       </c>
       <c r="J5" t="n">
-        <v>879</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6">
@@ -620,19 +620,19 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>60.8</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>92.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>11.4</v>
       </c>
       <c r="H6" t="n">
-        <v>304</v>
+        <v>305.1</v>
       </c>
       <c r="I6" t="n">
         <v>793.8</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>60.5</v>
+        <v>59.5</v>
       </c>
       <c r="E7" t="n">
-        <v>52.2</v>
+        <v>59.5</v>
       </c>
       <c r="F7" t="n">
-        <v>80.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="G7" t="n">
-        <v>49</v>
+        <v>56.2</v>
       </c>
       <c r="H7" t="n">
-        <v>181.6</v>
+        <v>119</v>
       </c>
       <c r="I7" t="n">
-        <v>817.7</v>
+        <v>786</v>
       </c>
       <c r="J7" t="n">
-        <v>926</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="E8" t="n">
-        <v>58.4</v>
+        <v>50.7</v>
       </c>
       <c r="F8" t="n">
-        <v>62.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>53.9</v>
+        <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>116.7</v>
+        <v>294.6</v>
       </c>
       <c r="I8" t="n">
-        <v>786</v>
+        <v>809.4</v>
       </c>
       <c r="J8" t="n">
-        <v>790</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9">
@@ -722,19 +722,19 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>57.4</v>
+        <v>58.5</v>
       </c>
       <c r="E9" t="n">
-        <v>57.4</v>
+        <v>58.5</v>
       </c>
       <c r="F9" t="n">
         <v>64.7</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>52.3</v>
       </c>
       <c r="H9" t="n">
-        <v>114.7</v>
+        <v>117</v>
       </c>
       <c r="I9" t="n">
         <v>784.5</v>
@@ -756,7 +756,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="E10" t="n">
         <v>56.2</v>
@@ -768,7 +768,7 @@
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>238.4</v>
+        <v>239.3</v>
       </c>
       <c r="I10" t="n">
         <v>782.8</v>
@@ -799,10 +799,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="I11" t="n">
         <v>764</v>
@@ -824,7 +824,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
@@ -836,7 +836,7 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>165.5</v>
+        <v>166.1</v>
       </c>
       <c r="I12" t="n">
         <v>719.7</v>
@@ -858,19 +858,19 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>3.3</v>
       </c>
       <c r="F13" t="n">
-        <v>38.5</v>
+        <v>40.4</v>
       </c>
       <c r="G13" t="n">
         <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>43.1</v>
+        <v>45</v>
       </c>
       <c r="I13" t="n">
         <v>658.7</v>
@@ -892,19 +892,19 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="E14" t="n">
         <v>5.9</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>35.7</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>47.7</v>
+        <v>49.4</v>
       </c>
       <c r="I14" t="n">
         <v>626.5</v>
@@ -1151,7 +1151,9 @@
       <c r="F8" t="n">
         <v>902</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>716</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1363,7 +1365,7 @@
         <v>30.5</v>
       </c>
       <c r="G2" t="n">
-        <v>94.40000000000001</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="3">
@@ -1388,7 +1390,7 @@
         <v>40.5</v>
       </c>
       <c r="G3" t="n">
-        <v>93.09999999999999</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="4">
@@ -1407,7 +1409,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>52.2</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="5">
@@ -1424,7 +1426,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6">
@@ -1447,7 +1449,7 @@
         <v>87.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>16.9</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="7">
@@ -1472,7 +1474,7 @@
         <v>67.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>41.8</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="8">
@@ -1494,7 +1496,9 @@
       <c r="F8" t="n">
         <v>90.90000000000001</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>25.3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1533,7 +1537,7 @@
         <v>48.8</v>
       </c>
       <c r="G10" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="11">
@@ -1552,7 +1556,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>38.5</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="12">
@@ -1569,7 +1573,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>53.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="13">
@@ -1592,7 +1596,7 @@
         <v>46.3</v>
       </c>
       <c r="G13" t="n">
-        <v>92.5</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1609,7 +1613,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="15">
@@ -1630,7 +1634,7 @@
         <v>1.9</v>
       </c>
       <c r="G15" t="n">
-        <v>34</v>
+        <v>35.7</v>
       </c>
     </row>
   </sheetData>
@@ -1816,16 +1820,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>780.9</v>
+        <v>775.9</v>
       </c>
       <c r="D7" t="n">
-        <v>91.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="E7" t="n">
-        <v>771.5</v>
+        <v>762</v>
       </c>
       <c r="F7" t="n">
         <v>927</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>58.9</v>
+        <v>58.5</v>
       </c>
       <c r="E8" t="n">
-        <v>50.7</v>
+        <v>58.5</v>
       </c>
       <c r="F8" t="n">
-        <v>90.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G8" t="n">
-        <v>25.3</v>
+        <v>52.3</v>
       </c>
       <c r="H8" t="n">
-        <v>294.6</v>
+        <v>117</v>
       </c>
       <c r="I8" t="n">
-        <v>809.4</v>
+        <v>784.5</v>
       </c>
       <c r="J8" t="n">
-        <v>902</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>58.5</v>
+        <v>53.9</v>
       </c>
       <c r="E9" t="n">
-        <v>58.5</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>64.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>52.3</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>117</v>
+        <v>323.4</v>
       </c>
       <c r="I9" t="n">
-        <v>784.5</v>
+        <v>812.3</v>
       </c>
       <c r="J9" t="n">
-        <v>788</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>47.9</v>
+        <v>51.8</v>
       </c>
       <c r="E10" t="n">
-        <v>56.2</v>
+        <v>44.8</v>
       </c>
       <c r="F10" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="H10" t="n">
-        <v>239.3</v>
+        <v>310.5</v>
       </c>
       <c r="I10" t="n">
-        <v>782.8</v>
+        <v>829.2</v>
       </c>
       <c r="J10" t="n">
-        <v>887</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11">
@@ -958,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -997,6 +997,11 @@
           <t>9/7/26</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>9/8/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1022,6 +1027,7 @@
       <c r="G2" t="n">
         <v>927</v>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1047,6 +1053,7 @@
       <c r="G3" t="n">
         <v>917</v>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1066,6 +1073,7 @@
       <c r="G4" t="n">
         <v>786</v>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1083,6 +1091,7 @@
       <c r="G5" t="n">
         <v>634</v>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1106,6 +1115,9 @@
       <c r="G6" t="n">
         <v>693</v>
       </c>
+      <c r="H6" t="n">
+        <v>960</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1131,6 +1143,7 @@
       <c r="G7" t="n">
         <v>762</v>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1153,6 +1166,9 @@
       </c>
       <c r="G8" t="n">
         <v>716</v>
+      </c>
+      <c r="H8" t="n">
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -1169,6 +1185,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1194,6 +1211,7 @@
       <c r="G10" t="n">
         <v>671</v>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1213,6 +1231,7 @@
       <c r="G11" t="n">
         <v>754</v>
       </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1230,6 +1249,7 @@
       <c r="G12" t="n">
         <v>790</v>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1253,6 +1273,7 @@
       <c r="G13" t="n">
         <v>913</v>
       </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1270,6 +1291,7 @@
       <c r="G14" t="n">
         <v>781</v>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1291,6 +1313,7 @@
       <c r="G15" t="n">
         <v>743</v>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1303,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1342,6 +1365,11 @@
           <t>9/7/26</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>9/8/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1367,6 +1395,7 @@
       <c r="G2" t="n">
         <v>95.3</v>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1392,6 +1421,7 @@
       <c r="G3" t="n">
         <v>94.2</v>
       </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1411,6 +1441,7 @@
       <c r="G4" t="n">
         <v>54.5</v>
       </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1428,6 +1459,7 @@
       <c r="G5" t="n">
         <v>5.7</v>
       </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1451,6 +1483,9 @@
       <c r="G6" t="n">
         <v>17.8</v>
       </c>
+      <c r="H6" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1476,6 +1511,7 @@
       <c r="G7" t="n">
         <v>43.9</v>
       </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1498,6 +1534,9 @@
       </c>
       <c r="G8" t="n">
         <v>25.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15.9</v>
       </c>
     </row>
     <row r="9">
@@ -1514,6 +1553,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1539,6 +1579,7 @@
       <c r="G10" t="n">
         <v>12.2</v>
       </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1558,6 +1599,7 @@
       <c r="G11" t="n">
         <v>40.4</v>
       </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1575,6 +1617,7 @@
       <c r="G12" t="n">
         <v>56.2</v>
       </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1598,6 +1641,7 @@
       <c r="G13" t="n">
         <v>93.59999999999999</v>
       </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1615,6 +1659,7 @@
       <c r="G14" t="n">
         <v>52.3</v>
       </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1636,6 +1681,7 @@
       <c r="G15" t="n">
         <v>35.7</v>
       </c>
+      <c r="H15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1648,7 +1694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,6 +1884,31 @@
         <v>634</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>9/8/26</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>944</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>944</v>
+      </c>
+      <c r="F8" t="n">
+        <v>960</v>
+      </c>
+      <c r="G8" t="n">
+        <v>928</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>68.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="E3" t="n">
-        <v>73.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>95.3</v>
+        <v>87.3</v>
       </c>
       <c r="G3" t="n">
-        <v>30.5</v>
+        <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>410.5</v>
+        <v>486.6</v>
       </c>
       <c r="I3" t="n">
-        <v>835.2</v>
+        <v>854.7</v>
       </c>
       <c r="J3" t="n">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>66.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>66.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>87.3</v>
+        <v>95.3</v>
       </c>
       <c r="G4" t="n">
-        <v>43.9</v>
+        <v>30.5</v>
       </c>
       <c r="H4" t="n">
-        <v>401.2</v>
+        <v>410.5</v>
       </c>
       <c r="I4" t="n">
-        <v>834.7</v>
+        <v>835.2</v>
       </c>
       <c r="J4" t="n">
-        <v>879</v>
+        <v>967</v>
       </c>
     </row>
     <row r="5">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>53.9</v>
+        <v>50.6</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>44.8</v>
       </c>
       <c r="F9" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>323.4</v>
+        <v>303.6</v>
       </c>
       <c r="I9" t="n">
-        <v>812.3</v>
+        <v>829.2</v>
       </c>
       <c r="J9" t="n">
-        <v>960</v>
+        <v>928</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>51.8</v>
+        <v>50.1</v>
       </c>
       <c r="E10" t="n">
-        <v>44.8</v>
+        <v>58.8</v>
       </c>
       <c r="F10" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>310.5</v>
+        <v>300.7</v>
       </c>
       <c r="I10" t="n">
-        <v>829.2</v>
+        <v>812.3</v>
       </c>
       <c r="J10" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="11">
@@ -1143,7 +1143,9 @@
       <c r="G7" t="n">
         <v>762</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>975</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1484,7 +1486,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>84.09999999999999</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="7">
@@ -1511,7 +1513,9 @@
       <c r="G7" t="n">
         <v>43.9</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>85.40000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1536,7 +1540,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>15.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -1891,19 +1895,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>944</v>
+        <v>954.3</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="E8" t="n">
-        <v>944</v>
+        <v>960</v>
       </c>
       <c r="F8" t="n">
-        <v>960</v>
+        <v>975</v>
       </c>
       <c r="G8" t="n">
         <v>928</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>81.7</v>
+        <v>77.2</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,13 +496,13 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>459.2</v>
+        <v>536.4</v>
       </c>
       <c r="I2" t="n">
-        <v>864.3</v>
+        <v>879.9</v>
       </c>
       <c r="J2" t="n">
-        <v>944</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>69.5</v>
+        <v>68.8</v>
       </c>
       <c r="E3" t="n">
         <v>67.09999999999999</v>
@@ -530,7 +530,7 @@
         <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>486.6</v>
+        <v>481.5</v>
       </c>
       <c r="I3" t="n">
         <v>854.7</v>
@@ -722,7 +722,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>50.6</v>
+        <v>49.9</v>
       </c>
       <c r="E9" t="n">
         <v>44.8</v>
@@ -731,10 +731,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>303.6</v>
+        <v>299.6</v>
       </c>
       <c r="I9" t="n">
         <v>829.2</v>
@@ -756,10 +756,10 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1</v>
+        <v>48.6</v>
       </c>
       <c r="E10" t="n">
-        <v>58.8</v>
+        <v>54.2</v>
       </c>
       <c r="F10" t="n">
         <v>87.90000000000001</v>
@@ -768,7 +768,7 @@
         <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>300.7</v>
+        <v>291.4</v>
       </c>
       <c r="I10" t="n">
         <v>812.3</v>
@@ -1053,7 +1053,9 @@
       <c r="G3" t="n">
         <v>917</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>973</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1423,7 +1425,9 @@
       <c r="G3" t="n">
         <v>94.2</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>77.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1486,7 +1490,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>61.4</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="7">
@@ -1514,7 +1518,7 @@
         <v>43.9</v>
       </c>
       <c r="H7" t="n">
-        <v>85.40000000000001</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="8">
@@ -1540,7 +1544,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1895,16 +1899,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>954.3</v>
+        <v>959</v>
       </c>
       <c r="D8" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="n">
-        <v>960</v>
+        <v>966.5</v>
       </c>
       <c r="F8" t="n">
         <v>975</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>76.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="E2" t="n">
-        <v>77.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>536.4</v>
+        <v>543.6</v>
       </c>
       <c r="I2" t="n">
         <v>879.9</v>
@@ -518,7 +518,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>68.8</v>
+        <v>69.5</v>
       </c>
       <c r="E3" t="n">
         <v>67.09999999999999</v>
@@ -530,7 +530,7 @@
         <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>481.5</v>
+        <v>486.5</v>
       </c>
       <c r="I3" t="n">
         <v>854.7</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
-        <v>73.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="F4" t="n">
         <v>95.3</v>
@@ -564,10 +564,10 @@
         <v>30.5</v>
       </c>
       <c r="H4" t="n">
-        <v>410.5</v>
+        <v>483</v>
       </c>
       <c r="I4" t="n">
-        <v>835.2</v>
+        <v>851.9</v>
       </c>
       <c r="J4" t="n">
         <v>967</v>
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>61.3</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>54.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>80.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>183.9</v>
+        <v>305.1</v>
       </c>
       <c r="I5" t="n">
-        <v>817.7</v>
+        <v>793.8</v>
       </c>
       <c r="J5" t="n">
-        <v>926</v>
+        <v>913</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>59.5</v>
       </c>
       <c r="E6" t="n">
-        <v>72.40000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="F6" t="n">
-        <v>93.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="G6" t="n">
-        <v>11.4</v>
+        <v>56.2</v>
       </c>
       <c r="H6" t="n">
-        <v>305.1</v>
+        <v>119</v>
       </c>
       <c r="I6" t="n">
-        <v>793.8</v>
+        <v>786</v>
       </c>
       <c r="J6" t="n">
-        <v>913</v>
+        <v>790</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="E7" t="n">
-        <v>59.5</v>
+        <v>58.5</v>
       </c>
       <c r="F7" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="G7" t="n">
-        <v>56.2</v>
+        <v>52.3</v>
       </c>
       <c r="H7" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I7" t="n">
-        <v>786</v>
+        <v>784.5</v>
       </c>
       <c r="J7" t="n">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>58.5</v>
+        <v>58.2</v>
       </c>
       <c r="E8" t="n">
-        <v>58.5</v>
+        <v>52.8</v>
       </c>
       <c r="F8" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>52.3</v>
+        <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>117</v>
+        <v>349.5</v>
       </c>
       <c r="I8" t="n">
-        <v>784.5</v>
+        <v>829.2</v>
       </c>
       <c r="J8" t="n">
-        <v>788</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>49.9</v>
+        <v>52.8</v>
       </c>
       <c r="E9" t="n">
-        <v>44.8</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>299.6</v>
+        <v>316.8</v>
       </c>
       <c r="I9" t="n">
-        <v>829.2</v>
+        <v>812.3</v>
       </c>
       <c r="J9" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="E10" t="n">
-        <v>54.2</v>
+        <v>51.8</v>
       </c>
       <c r="F10" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="H10" t="n">
-        <v>291.4</v>
+        <v>195</v>
       </c>
       <c r="I10" t="n">
-        <v>812.3</v>
+        <v>828.2</v>
       </c>
       <c r="J10" t="n">
-        <v>960</v>
+        <v>926</v>
       </c>
     </row>
     <row r="11">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>35.6</v>
+        <v>33.5</v>
       </c>
       <c r="E11" t="n">
-        <v>35.6</v>
+        <v>29.2</v>
       </c>
       <c r="F11" t="n">
         <v>65.59999999999999</v>
@@ -802,10 +802,10 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>71.3</v>
+        <v>100.5</v>
       </c>
       <c r="I11" t="n">
-        <v>764</v>
+        <v>807.3</v>
       </c>
       <c r="J11" t="n">
         <v>894</v>
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>12.4</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="F13" t="n">
-        <v>40.4</v>
+        <v>35.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>45</v>
+        <v>49.4</v>
       </c>
       <c r="I13" t="n">
-        <v>658.7</v>
+        <v>626.5</v>
       </c>
       <c r="J13" t="n">
-        <v>754</v>
+        <v>743</v>
       </c>
     </row>
     <row r="14">
@@ -885,32 +885,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="F14" t="n">
-        <v>35.7</v>
+        <v>40.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="I14" t="n">
-        <v>626.5</v>
+        <v>702</v>
       </c>
       <c r="J14" t="n">
-        <v>743</v>
+        <v>832</v>
       </c>
     </row>
     <row r="15">
@@ -1027,7 +1027,9 @@
       <c r="G2" t="n">
         <v>927</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>952</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1075,7 +1077,9 @@
       <c r="G4" t="n">
         <v>786</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>860</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1093,7 +1097,9 @@
       <c r="G5" t="n">
         <v>634</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>894</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1235,7 +1241,9 @@
       <c r="G11" t="n">
         <v>754</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>832</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1399,7 +1407,9 @@
       <c r="G2" t="n">
         <v>95.3</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>72.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1426,7 +1436,7 @@
         <v>94.2</v>
       </c>
       <c r="H3" t="n">
-        <v>77.2</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1447,7 +1457,9 @@
       <c r="G4" t="n">
         <v>54.5</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1465,7 +1477,9 @@
       <c r="G5" t="n">
         <v>5.7</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1490,7 +1504,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>52.1</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="7">
@@ -1518,7 +1532,7 @@
         <v>43.9</v>
       </c>
       <c r="H7" t="n">
-        <v>80.3</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="8">
@@ -1544,7 +1558,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="9">
@@ -1607,7 +1621,9 @@
       <c r="G11" t="n">
         <v>40.4</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1899,22 +1915,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>959</v>
+        <v>921.8</v>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>50.6</v>
       </c>
       <c r="E8" t="n">
-        <v>966.5</v>
+        <v>940</v>
       </c>
       <c r="F8" t="n">
         <v>975</v>
       </c>
       <c r="G8" t="n">
-        <v>928</v>
+        <v>832</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>77.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>84.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>543.6</v>
+        <v>547</v>
       </c>
       <c r="I2" t="n">
         <v>879.9</v>
@@ -518,19 +518,19 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>87.3</v>
+        <v>88.7</v>
       </c>
       <c r="G3" t="n">
         <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>486.5</v>
+        <v>489.9</v>
       </c>
       <c r="I3" t="n">
         <v>854.7</v>
@@ -552,10 +552,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="E4" t="n">
-        <v>72.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>95.3</v>
@@ -564,7 +564,7 @@
         <v>30.5</v>
       </c>
       <c r="H4" t="n">
-        <v>483</v>
+        <v>486.4</v>
       </c>
       <c r="I4" t="n">
         <v>851.9</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="E7" t="n">
-        <v>58.5</v>
+        <v>53.8</v>
       </c>
       <c r="F7" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>52.3</v>
+        <v>25.3</v>
       </c>
       <c r="H7" t="n">
-        <v>117</v>
+        <v>351.6</v>
       </c>
       <c r="I7" t="n">
-        <v>784.5</v>
+        <v>829.2</v>
       </c>
       <c r="J7" t="n">
-        <v>788</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>58.2</v>
+        <v>54.5</v>
       </c>
       <c r="E8" t="n">
-        <v>52.8</v>
+        <v>52.3</v>
       </c>
       <c r="F8" t="n">
-        <v>90.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G8" t="n">
-        <v>25.3</v>
+        <v>46.5</v>
       </c>
       <c r="H8" t="n">
-        <v>349.5</v>
+        <v>163.5</v>
       </c>
       <c r="I8" t="n">
-        <v>829.2</v>
+        <v>828.3</v>
       </c>
       <c r="J8" t="n">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>52.8</v>
+        <v>53.4</v>
       </c>
       <c r="E9" t="n">
         <v>59</v>
@@ -734,7 +734,7 @@
         <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>316.8</v>
+        <v>320.4</v>
       </c>
       <c r="I9" t="n">
         <v>812.3</v>
@@ -756,7 +756,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>48.8</v>
+        <v>48.3</v>
       </c>
       <c r="E10" t="n">
         <v>51.8</v>
@@ -765,10 +765,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>195</v>
+        <v>193.2</v>
       </c>
       <c r="I10" t="n">
         <v>828.2</v>
@@ -790,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
       <c r="E11" t="n">
-        <v>29.2</v>
+        <v>28.4</v>
       </c>
       <c r="F11" t="n">
         <v>65.59999999999999</v>
@@ -802,7 +802,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>100.5</v>
+        <v>99.7</v>
       </c>
       <c r="I11" t="n">
         <v>807.3</v>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>27.7</v>
+        <v>29.6</v>
       </c>
       <c r="E12" t="n">
-        <v>28.2</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>48.8</v>
@@ -836,13 +836,13 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>166.1</v>
+        <v>207.4</v>
       </c>
       <c r="I12" t="n">
-        <v>719.7</v>
+        <v>746.9</v>
       </c>
       <c r="J12" t="n">
-        <v>835</v>
+        <v>910</v>
       </c>
     </row>
     <row r="13">
@@ -892,10 +892,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>40.4</v>
@@ -904,7 +904,7 @@
         <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
       <c r="I14" t="n">
         <v>702</v>
@@ -1221,7 +1221,9 @@
       <c r="G10" t="n">
         <v>671</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>910</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1303,7 +1305,9 @@
       <c r="G14" t="n">
         <v>781</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>916</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1408,7 +1412,7 @@
         <v>95.3</v>
       </c>
       <c r="H2" t="n">
-        <v>72.5</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1436,7 +1440,7 @@
         <v>94.2</v>
       </c>
       <c r="H3" t="n">
-        <v>84.40000000000001</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="4">
@@ -1458,7 +1462,7 @@
         <v>54.5</v>
       </c>
       <c r="H4" t="n">
-        <v>11.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1478,7 +1482,7 @@
         <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>29.2</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="6">
@@ -1504,7 +1508,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>77.5</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1532,7 +1536,7 @@
         <v>43.9</v>
       </c>
       <c r="H7" t="n">
-        <v>85.3</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="8">
@@ -1558,7 +1562,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>54.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1601,7 +1605,9 @@
       <c r="G10" t="n">
         <v>12.2</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>41.3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1622,7 +1628,7 @@
         <v>40.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -1683,7 +1689,9 @@
       <c r="G14" t="n">
         <v>52.3</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>46.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1915,16 +1923,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>921.8</v>
+        <v>920</v>
       </c>
       <c r="D8" t="n">
-        <v>50.6</v>
+        <v>45.5</v>
       </c>
       <c r="E8" t="n">
-        <v>940</v>
+        <v>922</v>
       </c>
       <c r="F8" t="n">
         <v>975</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>78.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I2" t="n">
         <v>879.9</v>
@@ -518,19 +518,19 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>88.7</v>
+        <v>89.5</v>
       </c>
       <c r="G3" t="n">
         <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>489.9</v>
+        <v>490.7</v>
       </c>
       <c r="I3" t="n">
         <v>854.7</v>
@@ -552,10 +552,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>69.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>75.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="F4" t="n">
         <v>95.3</v>
@@ -564,7 +564,7 @@
         <v>30.5</v>
       </c>
       <c r="H4" t="n">
-        <v>486.4</v>
+        <v>489.2</v>
       </c>
       <c r="I4" t="n">
         <v>851.9</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>59.5</v>
       </c>
       <c r="E6" t="n">
-        <v>59.5</v>
+        <v>56.6</v>
       </c>
       <c r="F6" t="n">
-        <v>62.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>56.2</v>
+        <v>25.3</v>
       </c>
       <c r="H6" t="n">
-        <v>119</v>
+        <v>357.1</v>
       </c>
       <c r="I6" t="n">
-        <v>786</v>
+        <v>829.2</v>
       </c>
       <c r="J6" t="n">
-        <v>790</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>58.6</v>
+        <v>59.5</v>
       </c>
       <c r="E7" t="n">
-        <v>53.8</v>
+        <v>59.5</v>
       </c>
       <c r="F7" t="n">
-        <v>90.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="G7" t="n">
-        <v>25.3</v>
+        <v>56.2</v>
       </c>
       <c r="H7" t="n">
-        <v>351.6</v>
+        <v>119</v>
       </c>
       <c r="I7" t="n">
-        <v>829.2</v>
+        <v>786</v>
       </c>
       <c r="J7" t="n">
-        <v>928</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
@@ -688,19 +688,19 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>54.5</v>
+        <v>56.7</v>
       </c>
       <c r="E8" t="n">
-        <v>52.3</v>
+        <v>53.2</v>
       </c>
       <c r="F8" t="n">
         <v>64.7</v>
       </c>
       <c r="G8" t="n">
-        <v>46.5</v>
+        <v>52.3</v>
       </c>
       <c r="H8" t="n">
-        <v>163.5</v>
+        <v>170.2</v>
       </c>
       <c r="I8" t="n">
         <v>828.3</v>
@@ -722,7 +722,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>53.4</v>
+        <v>53.7</v>
       </c>
       <c r="E9" t="n">
         <v>59</v>
@@ -734,7 +734,7 @@
         <v>15.5</v>
       </c>
       <c r="H9" t="n">
-        <v>320.4</v>
+        <v>322.4</v>
       </c>
       <c r="I9" t="n">
         <v>812.3</v>
@@ -756,7 +756,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>48.3</v>
+        <v>49.7</v>
       </c>
       <c r="E10" t="n">
         <v>51.8</v>
@@ -765,10 +765,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>9.300000000000001</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>193.2</v>
+        <v>198.9</v>
       </c>
       <c r="I10" t="n">
         <v>828.2</v>
@@ -790,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>33.2</v>
+        <v>35.8</v>
       </c>
       <c r="E11" t="n">
-        <v>28.4</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
         <v>65.59999999999999</v>
@@ -802,7 +802,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>99.7</v>
+        <v>107.3</v>
       </c>
       <c r="I11" t="n">
         <v>807.3</v>
@@ -824,7 +824,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
@@ -836,7 +836,7 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>207.4</v>
+        <v>214.5</v>
       </c>
       <c r="I12" t="n">
         <v>746.9</v>
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="F13" t="n">
-        <v>35.7</v>
+        <v>40.4</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
       <c r="I13" t="n">
-        <v>626.5</v>
+        <v>702</v>
       </c>
       <c r="J13" t="n">
-        <v>743</v>
+        <v>832</v>
       </c>
     </row>
     <row r="14">
@@ -885,29 +885,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="n">
-        <v>40.4</v>
+        <v>35.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>47.6</v>
+        <v>54.9</v>
       </c>
       <c r="I14" t="n">
-        <v>702</v>
+        <v>667.6</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1329,7 +1329,9 @@
       <c r="G15" t="n">
         <v>743</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>832</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1412,7 +1414,7 @@
         <v>95.3</v>
       </c>
       <c r="H2" t="n">
-        <v>75.90000000000001</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="3">
@@ -1440,7 +1442,7 @@
         <v>94.2</v>
       </c>
       <c r="H3" t="n">
-        <v>87.8</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="4">
@@ -1462,7 +1464,7 @@
         <v>54.5</v>
       </c>
       <c r="H4" t="n">
-        <v>9.300000000000001</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1482,7 +1484,7 @@
         <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>28.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -1508,7 +1510,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>81.09999999999999</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1536,7 +1538,7 @@
         <v>43.9</v>
       </c>
       <c r="H7" t="n">
-        <v>88.7</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="8">
@@ -1562,7 +1564,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>57</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="9">
@@ -1606,7 +1608,7 @@
         <v>12.2</v>
       </c>
       <c r="H10" t="n">
-        <v>41.3</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="11">
@@ -1628,7 +1630,7 @@
         <v>40.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="12">
@@ -1690,7 +1692,7 @@
         <v>52.3</v>
       </c>
       <c r="H14" t="n">
-        <v>46.5</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="15">
@@ -1713,7 +1715,9 @@
       <c r="G15" t="n">
         <v>35.7</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>5.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1923,16 +1927,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="D8" t="n">
-        <v>45.5</v>
+        <v>50.2</v>
       </c>
       <c r="E8" t="n">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="F8" t="n">
         <v>975</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>548</v>
+        <v>549.5</v>
       </c>
       <c r="I2" t="n">
         <v>879.9</v>
@@ -518,19 +518,19 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="E3" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>89.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>490.7</v>
+        <v>492.1</v>
       </c>
       <c r="I3" t="n">
         <v>854.7</v>
@@ -552,10 +552,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>69.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="E4" t="n">
-        <v>78.7</v>
+        <v>81.2</v>
       </c>
       <c r="F4" t="n">
         <v>95.3</v>
@@ -564,7 +564,7 @@
         <v>30.5</v>
       </c>
       <c r="H4" t="n">
-        <v>489.2</v>
+        <v>491.7</v>
       </c>
       <c r="I4" t="n">
         <v>851.9</v>
@@ -620,10 +620,10 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>59.5</v>
+        <v>60.1</v>
       </c>
       <c r="E6" t="n">
-        <v>56.6</v>
+        <v>58.4</v>
       </c>
       <c r="F6" t="n">
         <v>90.90000000000001</v>
@@ -632,7 +632,7 @@
         <v>25.3</v>
       </c>
       <c r="H6" t="n">
-        <v>357.1</v>
+        <v>360.7</v>
       </c>
       <c r="I6" t="n">
         <v>829.2</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>59.5</v>
+        <v>58.1</v>
       </c>
       <c r="E7" t="n">
-        <v>59.5</v>
+        <v>57.2</v>
       </c>
       <c r="F7" t="n">
-        <v>62.8</v>
+        <v>64.7</v>
       </c>
       <c r="G7" t="n">
-        <v>56.2</v>
+        <v>52.3</v>
       </c>
       <c r="H7" t="n">
-        <v>119</v>
+        <v>174.2</v>
       </c>
       <c r="I7" t="n">
-        <v>786</v>
+        <v>828.3</v>
       </c>
       <c r="J7" t="n">
-        <v>790</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>56.7</v>
+        <v>54.1</v>
       </c>
       <c r="E8" t="n">
-        <v>53.2</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
-        <v>64.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>52.3</v>
+        <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>170.2</v>
+        <v>324.4</v>
       </c>
       <c r="I8" t="n">
-        <v>828.3</v>
+        <v>812.3</v>
       </c>
       <c r="J8" t="n">
-        <v>916</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>53.7</v>
+        <v>50.5</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>51.8</v>
       </c>
       <c r="F9" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>322.4</v>
+        <v>201.9</v>
       </c>
       <c r="I9" t="n">
-        <v>812.3</v>
+        <v>828.2</v>
       </c>
       <c r="J9" t="n">
-        <v>960</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>49.7</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>51.8</v>
+        <v>56.2</v>
       </c>
       <c r="F10" t="n">
-        <v>80.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>12.9</v>
       </c>
       <c r="H10" t="n">
-        <v>198.9</v>
+        <v>131.9</v>
       </c>
       <c r="I10" t="n">
-        <v>828.2</v>
+        <v>807</v>
       </c>
       <c r="J10" t="n">
-        <v>926</v>
+        <v>849</v>
       </c>
     </row>
     <row r="11">
@@ -790,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>35.8</v>
+        <v>37.1</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>40.1</v>
       </c>
       <c r="F11" t="n">
         <v>65.59999999999999</v>
@@ -802,7 +802,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>107.3</v>
+        <v>111.4</v>
       </c>
       <c r="I11" t="n">
         <v>807.3</v>
@@ -824,19 +824,19 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>48.8</v>
+        <v>52.5</v>
       </c>
       <c r="G12" t="n">
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>214.5</v>
+        <v>218.6</v>
       </c>
       <c r="I12" t="n">
         <v>746.9</v>
@@ -858,10 +858,10 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="F13" t="n">
         <v>40.4</v>
@@ -870,7 +870,7 @@
         <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>50.5</v>
+        <v>52.2</v>
       </c>
       <c r="I13" t="n">
         <v>702</v>
@@ -892,10 +892,10 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="n">
         <v>35.7</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>54.9</v>
+        <v>56.6</v>
       </c>
       <c r="I14" t="n">
         <v>667.6</v>
@@ -1263,7 +1263,9 @@
       <c r="G12" t="n">
         <v>790</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>849</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1414,7 +1416,7 @@
         <v>95.3</v>
       </c>
       <c r="H2" t="n">
-        <v>78.7</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="3">
@@ -1442,7 +1444,7 @@
         <v>94.2</v>
       </c>
       <c r="H3" t="n">
-        <v>88.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="4">
@@ -1464,7 +1466,7 @@
         <v>54.5</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1484,7 +1486,7 @@
         <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>36</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="6">
@@ -1510,7 +1512,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>83.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1538,7 +1540,7 @@
         <v>43.9</v>
       </c>
       <c r="H7" t="n">
-        <v>89.5</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1564,7 +1566,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>62.5</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1608,7 +1610,7 @@
         <v>12.2</v>
       </c>
       <c r="H10" t="n">
-        <v>48.4</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="11">
@@ -1630,7 +1632,7 @@
         <v>40.4</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="12">
@@ -1649,7 +1651,9 @@
       <c r="G12" t="n">
         <v>56.2</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>12.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1692,7 +1696,7 @@
         <v>52.3</v>
       </c>
       <c r="H14" t="n">
-        <v>53.2</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="15">
@@ -1716,7 +1720,7 @@
         <v>35.7</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -1927,16 +1931,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>912</v>
+        <v>906.8</v>
       </c>
       <c r="D8" t="n">
-        <v>50.2</v>
+        <v>51.1</v>
       </c>
       <c r="E8" t="n">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="F8" t="n">
         <v>975</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>549.5</v>
+        <v>549.8</v>
       </c>
       <c r="I2" t="n">
         <v>879.9</v>
@@ -511,32 +511,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>kunalrs</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="E3" t="n">
-        <v>67.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="F3" t="n">
-        <v>90.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="G3" t="n">
-        <v>43.9</v>
+        <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>492.1</v>
+        <v>493.3</v>
       </c>
       <c r="I3" t="n">
-        <v>854.7</v>
+        <v>851.9</v>
       </c>
       <c r="J3" t="n">
-        <v>975</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4">
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kunalrs</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>70.2</v>
+        <v>70.3</v>
       </c>
       <c r="E4" t="n">
-        <v>81.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>95.3</v>
+        <v>91.2</v>
       </c>
       <c r="G4" t="n">
-        <v>30.5</v>
+        <v>43.9</v>
       </c>
       <c r="H4" t="n">
-        <v>491.7</v>
+        <v>492.4</v>
       </c>
       <c r="I4" t="n">
-        <v>851.9</v>
+        <v>854.7</v>
       </c>
       <c r="J4" t="n">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="5">
@@ -620,10 +620,10 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>60.1</v>
+        <v>60.7</v>
       </c>
       <c r="E6" t="n">
-        <v>58.4</v>
+        <v>60.2</v>
       </c>
       <c r="F6" t="n">
         <v>90.90000000000001</v>
@@ -632,7 +632,7 @@
         <v>25.3</v>
       </c>
       <c r="H6" t="n">
-        <v>360.7</v>
+        <v>364.4</v>
       </c>
       <c r="I6" t="n">
         <v>829.2</v>
@@ -654,10 +654,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="E7" t="n">
-        <v>57.2</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
         <v>64.7</v>
@@ -666,7 +666,7 @@
         <v>52.3</v>
       </c>
       <c r="H7" t="n">
-        <v>174.2</v>
+        <v>179</v>
       </c>
       <c r="I7" t="n">
         <v>828.3</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="E8" t="n">
         <v>59</v>
@@ -700,7 +700,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>324.4</v>
+        <v>325.4</v>
       </c>
       <c r="I8" t="n">
         <v>812.3</v>
@@ -722,7 +722,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>50.5</v>
+        <v>52.1</v>
       </c>
       <c r="E9" t="n">
         <v>51.8</v>
@@ -731,10 +731,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>24.6</v>
       </c>
       <c r="H9" t="n">
-        <v>201.9</v>
+        <v>208.5</v>
       </c>
       <c r="I9" t="n">
         <v>828.2</v>
@@ -756,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
         <v>56.2</v>
@@ -765,10 +765,10 @@
         <v>62.8</v>
       </c>
       <c r="G10" t="n">
-        <v>12.9</v>
+        <v>18.9</v>
       </c>
       <c r="H10" t="n">
-        <v>131.9</v>
+        <v>137.9</v>
       </c>
       <c r="I10" t="n">
         <v>807</v>
@@ -790,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>37.1</v>
+        <v>39.3</v>
       </c>
       <c r="E11" t="n">
-        <v>40.1</v>
+        <v>46.6</v>
       </c>
       <c r="F11" t="n">
         <v>65.59999999999999</v>
@@ -802,7 +802,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>111.4</v>
+        <v>117.9</v>
       </c>
       <c r="I11" t="n">
         <v>807.3</v>
@@ -824,19 +824,19 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>31.2</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>52.5</v>
+        <v>57.9</v>
       </c>
       <c r="G12" t="n">
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>218.6</v>
+        <v>224</v>
       </c>
       <c r="I12" t="n">
         <v>746.9</v>
@@ -858,10 +858,10 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="F13" t="n">
         <v>40.4</v>
@@ -870,7 +870,7 @@
         <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>52.2</v>
+        <v>56.8</v>
       </c>
       <c r="I13" t="n">
         <v>702</v>
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>11.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="n">
         <v>6.1</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>56.6</v>
+        <v>61.2</v>
       </c>
       <c r="I14" t="n">
         <v>667.6</v>
@@ -919,31 +919,65 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>803</v>
+      </c>
+      <c r="J15" t="n">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>johnson7</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
         <v>4.4</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>4.4</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>4.4</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>4.4</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>4.4</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>746</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>746</v>
       </c>
     </row>
@@ -958,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1333,6 +1367,22 @@
       </c>
       <c r="H15" t="n">
         <v>832</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>waltkin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -1346,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1416,7 +1466,7 @@
         <v>95.3</v>
       </c>
       <c r="H2" t="n">
-        <v>81.2</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="3">
@@ -1444,7 +1494,7 @@
         <v>94.2</v>
       </c>
       <c r="H3" t="n">
-        <v>90.3</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1466,7 +1516,7 @@
         <v>54.5</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="5">
@@ -1486,7 +1536,7 @@
         <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>40.1</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="6">
@@ -1512,7 +1562,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1540,7 +1590,7 @@
         <v>43.9</v>
       </c>
       <c r="H7" t="n">
-        <v>90.90000000000001</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="8">
@@ -1566,7 +1616,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>66.09999999999999</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="9">
@@ -1610,7 +1660,7 @@
         <v>12.2</v>
       </c>
       <c r="H10" t="n">
-        <v>52.5</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="11">
@@ -1632,7 +1682,7 @@
         <v>40.4</v>
       </c>
       <c r="H11" t="n">
-        <v>7.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="12">
@@ -1652,7 +1702,7 @@
         <v>56.2</v>
       </c>
       <c r="H12" t="n">
-        <v>12.9</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="13">
@@ -1696,7 +1746,7 @@
         <v>52.3</v>
       </c>
       <c r="H14" t="n">
-        <v>57.2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -1720,7 +1770,23 @@
         <v>35.7</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>waltkin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -1931,22 +1997,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>906.8</v>
+        <v>898.8</v>
       </c>
       <c r="D8" t="n">
-        <v>51.1</v>
+        <v>56.3</v>
       </c>
       <c r="E8" t="n">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="F8" t="n">
         <v>975</v>
       </c>
       <c r="G8" t="n">
-        <v>832</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>549.8</v>
+        <v>547.6</v>
       </c>
       <c r="I2" t="n">
         <v>879.9</v>
@@ -518,10 +518,10 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>70.5</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>82.8</v>
+        <v>79.7</v>
       </c>
       <c r="F3" t="n">
         <v>95.3</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>493.3</v>
+        <v>490.2</v>
       </c>
       <c r="I3" t="n">
         <v>851.9</v>
@@ -552,19 +552,19 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>70.3</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>91.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>43.9</v>
       </c>
       <c r="H4" t="n">
-        <v>492.4</v>
+        <v>490.3</v>
       </c>
       <c r="I4" t="n">
         <v>854.7</v>
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>72.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>93.59999999999999</v>
@@ -598,13 +598,13 @@
         <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>305.1</v>
+        <v>393.5</v>
       </c>
       <c r="I5" t="n">
-        <v>793.8</v>
+        <v>823.7</v>
       </c>
       <c r="J5" t="n">
-        <v>913</v>
+        <v>973</v>
       </c>
     </row>
     <row r="6">
@@ -620,10 +620,10 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>60.7</v>
+        <v>60.1</v>
       </c>
       <c r="E6" t="n">
-        <v>60.2</v>
+        <v>58.4</v>
       </c>
       <c r="F6" t="n">
         <v>90.90000000000001</v>
@@ -632,7 +632,7 @@
         <v>25.3</v>
       </c>
       <c r="H6" t="n">
-        <v>364.4</v>
+        <v>360.7</v>
       </c>
       <c r="I6" t="n">
         <v>829.2</v>
@@ -654,10 +654,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>59.7</v>
+        <v>58.4</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>58.2</v>
       </c>
       <c r="F7" t="n">
         <v>64.7</v>
@@ -666,7 +666,7 @@
         <v>52.3</v>
       </c>
       <c r="H7" t="n">
-        <v>179</v>
+        <v>175.2</v>
       </c>
       <c r="I7" t="n">
         <v>828.3</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>54.2</v>
+        <v>53.8</v>
       </c>
       <c r="E8" t="n">
         <v>59</v>
@@ -700,7 +700,7 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>325.4</v>
+        <v>322.7</v>
       </c>
       <c r="I8" t="n">
         <v>812.3</v>
@@ -722,7 +722,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="E9" t="n">
         <v>51.8</v>
@@ -731,10 +731,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>24.6</v>
+        <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>208.5</v>
+        <v>206.1</v>
       </c>
       <c r="I9" t="n">
         <v>828.2</v>
@@ -756,7 +756,7 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>45.3</v>
       </c>
       <c r="E10" t="n">
         <v>56.2</v>
@@ -765,10 +765,10 @@
         <v>62.8</v>
       </c>
       <c r="G10" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="H10" t="n">
-        <v>137.9</v>
+        <v>135.9</v>
       </c>
       <c r="I10" t="n">
         <v>807</v>
@@ -790,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>39.3</v>
+        <v>38.1</v>
       </c>
       <c r="E11" t="n">
-        <v>46.6</v>
+        <v>43.1</v>
       </c>
       <c r="F11" t="n">
         <v>65.59999999999999</v>
@@ -802,7 +802,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>117.9</v>
+        <v>114.4</v>
       </c>
       <c r="I11" t="n">
         <v>807.3</v>
@@ -824,19 +824,19 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>31.5</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
       <c r="G12" t="n">
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>224</v>
+        <v>220.2</v>
       </c>
       <c r="I12" t="n">
         <v>746.9</v>
@@ -858,10 +858,10 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="n">
         <v>40.4</v>
@@ -870,7 +870,7 @@
         <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>56.8</v>
+        <v>55.5</v>
       </c>
       <c r="I13" t="n">
         <v>702</v>
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>6.1</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>61.2</v>
+        <v>59.9</v>
       </c>
       <c r="I14" t="n">
         <v>667.6</v>
@@ -919,32 +919,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>johnson7</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>803</v>
+        <v>746</v>
       </c>
       <c r="J15" t="n">
-        <v>803</v>
+        <v>746</v>
       </c>
     </row>
     <row r="16">
@@ -953,32 +953,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>746</v>
+        <v>803</v>
       </c>
       <c r="J16" t="n">
-        <v>746</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1323,9 @@
       <c r="G13" t="n">
         <v>913</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>973</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1466,7 +1468,7 @@
         <v>95.3</v>
       </c>
       <c r="H2" t="n">
-        <v>82.8</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="3">
@@ -1494,7 +1496,7 @@
         <v>94.2</v>
       </c>
       <c r="H3" t="n">
-        <v>90.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1516,7 +1518,7 @@
         <v>54.5</v>
       </c>
       <c r="H4" t="n">
-        <v>24.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="5">
@@ -1536,7 +1538,7 @@
         <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>46.6</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="6">
@@ -1562,7 +1564,7 @@
         <v>17.8</v>
       </c>
       <c r="H6" t="n">
-        <v>86.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1590,7 +1592,7 @@
         <v>43.9</v>
       </c>
       <c r="H7" t="n">
-        <v>91.2</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1616,7 +1618,7 @@
         <v>25.3</v>
       </c>
       <c r="H8" t="n">
-        <v>69.8</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1660,7 +1662,7 @@
         <v>12.2</v>
       </c>
       <c r="H10" t="n">
-        <v>57.9</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="11">
@@ -1682,7 +1684,7 @@
         <v>40.4</v>
       </c>
       <c r="H11" t="n">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="12">
@@ -1702,7 +1704,7 @@
         <v>56.2</v>
       </c>
       <c r="H12" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="13">
@@ -1727,7 +1729,9 @@
       <c r="G13" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>88.40000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1746,7 +1750,7 @@
         <v>52.3</v>
       </c>
       <c r="H14" t="n">
-        <v>62</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="15">
@@ -1770,7 +1774,7 @@
         <v>35.7</v>
       </c>
       <c r="H15" t="n">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="16">
@@ -1786,7 +1790,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1997,16 +2001,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>898.8</v>
+        <v>904.1</v>
       </c>
       <c r="D8" t="n">
-        <v>56.3</v>
+        <v>57.6</v>
       </c>
       <c r="E8" t="n">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="F8" t="n">
         <v>975</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>67.5</v>
       </c>
       <c r="E4" t="n">
-        <v>67.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="F4" t="n">
         <v>89.09999999999999</v>
@@ -564,10 +564,10 @@
         <v>43.9</v>
       </c>
       <c r="H4" t="n">
-        <v>490.3</v>
+        <v>540.3</v>
       </c>
       <c r="I4" t="n">
-        <v>854.7</v>
+        <v>851.9</v>
       </c>
       <c r="J4" t="n">
         <v>975</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,11 @@
           <t>9/8/26</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1064,6 +1069,7 @@
       <c r="H2" t="n">
         <v>952</v>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1092,6 +1098,7 @@
       <c r="H3" t="n">
         <v>973</v>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1114,6 +1121,7 @@
       <c r="H4" t="n">
         <v>860</v>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1134,6 +1142,7 @@
       <c r="H5" t="n">
         <v>894</v>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1160,6 +1169,7 @@
       <c r="H6" t="n">
         <v>960</v>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1187,6 +1197,9 @@
       </c>
       <c r="H7" t="n">
         <v>975</v>
+      </c>
+      <c r="I7" t="n">
+        <v>832</v>
       </c>
     </row>
     <row r="8">
@@ -1214,6 +1227,7 @@
       <c r="H8" t="n">
         <v>928</v>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1230,6 +1244,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1258,6 +1273,7 @@
       <c r="H10" t="n">
         <v>910</v>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1280,6 +1296,7 @@
       <c r="H11" t="n">
         <v>832</v>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1300,6 +1317,7 @@
       <c r="H12" t="n">
         <v>849</v>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1326,6 +1344,7 @@
       <c r="H13" t="n">
         <v>973</v>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1346,6 +1365,7 @@
       <c r="H14" t="n">
         <v>916</v>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1370,6 +1390,7 @@
       <c r="H15" t="n">
         <v>832</v>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1386,6 +1407,7 @@
       <c r="H16" t="n">
         <v>803</v>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1398,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1464,11 @@
           <t>9/8/26</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1470,6 +1497,7 @@
       <c r="H2" t="n">
         <v>79.7</v>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1498,6 +1526,7 @@
       <c r="H3" t="n">
         <v>88.40000000000001</v>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1520,6 +1549,7 @@
       <c r="H4" t="n">
         <v>22.2</v>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1540,6 +1570,7 @@
       <c r="H5" t="n">
         <v>43.1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1566,6 +1597,7 @@
       <c r="H6" t="n">
         <v>83.40000000000001</v>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1593,6 +1625,9 @@
       </c>
       <c r="H7" t="n">
         <v>89.09999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1620,6 +1655,7 @@
       <c r="H8" t="n">
         <v>66.09999999999999</v>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1636,6 +1672,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1664,6 +1701,7 @@
       <c r="H10" t="n">
         <v>54.1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1686,6 +1724,7 @@
       <c r="H11" t="n">
         <v>10.5</v>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1706,6 +1745,7 @@
       <c r="H12" t="n">
         <v>16.9</v>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1732,6 +1772,7 @@
       <c r="H13" t="n">
         <v>88.40000000000001</v>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1752,6 +1793,7 @@
       <c r="H14" t="n">
         <v>58.2</v>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1776,6 +1818,7 @@
       <c r="H15" t="n">
         <v>10.5</v>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1792,6 +1835,7 @@
       <c r="H16" t="n">
         <v>4</v>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1804,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,6 +2063,31 @@
         <v>803</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>9/9/26</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>832</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>832</v>
+      </c>
+      <c r="F9" t="n">
+        <v>832</v>
+      </c>
+      <c r="G9" t="n">
+        <v>832</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>67.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>66.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>89.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>43.9</v>
+        <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>540.3</v>
+        <v>393.5</v>
       </c>
       <c r="I4" t="n">
-        <v>851.9</v>
+        <v>823.7</v>
       </c>
       <c r="J4" t="n">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>65.59999999999999</v>
+        <v>63.3</v>
       </c>
       <c r="E5" t="n">
-        <v>76.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F5" t="n">
-        <v>93.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>11.4</v>
+        <v>15.9</v>
       </c>
       <c r="H5" t="n">
-        <v>393.5</v>
+        <v>506.2</v>
       </c>
       <c r="I5" t="n">
-        <v>823.7</v>
+        <v>851.9</v>
       </c>
       <c r="J5" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6">
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>53.8</v>
+        <v>58.1</v>
       </c>
       <c r="E8" t="n">
-        <v>59</v>
+        <v>61.9</v>
       </c>
       <c r="F8" t="n">
         <v>87.90000000000001</v>
@@ -700,10 +700,10 @@
         <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>322.7</v>
+        <v>406.8</v>
       </c>
       <c r="I8" t="n">
-        <v>812.3</v>
+        <v>829.7</v>
       </c>
       <c r="J8" t="n">
         <v>960</v>
@@ -1169,7 +1169,9 @@
       <c r="H6" t="n">
         <v>960</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>934</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1597,7 +1599,9 @@
       <c r="H6" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1627,7 +1631,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="8">
@@ -2070,19 +2074,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>832</v>
+        <v>883</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>832</v>
+        <v>883</v>
       </c>
       <c r="F9" t="n">
-        <v>832</v>
+        <v>934</v>
       </c>
       <c r="G9" t="n">
         <v>832</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>63.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>15.9</v>
+        <v>26.2</v>
       </c>
       <c r="H5" t="n">
-        <v>506.2</v>
+        <v>516.5</v>
       </c>
       <c r="I5" t="n">
         <v>851.9</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>60.1</v>
+        <v>59.3</v>
       </c>
       <c r="E6" t="n">
-        <v>58.4</v>
+        <v>61.9</v>
       </c>
       <c r="F6" t="n">
-        <v>90.90000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>25.3</v>
+        <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>360.7</v>
+        <v>414.8</v>
       </c>
       <c r="I6" t="n">
-        <v>829.2</v>
+        <v>829.7</v>
       </c>
       <c r="J6" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>58.1</v>
+        <v>54.7</v>
       </c>
       <c r="E8" t="n">
-        <v>61.9</v>
+        <v>50.7</v>
       </c>
       <c r="F8" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5</v>
+        <v>21.9</v>
       </c>
       <c r="H8" t="n">
-        <v>406.8</v>
+        <v>382.6</v>
       </c>
       <c r="I8" t="n">
-        <v>829.7</v>
+        <v>828.6</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -1229,7 +1229,9 @@
       <c r="H8" t="n">
         <v>928</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>825</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1600,7 +1602,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>84.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1631,7 +1633,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>15.9</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="8">
@@ -1659,7 +1661,9 @@
       <c r="H8" t="n">
         <v>66.09999999999999</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2074,22 +2078,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>883</v>
+        <v>863.7</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>49.8</v>
       </c>
       <c r="E9" t="n">
-        <v>883</v>
+        <v>832</v>
       </c>
       <c r="F9" t="n">
         <v>934</v>
       </c>
       <c r="G9" t="n">
-        <v>832</v>
+        <v>825</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>72.7</v>
       </c>
       <c r="E3" t="n">
-        <v>79.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>95.3</v>
@@ -530,13 +530,13 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>490.2</v>
+        <v>581.8</v>
       </c>
       <c r="I3" t="n">
-        <v>851.9</v>
+        <v>869.2</v>
       </c>
       <c r="J3" t="n">
-        <v>967</v>
+        <v>991</v>
       </c>
     </row>
     <row r="4">
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>64.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>26.2</v>
+        <v>13.6</v>
       </c>
       <c r="H5" t="n">
-        <v>516.5</v>
+        <v>503.9</v>
       </c>
       <c r="I5" t="n">
         <v>851.9</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>59.3</v>
+        <v>58.4</v>
       </c>
       <c r="E6" t="n">
-        <v>61.9</v>
+        <v>58.2</v>
       </c>
       <c r="F6" t="n">
-        <v>92.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5</v>
+        <v>52.3</v>
       </c>
       <c r="H6" t="n">
-        <v>414.8</v>
+        <v>175.2</v>
       </c>
       <c r="I6" t="n">
-        <v>829.7</v>
+        <v>828.3</v>
       </c>
       <c r="J6" t="n">
-        <v>960</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>58.4</v>
+        <v>55.9</v>
       </c>
       <c r="E7" t="n">
-        <v>58.2</v>
+        <v>61.9</v>
       </c>
       <c r="F7" t="n">
-        <v>64.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>52.3</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>391.6</v>
       </c>
       <c r="I7" t="n">
-        <v>828.3</v>
+        <v>829.7</v>
       </c>
       <c r="J7" t="n">
-        <v>916</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="E8" t="n">
-        <v>50.7</v>
+        <v>54.5</v>
       </c>
       <c r="F8" t="n">
-        <v>90.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>382.6</v>
+        <v>272.8</v>
       </c>
       <c r="I8" t="n">
-        <v>828.6</v>
+        <v>848.6</v>
       </c>
       <c r="J8" t="n">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>51.5</v>
+        <v>53.2</v>
       </c>
       <c r="E9" t="n">
-        <v>51.8</v>
+        <v>50.7</v>
       </c>
       <c r="F9" t="n">
-        <v>80.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>22.2</v>
+        <v>11.4</v>
       </c>
       <c r="H9" t="n">
-        <v>206.1</v>
+        <v>372.1</v>
       </c>
       <c r="I9" t="n">
-        <v>828.2</v>
+        <v>828.6</v>
       </c>
       <c r="J9" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="10">
@@ -1069,7 +1069,9 @@
       <c r="H2" t="n">
         <v>952</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>991</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1121,7 +1123,9 @@
       <c r="H4" t="n">
         <v>860</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>930</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1501,7 +1505,9 @@
       <c r="H2" t="n">
         <v>79.7</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>91.59999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1553,7 +1559,9 @@
       <c r="H4" t="n">
         <v>22.2</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>66.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1602,7 +1610,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>92.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1633,7 +1641,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>26.2</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="8">
@@ -1662,7 +1670,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>21.9</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="9">
@@ -2078,19 +2086,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>863.7</v>
+        <v>902.4</v>
       </c>
       <c r="D9" t="n">
-        <v>49.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>832</v>
+        <v>930</v>
       </c>
       <c r="F9" t="n">
-        <v>934</v>
+        <v>991</v>
       </c>
       <c r="G9" t="n">
         <v>825</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>78.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>86.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,13 +496,13 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>547.6</v>
+        <v>636.5</v>
       </c>
       <c r="I2" t="n">
-        <v>879.9</v>
+        <v>894.5</v>
       </c>
       <c r="J2" t="n">
-        <v>973</v>
+        <v>997</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +518,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>72.7</v>
+        <v>72.2</v>
       </c>
       <c r="E3" t="n">
         <v>83.40000000000001</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>581.8</v>
+        <v>577.2</v>
       </c>
       <c r="I3" t="n">
         <v>869.2</v>
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>62.1</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>6.5</v>
       </c>
       <c r="H5" t="n">
-        <v>503.9</v>
+        <v>496.8</v>
       </c>
       <c r="I5" t="n">
         <v>851.9</v>
@@ -654,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>55.9</v>
+        <v>54.3</v>
       </c>
       <c r="E7" t="n">
-        <v>61.9</v>
+        <v>57.1</v>
       </c>
       <c r="F7" t="n">
         <v>87.90000000000001</v>
@@ -666,7 +666,7 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>391.6</v>
+        <v>379.8</v>
       </c>
       <c r="I7" t="n">
         <v>829.7</v>
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>54.6</v>
+        <v>52.3</v>
       </c>
       <c r="E8" t="n">
-        <v>54.5</v>
+        <v>50.7</v>
       </c>
       <c r="F8" t="n">
-        <v>80.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>5.2</v>
       </c>
       <c r="H8" t="n">
-        <v>272.8</v>
+        <v>365.9</v>
       </c>
       <c r="I8" t="n">
-        <v>848.6</v>
+        <v>828.6</v>
       </c>
       <c r="J8" t="n">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>53.2</v>
+        <v>52.1</v>
       </c>
       <c r="E9" t="n">
-        <v>50.7</v>
+        <v>54.5</v>
       </c>
       <c r="F9" t="n">
-        <v>90.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>11.4</v>
+        <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>372.1</v>
+        <v>260.6</v>
       </c>
       <c r="I9" t="n">
-        <v>828.6</v>
+        <v>848.6</v>
       </c>
       <c r="J9" t="n">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>45.3</v>
+        <v>45.8</v>
       </c>
       <c r="E10" t="n">
-        <v>56.2</v>
+        <v>54.4</v>
       </c>
       <c r="F10" t="n">
-        <v>62.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>16.9</v>
+        <v>5.7</v>
       </c>
       <c r="H10" t="n">
-        <v>135.9</v>
+        <v>183.3</v>
       </c>
       <c r="I10" t="n">
-        <v>807</v>
+        <v>843.8</v>
       </c>
       <c r="J10" t="n">
-        <v>849</v>
+        <v>953</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>38.1</v>
+        <v>45.3</v>
       </c>
       <c r="E11" t="n">
-        <v>43.1</v>
+        <v>56.2</v>
       </c>
       <c r="F11" t="n">
-        <v>65.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7</v>
+        <v>16.9</v>
       </c>
       <c r="H11" t="n">
-        <v>114.4</v>
+        <v>135.9</v>
       </c>
       <c r="I11" t="n">
-        <v>807.3</v>
+        <v>807</v>
       </c>
       <c r="J11" t="n">
-        <v>894</v>
+        <v>849</v>
       </c>
     </row>
     <row r="12">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>31.5</v>
+        <v>33.8</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>36.6</v>
       </c>
       <c r="F12" t="n">
         <v>54.1</v>
@@ -836,13 +836,13 @@
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>220.2</v>
+        <v>270.7</v>
       </c>
       <c r="I12" t="n">
-        <v>746.9</v>
+        <v>769</v>
       </c>
       <c r="J12" t="n">
-        <v>910</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13">
@@ -1100,7 +1100,9 @@
       <c r="H3" t="n">
         <v>973</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>997</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1146,7 +1148,9 @@
       <c r="H5" t="n">
         <v>894</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>953</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1281,7 +1285,9 @@
       <c r="H10" t="n">
         <v>910</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>924</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1506,7 +1512,7 @@
         <v>79.7</v>
       </c>
       <c r="I2" t="n">
-        <v>91.59999999999999</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -1536,7 +1542,9 @@
       <c r="H3" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>88.90000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1560,7 +1568,7 @@
         <v>22.2</v>
       </c>
       <c r="I4" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="5">
@@ -1582,7 +1590,9 @@
       <c r="H5" t="n">
         <v>43.1</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>68.90000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1610,7 +1620,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>68.90000000000001</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="7">
@@ -1641,7 +1651,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>13.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -1670,7 +1680,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>11.4</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="9">
@@ -1717,7 +1727,9 @@
       <c r="H10" t="n">
         <v>54.1</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>50.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2086,19 +2098,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>902.4</v>
+        <v>923.2</v>
       </c>
       <c r="D9" t="n">
-        <v>64.09999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="E9" t="n">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="F9" t="n">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="G9" t="n">
         <v>825</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>79.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>87.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>636.5</v>
+        <v>632.5</v>
       </c>
       <c r="I2" t="n">
         <v>894.5</v>
@@ -518,10 +518,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>72.2</v>
+        <v>71.7</v>
       </c>
       <c r="E3" t="n">
-        <v>83.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>95.3</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>577.2</v>
+        <v>573.7</v>
       </c>
       <c r="I3" t="n">
         <v>869.2</v>
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>62.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5</v>
+        <v>26.4</v>
       </c>
       <c r="H5" t="n">
-        <v>496.8</v>
+        <v>516.7</v>
       </c>
       <c r="I5" t="n">
         <v>851.9</v>
@@ -654,10 +654,10 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>54.3</v>
+        <v>55.5</v>
       </c>
       <c r="E7" t="n">
-        <v>57.1</v>
+        <v>61.9</v>
       </c>
       <c r="F7" t="n">
         <v>87.90000000000001</v>
@@ -666,7 +666,7 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>379.8</v>
+        <v>388.2</v>
       </c>
       <c r="I7" t="n">
         <v>829.7</v>
@@ -688,7 +688,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>52.3</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
         <v>50.7</v>
@@ -697,10 +697,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2</v>
+        <v>24.1</v>
       </c>
       <c r="H8" t="n">
-        <v>365.9</v>
+        <v>384.8</v>
       </c>
       <c r="I8" t="n">
         <v>828.6</v>
@@ -722,7 +722,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>52.1</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
         <v>54.5</v>
@@ -734,7 +734,7 @@
         <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>260.6</v>
+        <v>270.1</v>
       </c>
       <c r="I9" t="n">
         <v>848.6</v>
@@ -756,19 +756,19 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>45.8</v>
+        <v>46.7</v>
       </c>
       <c r="E10" t="n">
         <v>54.4</v>
       </c>
       <c r="F10" t="n">
-        <v>68.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G10" t="n">
         <v>5.7</v>
       </c>
       <c r="H10" t="n">
-        <v>183.3</v>
+        <v>186.6</v>
       </c>
       <c r="I10" t="n">
         <v>843.8</v>
@@ -824,19 +824,19 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>33.8</v>
+        <v>35.2</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>54.1</v>
+        <v>61.7</v>
       </c>
       <c r="G12" t="n">
         <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>270.7</v>
+        <v>281.9</v>
       </c>
       <c r="I12" t="n">
         <v>769</v>
@@ -889,25 +889,25 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="F14" t="n">
         <v>35.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>59.9</v>
+        <v>60.9</v>
       </c>
       <c r="I14" t="n">
-        <v>667.6</v>
+        <v>667.2</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1404,7 +1404,9 @@
       <c r="H15" t="n">
         <v>832</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>665</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1512,7 +1514,7 @@
         <v>79.7</v>
       </c>
       <c r="I2" t="n">
-        <v>87</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="3">
@@ -1543,7 +1545,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>88.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1568,7 +1570,7 @@
         <v>22.2</v>
       </c>
       <c r="I4" t="n">
-        <v>54.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -1591,7 +1593,7 @@
         <v>43.1</v>
       </c>
       <c r="I5" t="n">
-        <v>68.90000000000001</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="6">
@@ -1620,7 +1622,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>57.1</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="7">
@@ -1651,7 +1653,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>6.5</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="8">
@@ -1680,7 +1682,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>5.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="9">
@@ -1728,7 +1730,7 @@
         <v>54.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50.5</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="11">
@@ -1846,7 +1848,9 @@
       <c r="H15" t="n">
         <v>10.5</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2098,22 +2102,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>923.2</v>
+        <v>894.6</v>
       </c>
       <c r="D9" t="n">
-        <v>60.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="F9" t="n">
         <v>997</v>
       </c>
       <c r="G9" t="n">
-        <v>825</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -487,7 +487,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>85.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>632.5</v>
+        <v>633.1</v>
       </c>
       <c r="I2" t="n">
         <v>894.5</v>
@@ -518,10 +518,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="E3" t="n">
-        <v>81.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
         <v>95.3</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>573.7</v>
+        <v>574.5</v>
       </c>
       <c r="I3" t="n">
         <v>869.2</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>65.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="E4" t="n">
-        <v>76.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F4" t="n">
-        <v>93.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>11.4</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
-        <v>393.5</v>
+        <v>528.3</v>
       </c>
       <c r="I4" t="n">
-        <v>823.7</v>
+        <v>851.9</v>
       </c>
       <c r="J4" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>64.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>66.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>89.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>26.4</v>
+        <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>516.7</v>
+        <v>393.5</v>
       </c>
       <c r="I5" t="n">
-        <v>851.9</v>
+        <v>823.7</v>
       </c>
       <c r="J5" t="n">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="6">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>55.5</v>
+        <v>56.6</v>
       </c>
       <c r="E7" t="n">
-        <v>61.9</v>
+        <v>50.7</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>25.3</v>
       </c>
       <c r="H7" t="n">
-        <v>388.2</v>
+        <v>396.5</v>
       </c>
       <c r="I7" t="n">
-        <v>829.7</v>
+        <v>828.6</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>56.2</v>
       </c>
       <c r="E8" t="n">
-        <v>50.7</v>
+        <v>61.9</v>
       </c>
       <c r="F8" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>24.1</v>
+        <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>384.8</v>
+        <v>393.1</v>
       </c>
       <c r="I8" t="n">
-        <v>828.6</v>
+        <v>829.7</v>
       </c>
       <c r="J8" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>54</v>
+        <v>55.1</v>
       </c>
       <c r="E9" t="n">
         <v>54.5</v>
@@ -734,7 +734,7 @@
         <v>22.2</v>
       </c>
       <c r="H9" t="n">
-        <v>270.1</v>
+        <v>275.3</v>
       </c>
       <c r="I9" t="n">
         <v>848.6</v>
@@ -756,19 +756,19 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>46.7</v>
+        <v>47.5</v>
       </c>
       <c r="E10" t="n">
         <v>54.4</v>
       </c>
       <c r="F10" t="n">
-        <v>72.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>5.7</v>
       </c>
       <c r="H10" t="n">
-        <v>186.6</v>
+        <v>190</v>
       </c>
       <c r="I10" t="n">
         <v>843.8</v>
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>45.3</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
-        <v>56.2</v>
+        <v>36.6</v>
       </c>
       <c r="F11" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G11" t="n">
-        <v>16.9</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>135.9</v>
+        <v>287.7</v>
       </c>
       <c r="I11" t="n">
-        <v>807</v>
+        <v>769</v>
       </c>
       <c r="J11" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>61.7</v>
+        <v>62.8</v>
       </c>
       <c r="G12" t="n">
-        <v>8.4</v>
+        <v>2.9</v>
       </c>
       <c r="H12" t="n">
-        <v>281.9</v>
+        <v>138.8</v>
       </c>
       <c r="I12" t="n">
-        <v>769</v>
+        <v>765.2</v>
       </c>
       <c r="J12" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13">
@@ -892,7 +892,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="E14" t="n">
         <v>5.9</v>
@@ -901,10 +901,10 @@
         <v>35.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>60.9</v>
+        <v>64.5</v>
       </c>
       <c r="I14" t="n">
         <v>667.2</v>
@@ -1331,7 +1331,9 @@
       <c r="H12" t="n">
         <v>849</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>640</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1514,7 +1516,7 @@
         <v>79.7</v>
       </c>
       <c r="I2" t="n">
-        <v>83.5</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="3">
@@ -1545,7 +1547,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>84.90000000000001</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="4">
@@ -1570,7 +1572,7 @@
         <v>22.2</v>
       </c>
       <c r="I4" t="n">
-        <v>64</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="5">
@@ -1593,7 +1595,7 @@
         <v>43.1</v>
       </c>
       <c r="I5" t="n">
-        <v>72.2</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1622,7 +1624,7 @@
         <v>83.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>65.5</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1653,7 +1655,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>26.4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -1682,7 +1684,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>24.1</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="9">
@@ -1730,7 +1732,7 @@
         <v>54.1</v>
       </c>
       <c r="I10" t="n">
-        <v>61.7</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="11">
@@ -1775,7 +1777,9 @@
       <c r="H12" t="n">
         <v>16.9</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1849,7 +1853,7 @@
         <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="16">
@@ -2102,22 +2106,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>894.6</v>
+        <v>869.1</v>
       </c>
       <c r="D9" t="n">
-        <v>99.09999999999999</v>
+        <v>121.1</v>
       </c>
       <c r="E9" t="n">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="F9" t="n">
         <v>997</v>
       </c>
       <c r="G9" t="n">
-        <v>665</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>633.1</v>
+        <v>633</v>
       </c>
       <c r="I2" t="n">
         <v>894.5</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>66</v>
+        <v>68.3</v>
       </c>
       <c r="E4" t="n">
-        <v>66.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>89.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>528.3</v>
+        <v>477.8</v>
       </c>
       <c r="I4" t="n">
-        <v>851.9</v>
+        <v>847.6</v>
       </c>
       <c r="J4" t="n">
-        <v>975</v>
+        <v>991</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>65.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>76.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F5" t="n">
-        <v>93.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>11.4</v>
+        <v>38.2</v>
       </c>
       <c r="H5" t="n">
-        <v>393.5</v>
+        <v>528.5</v>
       </c>
       <c r="I5" t="n">
-        <v>823.7</v>
+        <v>851.9</v>
       </c>
       <c r="J5" t="n">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>58.4</v>
+        <v>56.7</v>
       </c>
       <c r="E6" t="n">
-        <v>58.2</v>
+        <v>50.7</v>
       </c>
       <c r="F6" t="n">
-        <v>64.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>52.3</v>
+        <v>25.3</v>
       </c>
       <c r="H6" t="n">
-        <v>175.2</v>
+        <v>396.7</v>
       </c>
       <c r="I6" t="n">
-        <v>828.3</v>
+        <v>828.6</v>
       </c>
       <c r="J6" t="n">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E7" t="n">
-        <v>50.7</v>
+        <v>61.9</v>
       </c>
       <c r="F7" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>25.3</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>396.5</v>
+        <v>393.1</v>
       </c>
       <c r="I7" t="n">
-        <v>828.6</v>
+        <v>829.7</v>
       </c>
       <c r="J7" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>56.2</v>
+        <v>55.1</v>
       </c>
       <c r="E8" t="n">
-        <v>61.9</v>
+        <v>54.5</v>
       </c>
       <c r="F8" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>393.1</v>
+        <v>275.4</v>
       </c>
       <c r="I8" t="n">
-        <v>829.7</v>
+        <v>848.6</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>55.1</v>
+        <v>47.5</v>
       </c>
       <c r="E9" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="F9" t="n">
-        <v>80.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>22.2</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>275.3</v>
+        <v>190</v>
       </c>
       <c r="I9" t="n">
-        <v>848.6</v>
+        <v>843.8</v>
       </c>
       <c r="J9" t="n">
-        <v>930</v>
+        <v>953</v>
       </c>
     </row>
     <row r="10">
@@ -749,7 +749,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -759,22 +759,22 @@
         <v>47.5</v>
       </c>
       <c r="E10" t="n">
-        <v>54.4</v>
+        <v>55.2</v>
       </c>
       <c r="F10" t="n">
-        <v>75.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G10" t="n">
-        <v>5.7</v>
+        <v>14.9</v>
       </c>
       <c r="H10" t="n">
-        <v>190</v>
+        <v>190.1</v>
       </c>
       <c r="I10" t="n">
-        <v>843.8</v>
+        <v>806.8</v>
       </c>
       <c r="J10" t="n">
-        <v>953</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11">
@@ -833,10 +833,10 @@
         <v>62.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>138.8</v>
+        <v>138.9</v>
       </c>
       <c r="I12" t="n">
         <v>765.2</v>
@@ -904,7 +904,7 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>667.2</v>
@@ -1360,7 +1360,9 @@
       <c r="H13" t="n">
         <v>973</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>991</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1381,7 +1383,9 @@
       <c r="H14" t="n">
         <v>916</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>742</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1547,7 +1551,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1572,7 +1576,7 @@
         <v>22.2</v>
       </c>
       <c r="I4" t="n">
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="5">
@@ -1655,7 +1659,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="8">
@@ -1684,7 +1688,7 @@
         <v>66.09999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -1778,7 +1782,7 @@
         <v>16.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1806,7 +1810,9 @@
       <c r="H13" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>84.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1827,7 +1833,9 @@
       <c r="H14" t="n">
         <v>58.2</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1853,7 +1861,7 @@
         <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="16">
@@ -2106,13 +2114,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>869.1</v>
+        <v>868.7</v>
       </c>
       <c r="D9" t="n">
-        <v>121.1</v>
+        <v>121.7</v>
       </c>
       <c r="E9" t="n">
         <v>927</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -583,25 +583,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>66.09999999999999</v>
+        <v>60.5</v>
       </c>
       <c r="E5" t="n">
-        <v>66.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>38.2</v>
+        <v>15.9</v>
       </c>
       <c r="H5" t="n">
-        <v>528.5</v>
+        <v>544.4</v>
       </c>
       <c r="I5" t="n">
-        <v>851.9</v>
+        <v>826</v>
       </c>
       <c r="J5" t="n">
         <v>975</v>
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>56.7</v>
+        <v>60.1</v>
       </c>
       <c r="E6" t="n">
-        <v>50.7</v>
+        <v>58.4</v>
       </c>
       <c r="F6" t="n">
         <v>90.90000000000001</v>
@@ -632,10 +632,10 @@
         <v>25.3</v>
       </c>
       <c r="H6" t="n">
-        <v>396.7</v>
+        <v>480.8</v>
       </c>
       <c r="I6" t="n">
-        <v>828.6</v>
+        <v>802.6</v>
       </c>
       <c r="J6" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1041,6 +1041,11 @@
           <t>9/9/26</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>9/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1072,6 +1077,7 @@
       <c r="I2" t="n">
         <v>991</v>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1103,6 +1109,7 @@
       <c r="I3" t="n">
         <v>997</v>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1128,6 +1135,7 @@
       <c r="I4" t="n">
         <v>930</v>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1151,6 +1159,7 @@
       <c r="I5" t="n">
         <v>953</v>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1180,6 +1189,7 @@
       <c r="I6" t="n">
         <v>934</v>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1210,6 +1220,9 @@
       </c>
       <c r="I7" t="n">
         <v>832</v>
+      </c>
+      <c r="J7" t="n">
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -1239,6 +1252,9 @@
       </c>
       <c r="I8" t="n">
         <v>825</v>
+      </c>
+      <c r="J8" t="n">
+        <v>621</v>
       </c>
     </row>
     <row r="9">
@@ -1257,6 +1273,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1288,6 +1305,7 @@
       <c r="I10" t="n">
         <v>924</v>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1311,6 +1329,7 @@
         <v>832</v>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1334,6 +1353,7 @@
       <c r="I12" t="n">
         <v>640</v>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1363,6 +1383,7 @@
       <c r="I13" t="n">
         <v>991</v>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1386,6 +1407,7 @@
       <c r="I14" t="n">
         <v>742</v>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1413,6 +1435,7 @@
       <c r="I15" t="n">
         <v>665</v>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1430,6 +1453,7 @@
         <v>803</v>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1442,7 +1466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,6 +1515,11 @@
           <t>9/9/26</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>9/10/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1522,6 +1551,7 @@
       <c r="I2" t="n">
         <v>84.3</v>
       </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1553,6 +1583,7 @@
       <c r="I3" t="n">
         <v>85.40000000000001</v>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1578,6 +1609,7 @@
       <c r="I4" t="n">
         <v>69.3</v>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1601,6 +1633,7 @@
       <c r="I5" t="n">
         <v>75.59999999999999</v>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1630,6 +1663,7 @@
       <c r="I6" t="n">
         <v>70.40000000000001</v>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1660,6 +1694,9 @@
       </c>
       <c r="I7" t="n">
         <v>38.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15.9</v>
       </c>
     </row>
     <row r="8">
@@ -1689,6 +1726,9 @@
       </c>
       <c r="I8" t="n">
         <v>36</v>
+      </c>
+      <c r="J8" t="n">
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1707,6 +1747,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1738,6 +1779,7 @@
       <c r="I10" t="n">
         <v>67.5</v>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1761,6 +1803,7 @@
         <v>10.5</v>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1784,6 +1827,7 @@
       <c r="I12" t="n">
         <v>3</v>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1813,6 +1857,7 @@
       <c r="I13" t="n">
         <v>84.3</v>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1836,6 +1881,7 @@
       <c r="I14" t="n">
         <v>14.9</v>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1863,6 +1909,7 @@
       <c r="I15" t="n">
         <v>4.7</v>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1880,6 +1927,7 @@
         <v>4</v>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1892,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,6 +2180,31 @@
         <v>640</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9/10/26</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>620</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>620</v>
+      </c>
+      <c r="F10" t="n">
+        <v>621</v>
+      </c>
+      <c r="G10" t="n">
+        <v>619</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>60.5</v>
+        <v>60.9</v>
       </c>
       <c r="E5" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F5" t="n">
-        <v>89.09999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="H5" t="n">
-        <v>544.4</v>
+        <v>487.5</v>
       </c>
       <c r="I5" t="n">
-        <v>826</v>
+        <v>814.1</v>
       </c>
       <c r="J5" t="n">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>60.1</v>
+        <v>60.8</v>
       </c>
       <c r="E6" t="n">
-        <v>58.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>25.3</v>
+        <v>18.8</v>
       </c>
       <c r="H6" t="n">
-        <v>480.8</v>
+        <v>547.3</v>
       </c>
       <c r="I6" t="n">
-        <v>802.6</v>
+        <v>826</v>
       </c>
       <c r="J6" t="n">
-        <v>928</v>
+        <v>975</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>56.2</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
-        <v>61.9</v>
+        <v>54.7</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>393.1</v>
+        <v>330.3</v>
       </c>
       <c r="I7" t="n">
-        <v>829.7</v>
+        <v>816.2</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>55.1</v>
+        <v>52.1</v>
       </c>
       <c r="E8" t="n">
-        <v>54.5</v>
+        <v>44.8</v>
       </c>
       <c r="F8" t="n">
-        <v>80.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>20.4</v>
       </c>
       <c r="H8" t="n">
-        <v>275.4</v>
+        <v>417.1</v>
       </c>
       <c r="I8" t="n">
-        <v>848.6</v>
+        <v>802.6</v>
       </c>
       <c r="J8" t="n">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -1135,7 +1135,9 @@
       <c r="I4" t="n">
         <v>930</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>654</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1189,7 +1191,9 @@
       <c r="I6" t="n">
         <v>934</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>705</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1609,7 +1613,9 @@
       <c r="I4" t="n">
         <v>69.3</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>54.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1663,7 +1669,9 @@
       <c r="I6" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>94.40000000000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1696,7 +1704,7 @@
         <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>15.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="8">
@@ -1728,7 +1736,7 @@
         <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>84.09999999999999</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="9">
@@ -2187,19 +2195,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>620</v>
+        <v>649.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>34.8</v>
       </c>
       <c r="E10" t="n">
-        <v>620</v>
+        <v>637.5</v>
       </c>
       <c r="F10" t="n">
-        <v>621</v>
+        <v>705</v>
       </c>
       <c r="G10" t="n">
         <v>619</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>86.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,10 +496,10 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>633</v>
+        <v>712.3</v>
       </c>
       <c r="I2" t="n">
-        <v>894.5</v>
+        <v>887.2</v>
       </c>
       <c r="J2" t="n">
         <v>997</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>84.3</v>
       </c>
       <c r="F3" t="n">
         <v>95.3</v>
@@ -530,10 +530,10 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>574.5</v>
+        <v>668</v>
       </c>
       <c r="I3" t="n">
-        <v>869.2</v>
+        <v>873.2</v>
       </c>
       <c r="J3" t="n">
         <v>991</v>
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>60.9</v>
+        <v>60.2</v>
       </c>
       <c r="E5" t="n">
-        <v>66.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>94.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>487.5</v>
+        <v>542</v>
       </c>
       <c r="I5" t="n">
-        <v>814.1</v>
+        <v>826</v>
       </c>
       <c r="J5" t="n">
-        <v>960</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>60.8</v>
+        <v>53.8</v>
       </c>
       <c r="E6" t="n">
-        <v>65.40000000000001</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>89.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>18.8</v>
+        <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>547.3</v>
+        <v>430.6</v>
       </c>
       <c r="I6" t="n">
-        <v>826</v>
+        <v>814.1</v>
       </c>
       <c r="J6" t="n">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>51.3</v>
       </c>
       <c r="E7" t="n">
-        <v>54.7</v>
+        <v>44.8</v>
       </c>
       <c r="F7" t="n">
-        <v>80.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>22.2</v>
+        <v>13.9</v>
       </c>
       <c r="H7" t="n">
-        <v>330.3</v>
+        <v>410.6</v>
       </c>
       <c r="I7" t="n">
-        <v>816.2</v>
+        <v>802.6</v>
       </c>
       <c r="J7" t="n">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>52.1</v>
+        <v>49.5</v>
       </c>
       <c r="E8" t="n">
-        <v>44.8</v>
+        <v>51.8</v>
       </c>
       <c r="F8" t="n">
-        <v>90.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="H8" t="n">
-        <v>417.1</v>
+        <v>297</v>
       </c>
       <c r="I8" t="n">
-        <v>802.6</v>
+        <v>816.2</v>
       </c>
       <c r="J8" t="n">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>43.6</v>
       </c>
       <c r="E11" t="n">
-        <v>36.6</v>
+        <v>43.6</v>
       </c>
       <c r="F11" t="n">
-        <v>67.5</v>
+        <v>83.2</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>287.7</v>
+        <v>87.2</v>
       </c>
       <c r="I11" t="n">
-        <v>769</v>
+        <v>824</v>
       </c>
       <c r="J11" t="n">
-        <v>924</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>34.7</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>138.9</v>
+        <v>287.7</v>
       </c>
       <c r="I12" t="n">
-        <v>765.2</v>
+        <v>769</v>
       </c>
       <c r="J12" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>34.7</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>36.6</v>
       </c>
       <c r="F13" t="n">
-        <v>40.4</v>
+        <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>55.5</v>
+        <v>138.9</v>
       </c>
       <c r="I13" t="n">
-        <v>702</v>
+        <v>765.2</v>
       </c>
       <c r="J13" t="n">
-        <v>832</v>
+        <v>849</v>
       </c>
     </row>
     <row r="14">
@@ -885,29 +885,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>10.8</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="F14" t="n">
-        <v>35.7</v>
+        <v>40.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>64.59999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="I14" t="n">
-        <v>667.2</v>
+        <v>702</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -919,32 +919,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>johnson7</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4</v>
+        <v>10.8</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="F15" t="n">
-        <v>4.4</v>
+        <v>35.7</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>746</v>
+        <v>667.2</v>
       </c>
       <c r="J15" t="n">
-        <v>746</v>
+        <v>832</v>
       </c>
     </row>
     <row r="16">
@@ -953,32 +953,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>johnson7</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>803</v>
+        <v>746</v>
       </c>
       <c r="J16" t="n">
-        <v>803</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1077,9 @@
       <c r="I2" t="n">
         <v>991</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>905</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1109,7 +1111,9 @@
       <c r="I3" t="n">
         <v>997</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>829</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1457,7 +1461,9 @@
         <v>803</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>845</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1555,7 +1561,9 @@
       <c r="I2" t="n">
         <v>84.3</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>93.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1587,7 +1595,9 @@
       <c r="I3" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>79.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1614,7 +1624,7 @@
         <v>69.3</v>
       </c>
       <c r="J4" t="n">
-        <v>54.9</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="5">
@@ -1670,7 +1680,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>94.40000000000001</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="7">
@@ -1704,7 +1714,7 @@
         <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>18.8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="8">
@@ -1736,7 +1746,7 @@
         <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>20.4</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="9">
@@ -1935,7 +1945,9 @@
         <v>4</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>83.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2195,19 +2207,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>649.8</v>
+        <v>739.7</v>
       </c>
       <c r="D10" t="n">
-        <v>34.8</v>
+        <v>109.3</v>
       </c>
       <c r="E10" t="n">
-        <v>637.5</v>
+        <v>705</v>
       </c>
       <c r="F10" t="n">
-        <v>705</v>
+        <v>905</v>
       </c>
       <c r="G10" t="n">
         <v>619</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>79.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="E2" t="n">
         <v>85.40000000000001</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>712.3</v>
+        <v>715.3</v>
       </c>
       <c r="I2" t="n">
         <v>887.2</v>
@@ -518,7 +518,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>74.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>84.3</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>668</v>
+        <v>669.6</v>
       </c>
       <c r="I3" t="n">
         <v>873.2</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H5" t="n">
-        <v>542</v>
+        <v>542.1</v>
       </c>
       <c r="I5" t="n">
         <v>826</v>
@@ -620,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
       <c r="E6" t="n">
         <v>59</v>
@@ -632,7 +632,7 @@
         <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>430.6</v>
+        <v>432.5</v>
       </c>
       <c r="I6" t="n">
         <v>814.1</v>
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E7" t="n">
         <v>44.8</v>
@@ -663,10 +663,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="H7" t="n">
-        <v>410.6</v>
+        <v>410.8</v>
       </c>
       <c r="I7" t="n">
         <v>802.6</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E8" t="n">
         <v>51.8</v>
@@ -697,10 +697,10 @@
         <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>297</v>
+        <v>297.8</v>
       </c>
       <c r="I8" t="n">
         <v>816.2</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -725,22 +725,22 @@
         <v>47.5</v>
       </c>
       <c r="E9" t="n">
-        <v>54.4</v>
+        <v>55.2</v>
       </c>
       <c r="F9" t="n">
-        <v>75.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G9" t="n">
-        <v>5.7</v>
+        <v>14.9</v>
       </c>
       <c r="H9" t="n">
-        <v>190</v>
+        <v>190.1</v>
       </c>
       <c r="I9" t="n">
-        <v>843.8</v>
+        <v>806.8</v>
       </c>
       <c r="J9" t="n">
-        <v>953</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>45</v>
+      </c>
+      <c r="E10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" t="n">
+        <v>86</v>
+      </c>
+      <c r="G10" t="n">
         <v>4</v>
       </c>
-      <c r="D10" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="F10" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>14.9</v>
-      </c>
       <c r="H10" t="n">
-        <v>190.1</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>806.8</v>
+        <v>824</v>
       </c>
       <c r="J10" t="n">
-        <v>916</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>43.6</v>
+        <v>44.4</v>
       </c>
       <c r="E11" t="n">
-        <v>43.6</v>
+        <v>43.1</v>
       </c>
       <c r="F11" t="n">
-        <v>83.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>87.2</v>
+        <v>222.2</v>
       </c>
       <c r="I11" t="n">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="J11" t="n">
-        <v>845</v>
+        <v>953</v>
       </c>
     </row>
     <row r="12">
@@ -1165,7 +1165,9 @@
       <c r="I5" t="n">
         <v>953</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>685</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1562,7 +1564,7 @@
         <v>84.3</v>
       </c>
       <c r="J2" t="n">
-        <v>93.5</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1596,7 +1598,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>79.3</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="4">
@@ -1624,7 +1626,7 @@
         <v>69.3</v>
       </c>
       <c r="J4" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="5">
@@ -1649,7 +1651,9 @@
       <c r="I5" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>32.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1680,7 +1684,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>37.5</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="7">
@@ -1714,7 +1718,7 @@
         <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="8">
@@ -1746,7 +1750,7 @@
         <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="9">
@@ -1946,7 +1950,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>83.2</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2207,16 +2211,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>739.7</v>
+        <v>732.9</v>
       </c>
       <c r="D10" t="n">
-        <v>109.3</v>
+        <v>103.8</v>
       </c>
       <c r="E10" t="n">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="F10" t="n">
         <v>905</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
       <c r="E2" t="n">
         <v>85.40000000000001</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>715.3</v>
+        <v>717.5</v>
       </c>
       <c r="I2" t="n">
         <v>887.2</v>
@@ -518,19 +518,19 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="E3" t="n">
         <v>84.3</v>
       </c>
       <c r="F3" t="n">
-        <v>95.3</v>
+        <v>96.3</v>
       </c>
       <c r="G3" t="n">
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>669.6</v>
+        <v>670.8</v>
       </c>
       <c r="I3" t="n">
         <v>873.2</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H5" t="n">
-        <v>542.1</v>
+        <v>541.8</v>
       </c>
       <c r="I5" t="n">
         <v>826</v>
@@ -620,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="E6" t="n">
         <v>59</v>
@@ -632,7 +632,7 @@
         <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>432.5</v>
+        <v>433.6</v>
       </c>
       <c r="I6" t="n">
         <v>814.1</v>
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="E7" t="n">
         <v>44.8</v>
@@ -663,10 +663,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="H7" t="n">
-        <v>410.8</v>
+        <v>410.4</v>
       </c>
       <c r="I7" t="n">
         <v>802.6</v>
@@ -756,19 +756,19 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10" t="n">
-        <v>86</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>824</v>
@@ -790,7 +790,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="E11" t="n">
         <v>43.1</v>
@@ -802,7 +802,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>222.2</v>
+        <v>222.8</v>
       </c>
       <c r="I11" t="n">
         <v>812</v>
@@ -885,29 +885,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cartert</t>
+          <t>brhunt</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="F14" t="n">
-        <v>40.4</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>55.5</v>
+        <v>101.6</v>
       </c>
       <c r="I14" t="n">
-        <v>702</v>
+        <v>671.3</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -919,29 +919,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>brhunt</t>
+          <t>cartert</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>10.8</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="F15" t="n">
-        <v>35.7</v>
+        <v>40.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="H15" t="n">
-        <v>64.59999999999999</v>
+        <v>55.5</v>
       </c>
       <c r="I15" t="n">
-        <v>667.2</v>
+        <v>702</v>
       </c>
       <c r="J15" t="n">
         <v>832</v>
@@ -1445,7 +1445,9 @@
       <c r="I15" t="n">
         <v>665</v>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>696</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1564,7 +1566,7 @@
         <v>84.3</v>
       </c>
       <c r="J2" t="n">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="3">
@@ -1598,7 +1600,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>82.3</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="4">
@@ -1652,7 +1654,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="6">
@@ -1684,7 +1686,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>39.4</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="7">
@@ -1718,7 +1720,7 @@
         <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="8">
@@ -1750,7 +1752,7 @@
         <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="9">
@@ -1931,7 +1933,9 @@
       <c r="I15" t="n">
         <v>4.7</v>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>37</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>86</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2211,16 +2215,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>732.9</v>
+        <v>728.8</v>
       </c>
       <c r="D10" t="n">
-        <v>103.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F10" t="n">
         <v>905</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,10 +484,10 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>79.7</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
-        <v>85.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>717.5</v>
+        <v>719.9</v>
       </c>
       <c r="I2" t="n">
         <v>887.2</v>
@@ -518,19 +518,19 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E3" t="n">
         <v>84.3</v>
       </c>
       <c r="F3" t="n">
-        <v>96.3</v>
+        <v>97.2</v>
       </c>
       <c r="G3" t="n">
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>670.8</v>
+        <v>671.7</v>
       </c>
       <c r="I3" t="n">
         <v>873.2</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>68.3</v>
+        <v>62.4</v>
       </c>
       <c r="E4" t="n">
-        <v>81.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>477.8</v>
+        <v>499.4</v>
       </c>
       <c r="I4" t="n">
-        <v>847.6</v>
+        <v>822.1</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -586,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>60.2</v>
+        <v>60.4</v>
       </c>
       <c r="E5" t="n">
         <v>65.40000000000001</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>13.3</v>
+        <v>14.8</v>
       </c>
       <c r="H5" t="n">
-        <v>541.8</v>
+        <v>543.3</v>
       </c>
       <c r="I5" t="n">
         <v>826</v>
@@ -620,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>54.2</v>
+        <v>54.6</v>
       </c>
       <c r="E6" t="n">
         <v>59</v>
@@ -632,7 +632,7 @@
         <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>433.6</v>
+        <v>436.8</v>
       </c>
       <c r="I6" t="n">
         <v>814.1</v>
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="E7" t="n">
         <v>44.8</v>
@@ -663,10 +663,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7</v>
+        <v>15.3</v>
       </c>
       <c r="H7" t="n">
-        <v>410.4</v>
+        <v>412</v>
       </c>
       <c r="I7" t="n">
         <v>802.6</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
         <v>51.8</v>
@@ -700,7 +700,7 @@
         <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>297.8</v>
+        <v>300.1</v>
       </c>
       <c r="I8" t="n">
         <v>816.2</v>
@@ -756,19 +756,19 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
-        <v>88.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>92.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>824</v>
@@ -790,7 +790,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>44.6</v>
+        <v>45.2</v>
       </c>
       <c r="E11" t="n">
         <v>43.1</v>
@@ -802,7 +802,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>222.8</v>
+        <v>225.8</v>
       </c>
       <c r="I11" t="n">
         <v>812</v>
@@ -892,19 +892,19 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
         <v>6.1</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>40.1</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>101.6</v>
+        <v>104.7</v>
       </c>
       <c r="I14" t="n">
         <v>671.3</v>
@@ -1393,7 +1393,9 @@
       <c r="I13" t="n">
         <v>991</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>644</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1566,7 +1568,7 @@
         <v>84.3</v>
       </c>
       <c r="J2" t="n">
-        <v>96.3</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="3">
@@ -1600,7 +1602,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>84.5</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1628,7 +1630,7 @@
         <v>69.3</v>
       </c>
       <c r="J4" t="n">
-        <v>22.4</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="5">
@@ -1654,7 +1656,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>32.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="6">
@@ -1686,7 +1688,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>40.5</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="7">
@@ -1720,7 +1722,7 @@
         <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>13.3</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="8">
@@ -1752,7 +1754,7 @@
         <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>13.7</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="9">
@@ -1881,7 +1883,9 @@
       <c r="I13" t="n">
         <v>84.3</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1934,7 +1938,7 @@
         <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>37</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="16">
@@ -1954,7 +1958,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>88.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2215,16 +2219,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>728.8</v>
+        <v>720.3</v>
       </c>
       <c r="D10" t="n">
-        <v>98.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>696</v>
+        <v>690.5</v>
       </c>
       <c r="F10" t="n">
         <v>905</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>80.2</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>719.9</v>
+        <v>721.8</v>
       </c>
       <c r="I2" t="n">
         <v>887.2</v>
@@ -518,19 +518,19 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="E3" t="n">
         <v>84.3</v>
       </c>
       <c r="F3" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
       <c r="G3" t="n">
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>671.7</v>
+        <v>672.2</v>
       </c>
       <c r="I3" t="n">
         <v>873.2</v>
@@ -552,7 +552,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>62.4</v>
+        <v>62.8</v>
       </c>
       <c r="E4" t="n">
         <v>76.90000000000001</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>499.4</v>
+        <v>502.8</v>
       </c>
       <c r="I4" t="n">
         <v>822.1</v>
@@ -586,7 +586,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>60.4</v>
+        <v>60.7</v>
       </c>
       <c r="E5" t="n">
         <v>65.40000000000001</v>
@@ -595,10 +595,10 @@
         <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>14.8</v>
+        <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>543.3</v>
+        <v>546.1</v>
       </c>
       <c r="I5" t="n">
         <v>826</v>
@@ -620,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>54.6</v>
+        <v>55.1</v>
       </c>
       <c r="E6" t="n">
         <v>59</v>
@@ -632,7 +632,7 @@
         <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>436.8</v>
+        <v>441</v>
       </c>
       <c r="I6" t="n">
         <v>814.1</v>
@@ -654,7 +654,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>51.5</v>
+        <v>51.9</v>
       </c>
       <c r="E7" t="n">
         <v>44.8</v>
@@ -663,10 +663,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
       <c r="H7" t="n">
-        <v>412</v>
+        <v>414.8</v>
       </c>
       <c r="I7" t="n">
         <v>802.6</v>
@@ -688,7 +688,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
       <c r="E8" t="n">
         <v>51.8</v>
@@ -700,7 +700,7 @@
         <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>300.1</v>
+        <v>303.7</v>
       </c>
       <c r="I8" t="n">
         <v>816.2</v>
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meghan</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="G9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>14.9</v>
-      </c>
       <c r="H9" t="n">
-        <v>190.1</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>806.8</v>
+        <v>824</v>
       </c>
       <c r="J9" t="n">
-        <v>916</v>
+        <v>845</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" t="n">
-        <v>47</v>
+        <v>43.1</v>
       </c>
       <c r="F10" t="n">
-        <v>90.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="H10" t="n">
-        <v>94.09999999999999</v>
+        <v>229.9</v>
       </c>
       <c r="I10" t="n">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="J10" t="n">
-        <v>845</v>
+        <v>953</v>
       </c>
     </row>
     <row r="11">
@@ -783,32 +783,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>Meghan</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>45.2</v>
+        <v>41</v>
       </c>
       <c r="E11" t="n">
-        <v>43.1</v>
+        <v>52.3</v>
       </c>
       <c r="F11" t="n">
-        <v>75.59999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7</v>
+        <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>225.8</v>
+        <v>204.9</v>
       </c>
       <c r="I11" t="n">
-        <v>812</v>
+        <v>767</v>
       </c>
       <c r="J11" t="n">
-        <v>953</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12">
@@ -892,19 +892,19 @@
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="n">
         <v>6.1</v>
       </c>
       <c r="F14" t="n">
-        <v>40.1</v>
+        <v>44.3</v>
       </c>
       <c r="G14" t="n">
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>104.7</v>
+        <v>108.9</v>
       </c>
       <c r="I14" t="n">
         <v>671.3</v>
@@ -1419,7 +1419,9 @@
       <c r="I14" t="n">
         <v>742</v>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>608</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1568,7 +1570,7 @@
         <v>84.3</v>
       </c>
       <c r="J2" t="n">
-        <v>97.2</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="3">
@@ -1602,7 +1604,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>86.90000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="4">
@@ -1630,7 +1632,7 @@
         <v>69.3</v>
       </c>
       <c r="J4" t="n">
-        <v>24.7</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="5">
@@ -1656,7 +1658,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>35.8</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="6">
@@ -1688,7 +1690,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>43.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="7">
@@ -1722,7 +1724,7 @@
         <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>14.8</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="8">
@@ -1754,7 +1756,7 @@
         <v>36</v>
       </c>
       <c r="J8" t="n">
-        <v>15.3</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="9">
@@ -1884,7 +1886,7 @@
         <v>84.3</v>
       </c>
       <c r="J13" t="n">
-        <v>21.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -1909,7 +1911,9 @@
       <c r="I14" t="n">
         <v>14.9</v>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>14.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1938,7 +1942,7 @@
         <v>4.7</v>
       </c>
       <c r="J15" t="n">
-        <v>40.1</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="16">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>90.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2219,22 +2223,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>720.3</v>
+        <v>710.1</v>
       </c>
       <c r="D10" t="n">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>690.5</v>
+        <v>685</v>
       </c>
       <c r="F10" t="n">
         <v>905</v>
       </c>
       <c r="G10" t="n">
-        <v>619</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="E7" t="n">
-        <v>44.8</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
         <v>90.90000000000001</v>
@@ -666,10 +666,10 @@
         <v>18.1</v>
       </c>
       <c r="H7" t="n">
-        <v>414.8</v>
+        <v>464.8</v>
       </c>
       <c r="I7" t="n">
-        <v>802.6</v>
+        <v>809.3</v>
       </c>
       <c r="J7" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1046,11 @@
           <t>9/10/26</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>9/11/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1080,6 +1085,7 @@
       <c r="J2" t="n">
         <v>905</v>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1114,6 +1120,7 @@
       <c r="J3" t="n">
         <v>829</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1142,6 +1149,7 @@
       <c r="J4" t="n">
         <v>654</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1168,6 +1176,7 @@
       <c r="J5" t="n">
         <v>685</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1200,6 +1209,7 @@
       <c r="J6" t="n">
         <v>705</v>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1234,6 +1244,7 @@
       <c r="J7" t="n">
         <v>619</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1265,6 +1276,9 @@
       </c>
       <c r="J8" t="n">
         <v>621</v>
+      </c>
+      <c r="K8" t="n">
+        <v>863</v>
       </c>
     </row>
     <row r="9">
@@ -1284,6 +1298,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1316,6 +1331,7 @@
         <v>924</v>
       </c>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1340,6 +1356,7 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1364,6 +1381,7 @@
         <v>640</v>
       </c>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1396,6 +1414,7 @@
       <c r="J13" t="n">
         <v>644</v>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1422,6 +1441,7 @@
       <c r="J14" t="n">
         <v>608</v>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1452,6 +1472,7 @@
       <c r="J15" t="n">
         <v>696</v>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1472,6 +1493,7 @@
       <c r="J16" t="n">
         <v>845</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1484,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,6 +1560,11 @@
           <t>9/10/26</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>9/11/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1572,6 +1599,7 @@
       <c r="J2" t="n">
         <v>97.7</v>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1606,6 +1634,7 @@
       <c r="J3" t="n">
         <v>88.8</v>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1634,6 +1663,7 @@
       <c r="J4" t="n">
         <v>28.3</v>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1660,6 +1690,7 @@
       <c r="J5" t="n">
         <v>39.9</v>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1692,6 +1723,7 @@
       <c r="J6" t="n">
         <v>47.9</v>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1726,6 +1758,7 @@
       <c r="J7" t="n">
         <v>17.6</v>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1757,6 +1790,9 @@
       </c>
       <c r="J8" t="n">
         <v>18.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1776,6 +1812,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1808,6 +1845,7 @@
         <v>67.5</v>
       </c>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1832,6 +1870,7 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1856,6 +1895,7 @@
         <v>3</v>
       </c>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1888,6 +1928,7 @@
       <c r="J13" t="n">
         <v>25</v>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1914,6 +1955,7 @@
       <c r="J14" t="n">
         <v>14.8</v>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1944,6 +1986,7 @@
       <c r="J15" t="n">
         <v>44.3</v>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1964,6 +2007,7 @@
       <c r="J16" t="n">
         <v>91.59999999999999</v>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1976,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2285,31 @@
         <v>608</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9/11/26</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>863</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>863</v>
+      </c>
+      <c r="F11" t="n">
+        <v>863</v>
+      </c>
+      <c r="G11" t="n">
+        <v>863</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>55.1</v>
+        <v>55.4</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>50.7</v>
       </c>
       <c r="F6" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5</v>
+        <v>18.1</v>
       </c>
       <c r="H6" t="n">
-        <v>441</v>
+        <v>498.9</v>
       </c>
       <c r="I6" t="n">
-        <v>814.1</v>
+        <v>809.3</v>
       </c>
       <c r="J6" t="n">
-        <v>960</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>51.6</v>
+        <v>55.1</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>18.1</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>464.8</v>
+        <v>441</v>
       </c>
       <c r="I7" t="n">
-        <v>809.3</v>
+        <v>814.1</v>
       </c>
       <c r="J7" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>34.7</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
       <c r="G12" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>287.7</v>
+        <v>138.9</v>
       </c>
       <c r="I12" t="n">
-        <v>769</v>
+        <v>765.2</v>
       </c>
       <c r="J12" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>34.7</v>
+        <v>33.7</v>
       </c>
       <c r="E13" t="n">
-        <v>36.6</v>
+        <v>33</v>
       </c>
       <c r="F13" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="H13" t="n">
-        <v>138.9</v>
+        <v>303.6</v>
       </c>
       <c r="I13" t="n">
-        <v>765.2</v>
+        <v>754.9</v>
       </c>
       <c r="J13" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="14">
@@ -1331,7 +1331,9 @@
         <v>924</v>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>642</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1792,7 +1794,7 @@
         <v>18.1</v>
       </c>
       <c r="K8" t="n">
-        <v>50</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1845,7 +1847,9 @@
         <v>67.5</v>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2292,22 +2296,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>863</v>
+        <v>752.5</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>110.5</v>
       </c>
       <c r="E11" t="n">
-        <v>863</v>
+        <v>752.5</v>
       </c>
       <c r="F11" t="n">
         <v>863</v>
       </c>
       <c r="G11" t="n">
-        <v>863</v>
+        <v>642</v>
       </c>
     </row>
   </sheetData>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
       <c r="E4" t="n">
-        <v>76.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F4" t="n">
-        <v>93.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>11.4</v>
+        <v>17.6</v>
       </c>
       <c r="H4" t="n">
-        <v>502.8</v>
+        <v>630.6</v>
       </c>
       <c r="I4" t="n">
-        <v>822.1</v>
+        <v>834.4</v>
       </c>
       <c r="J4" t="n">
-        <v>991</v>
+        <v>975</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>60.7</v>
+        <v>62.8</v>
       </c>
       <c r="E5" t="n">
-        <v>65.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>89.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>17.6</v>
+        <v>11.4</v>
       </c>
       <c r="H5" t="n">
-        <v>546.1</v>
+        <v>502.8</v>
       </c>
       <c r="I5" t="n">
-        <v>826</v>
+        <v>822.1</v>
       </c>
       <c r="J5" t="n">
-        <v>975</v>
+        <v>991</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>55.4</v>
+        <v>54.8</v>
       </c>
       <c r="E6" t="n">
-        <v>50.7</v>
+        <v>56.2</v>
       </c>
       <c r="F6" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>18.1</v>
+        <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>498.9</v>
+        <v>493.4</v>
       </c>
       <c r="I6" t="n">
-        <v>809.3</v>
+        <v>814</v>
       </c>
       <c r="J6" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>55.1</v>
+        <v>54</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>50.7</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>18.1</v>
       </c>
       <c r="H7" t="n">
-        <v>441</v>
+        <v>485.8</v>
       </c>
       <c r="I7" t="n">
-        <v>814.1</v>
+        <v>809.3</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>928</v>
       </c>
     </row>
     <row r="8">
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
       <c r="E13" t="n">
         <v>33</v>
@@ -867,10 +867,10 @@
         <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="H13" t="n">
-        <v>303.6</v>
+        <v>292.9</v>
       </c>
       <c r="I13" t="n">
         <v>754.9</v>
@@ -1209,7 +1209,9 @@
       <c r="J6" t="n">
         <v>705</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>813</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1244,7 +1246,9 @@
       <c r="J7" t="n">
         <v>619</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>910</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1725,7 +1729,9 @@
       <c r="J6" t="n">
         <v>47.9</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>52.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1760,7 +1766,9 @@
       <c r="J7" t="n">
         <v>17.6</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>84.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1794,7 +1802,7 @@
         <v>18.1</v>
       </c>
       <c r="K8" t="n">
-        <v>84.09999999999999</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1848,7 +1856,7 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>15.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="11">
@@ -2296,19 +2304,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>752.5</v>
+        <v>807</v>
       </c>
       <c r="D11" t="n">
-        <v>110.5</v>
+        <v>101.2</v>
       </c>
       <c r="E11" t="n">
-        <v>752.5</v>
+        <v>838</v>
       </c>
       <c r="F11" t="n">
-        <v>863</v>
+        <v>910</v>
       </c>
       <c r="G11" t="n">
         <v>642</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>80.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>86.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,10 +496,10 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>721.8</v>
+        <v>794</v>
       </c>
       <c r="I2" t="n">
-        <v>887.2</v>
+        <v>887.5</v>
       </c>
       <c r="J2" t="n">
         <v>997</v>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jbarn11</t>
+          <t>Spy</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>63.1</v>
+        <v>62.8</v>
       </c>
       <c r="E4" t="n">
-        <v>66.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>89.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>17.6</v>
+        <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>630.6</v>
+        <v>502.8</v>
       </c>
       <c r="I4" t="n">
-        <v>834.4</v>
+        <v>822.1</v>
       </c>
       <c r="J4" t="n">
-        <v>975</v>
+        <v>991</v>
       </c>
     </row>
     <row r="5">
@@ -579,32 +579,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Spy</t>
+          <t>jbarn11</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>62.8</v>
+        <v>62.5</v>
       </c>
       <c r="E5" t="n">
-        <v>76.90000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F5" t="n">
-        <v>93.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>11.4</v>
+        <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>502.8</v>
+        <v>625.1</v>
       </c>
       <c r="I5" t="n">
-        <v>822.1</v>
+        <v>834.4</v>
       </c>
       <c r="J5" t="n">
-        <v>991</v>
+        <v>975</v>
       </c>
     </row>
     <row r="6">
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>54.8</v>
+        <v>54</v>
       </c>
       <c r="E6" t="n">
-        <v>56.2</v>
+        <v>54.5</v>
       </c>
       <c r="F6" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>493.4</v>
+        <v>378.1</v>
       </c>
       <c r="I6" t="n">
-        <v>814</v>
+        <v>827.6</v>
       </c>
       <c r="J6" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53.5</v>
       </c>
       <c r="E7" t="n">
-        <v>50.7</v>
+        <v>56.2</v>
       </c>
       <c r="F7" t="n">
-        <v>90.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>18.1</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>485.8</v>
+        <v>481.3</v>
       </c>
       <c r="I7" t="n">
-        <v>809.3</v>
+        <v>814</v>
       </c>
       <c r="J7" t="n">
-        <v>928</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>50.6</v>
+        <v>52.9</v>
       </c>
       <c r="E8" t="n">
-        <v>51.8</v>
+        <v>50.7</v>
       </c>
       <c r="F8" t="n">
-        <v>80.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>22.2</v>
+        <v>18.1</v>
       </c>
       <c r="H8" t="n">
-        <v>303.7</v>
+        <v>476.5</v>
       </c>
       <c r="I8" t="n">
-        <v>816.2</v>
+        <v>809.3</v>
       </c>
       <c r="J8" t="n">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9">
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5</v>
+        <v>32.2</v>
       </c>
       <c r="E13" t="n">
         <v>33</v>
@@ -867,10 +867,10 @@
         <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="H13" t="n">
-        <v>292.9</v>
+        <v>289.5</v>
       </c>
       <c r="I13" t="n">
         <v>754.9</v>
@@ -1120,7 +1120,9 @@
       <c r="J3" t="n">
         <v>829</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>890</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1149,7 +1151,9 @@
       <c r="J4" t="n">
         <v>654</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>896</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1640,7 +1644,9 @@
       <c r="J3" t="n">
         <v>88.8</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>72.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1669,7 +1675,9 @@
       <c r="J4" t="n">
         <v>28.3</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>74.40000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1730,7 +1738,7 @@
         <v>47.9</v>
       </c>
       <c r="K6" t="n">
-        <v>52.4</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="7">
@@ -1767,7 +1775,7 @@
         <v>17.6</v>
       </c>
       <c r="K7" t="n">
-        <v>84.5</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -1802,7 +1810,7 @@
         <v>18.1</v>
       </c>
       <c r="K8" t="n">
-        <v>71</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="9">
@@ -1856,7 +1864,7 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -2304,16 +2312,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>807</v>
+        <v>835.7</v>
       </c>
       <c r="D11" t="n">
-        <v>101.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>838</v>
+        <v>876.5</v>
       </c>
       <c r="F11" t="n">
         <v>910</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>79.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>86.09999999999999</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>794</v>
+        <v>791.4</v>
       </c>
       <c r="I2" t="n">
         <v>887.5</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>74.7</v>
+        <v>74.5</v>
       </c>
       <c r="E3" t="n">
-        <v>84.3</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
         <v>97.7</v>
@@ -530,10 +530,10 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>672.2</v>
+        <v>745.3</v>
       </c>
       <c r="I3" t="n">
-        <v>873.2</v>
+        <v>875.8</v>
       </c>
       <c r="J3" t="n">
         <v>991</v>
@@ -586,7 +586,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>62.5</v>
+        <v>62.3</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>625.1</v>
+        <v>623.2</v>
       </c>
       <c r="I5" t="n">
         <v>834.4</v>
@@ -620,7 +620,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>378.1</v>
+        <v>375.7</v>
       </c>
       <c r="I6" t="n">
         <v>827.6</v>
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>53.5</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>56.2</v>
@@ -666,7 +666,7 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>481.3</v>
+        <v>476.9</v>
       </c>
       <c r="I7" t="n">
         <v>814</v>
@@ -688,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="E8" t="n">
         <v>50.7</v>
@@ -700,7 +700,7 @@
         <v>18.1</v>
       </c>
       <c r="H8" t="n">
-        <v>476.5</v>
+        <v>473</v>
       </c>
       <c r="I8" t="n">
         <v>809.3</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="E13" t="n">
         <v>33</v>
@@ -867,10 +867,10 @@
         <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="H13" t="n">
-        <v>289.5</v>
+        <v>288.8</v>
       </c>
       <c r="I13" t="n">
         <v>754.9</v>
@@ -1085,7 +1085,9 @@
       <c r="J2" t="n">
         <v>905</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>899</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1609,7 +1611,9 @@
       <c r="J2" t="n">
         <v>97.7</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>73.09999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1645,7 +1649,7 @@
         <v>88.8</v>
       </c>
       <c r="K3" t="n">
-        <v>72.2</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1676,7 +1680,7 @@
         <v>28.3</v>
       </c>
       <c r="K4" t="n">
-        <v>74.40000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -1738,7 +1742,7 @@
         <v>47.9</v>
       </c>
       <c r="K6" t="n">
-        <v>40.3</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="7">
@@ -1775,7 +1779,7 @@
         <v>17.6</v>
       </c>
       <c r="K7" t="n">
-        <v>79</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1810,7 +1814,7 @@
         <v>18.1</v>
       </c>
       <c r="K8" t="n">
-        <v>61.7</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="9">
@@ -1864,7 +1868,7 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -2312,16 +2316,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>835.7</v>
+        <v>844.7</v>
       </c>
       <c r="D11" t="n">
-        <v>92.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>876.5</v>
+        <v>890</v>
       </c>
       <c r="F11" t="n">
         <v>910</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
         <v>86.09999999999999</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>791.4</v>
+        <v>790.5</v>
       </c>
       <c r="I2" t="n">
         <v>887.5</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>745.3</v>
+        <v>744.7</v>
       </c>
       <c r="I3" t="n">
         <v>875.8</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>62.8</v>
+        <v>64.2</v>
       </c>
       <c r="E4" t="n">
-        <v>76.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>502.8</v>
+        <v>578.1</v>
       </c>
       <c r="I4" t="n">
-        <v>822.1</v>
+        <v>831.4</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>623.2</v>
+        <v>622.9</v>
       </c>
       <c r="I5" t="n">
         <v>834.4</v>
@@ -620,7 +620,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>53.7</v>
+        <v>53.6</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>375.7</v>
+        <v>375</v>
       </c>
       <c r="I6" t="n">
         <v>827.6</v>
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52.6</v>
       </c>
       <c r="E7" t="n">
         <v>56.2</v>
@@ -666,7 +666,7 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>476.9</v>
+        <v>473.7</v>
       </c>
       <c r="I7" t="n">
         <v>814</v>
@@ -688,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="E8" t="n">
         <v>50.7</v>
@@ -700,7 +700,7 @@
         <v>18.1</v>
       </c>
       <c r="H8" t="n">
-        <v>473</v>
+        <v>471.2</v>
       </c>
       <c r="I8" t="n">
         <v>809.3</v>
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>waltkin</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>47.8</v>
+        <v>51.1</v>
       </c>
       <c r="E9" t="n">
-        <v>47.8</v>
+        <v>54.4</v>
       </c>
       <c r="F9" t="n">
-        <v>91.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>95.59999999999999</v>
+        <v>306.7</v>
       </c>
       <c r="I9" t="n">
-        <v>824</v>
+        <v>828.3</v>
       </c>
       <c r="J9" t="n">
-        <v>845</v>
+        <v>953</v>
       </c>
     </row>
     <row r="10">
@@ -749,32 +749,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>waltkin</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>47.8</v>
       </c>
       <c r="E10" t="n">
-        <v>43.1</v>
+        <v>47.8</v>
       </c>
       <c r="F10" t="n">
-        <v>75.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>229.9</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="J10" t="n">
-        <v>953</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11">
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>36.9</v>
       </c>
       <c r="E11" t="n">
-        <v>52.3</v>
+        <v>34.3</v>
       </c>
       <c r="F11" t="n">
         <v>64.7</v>
@@ -802,10 +802,10 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>204.9</v>
+        <v>221.2</v>
       </c>
       <c r="I11" t="n">
-        <v>767</v>
+        <v>767.3</v>
       </c>
       <c r="J11" t="n">
         <v>916</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
         <v>33</v>
@@ -867,10 +867,10 @@
         <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H13" t="n">
-        <v>288.8</v>
+        <v>288.3</v>
       </c>
       <c r="I13" t="n">
         <v>754.9</v>
@@ -1182,7 +1182,9 @@
       <c r="J5" t="n">
         <v>685</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>910</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1426,7 +1428,9 @@
       <c r="J13" t="n">
         <v>644</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>906</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1453,7 +1457,9 @@
       <c r="J14" t="n">
         <v>608</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>769</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1612,7 +1618,7 @@
         <v>97.7</v>
       </c>
       <c r="K2" t="n">
-        <v>73.09999999999999</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="3">
@@ -1649,7 +1655,7 @@
         <v>88.8</v>
       </c>
       <c r="K3" t="n">
-        <v>69.59999999999999</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="4">
@@ -1680,7 +1686,7 @@
         <v>28.3</v>
       </c>
       <c r="K4" t="n">
-        <v>72</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="5">
@@ -1708,7 +1714,9 @@
       <c r="J5" t="n">
         <v>39.9</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>76.8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1742,7 +1750,7 @@
         <v>47.9</v>
       </c>
       <c r="K6" t="n">
-        <v>35.9</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="7">
@@ -1779,7 +1787,7 @@
         <v>17.6</v>
       </c>
       <c r="K7" t="n">
-        <v>77.09999999999999</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="8">
@@ -1814,7 +1822,7 @@
         <v>18.1</v>
       </c>
       <c r="K8" t="n">
-        <v>58.2</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="9">
@@ -1868,7 +1876,7 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -1952,7 +1960,9 @@
       <c r="J13" t="n">
         <v>25</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>75.3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1979,7 +1989,9 @@
       <c r="J14" t="n">
         <v>14.8</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>16.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2316,16 +2328,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>844.7</v>
+        <v>849.8</v>
       </c>
       <c r="D11" t="n">
-        <v>88.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="F11" t="n">
         <v>910</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>86.09999999999999</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>790.5</v>
+        <v>794.2</v>
       </c>
       <c r="I2" t="n">
         <v>887.5</v>
@@ -518,7 +518,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>74.5</v>
+        <v>74.8</v>
       </c>
       <c r="E3" t="n">
         <v>82</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>744.7</v>
+        <v>748</v>
       </c>
       <c r="I3" t="n">
         <v>875.8</v>
@@ -552,10 +552,10 @@
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>64.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>75.3</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>578.1</v>
+        <v>581.1</v>
       </c>
       <c r="I4" t="n">
         <v>831.4</v>
@@ -586,7 +586,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>62.3</v>
+        <v>62.6</v>
       </c>
       <c r="E5" t="n">
         <v>66.2</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>622.9</v>
+        <v>625.8</v>
       </c>
       <c r="I5" t="n">
         <v>834.4</v>
@@ -620,7 +620,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>53.6</v>
+        <v>54.1</v>
       </c>
       <c r="E6" t="n">
         <v>54.5</v>
@@ -632,7 +632,7 @@
         <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>375</v>
+        <v>378.4</v>
       </c>
       <c r="I6" t="n">
         <v>827.6</v>
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>52.6</v>
+        <v>53.2</v>
       </c>
       <c r="E7" t="n">
         <v>56.2</v>
@@ -666,7 +666,7 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>473.7</v>
+        <v>478.9</v>
       </c>
       <c r="I7" t="n">
         <v>814</v>
@@ -688,7 +688,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="E8" t="n">
         <v>50.7</v>
@@ -700,7 +700,7 @@
         <v>18.1</v>
       </c>
       <c r="H8" t="n">
-        <v>471.2</v>
+        <v>475.8</v>
       </c>
       <c r="I8" t="n">
         <v>809.3</v>
@@ -722,19 +722,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="E9" t="n">
         <v>54.4</v>
       </c>
       <c r="F9" t="n">
-        <v>76.8</v>
+        <v>79.7</v>
       </c>
       <c r="G9" t="n">
         <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>306.7</v>
+        <v>309.6</v>
       </c>
       <c r="I9" t="n">
         <v>828.3</v>
@@ -790,10 +790,10 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>36.9</v>
+        <v>37.6</v>
       </c>
       <c r="E11" t="n">
-        <v>34.3</v>
+        <v>36.4</v>
       </c>
       <c r="F11" t="n">
         <v>64.7</v>
@@ -802,7 +802,7 @@
         <v>14.8</v>
       </c>
       <c r="H11" t="n">
-        <v>221.2</v>
+        <v>225.4</v>
       </c>
       <c r="I11" t="n">
         <v>767.3</v>
@@ -858,7 +858,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="E13" t="n">
         <v>33</v>
@@ -867,10 +867,10 @@
         <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>288.3</v>
+        <v>288.7</v>
       </c>
       <c r="I13" t="n">
         <v>754.9</v>
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>44.3</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>108.9</v>
+        <v>119.8</v>
       </c>
       <c r="I14" t="n">
-        <v>671.3</v>
+        <v>679.1</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1490,7 +1490,9 @@
       <c r="J15" t="n">
         <v>696</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>734</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1618,7 +1620,7 @@
         <v>97.7</v>
       </c>
       <c r="K2" t="n">
-        <v>72.5</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="3">
@@ -1655,7 +1657,7 @@
         <v>88.8</v>
       </c>
       <c r="K3" t="n">
-        <v>68.7</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1686,7 +1688,7 @@
         <v>28.3</v>
       </c>
       <c r="K4" t="n">
-        <v>71.3</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="5">
@@ -1715,7 +1717,7 @@
         <v>39.9</v>
       </c>
       <c r="K5" t="n">
-        <v>76.8</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="6">
@@ -1750,7 +1752,7 @@
         <v>47.9</v>
       </c>
       <c r="K6" t="n">
-        <v>32.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="7">
@@ -1787,7 +1789,7 @@
         <v>17.6</v>
       </c>
       <c r="K7" t="n">
-        <v>76.8</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="8">
@@ -1822,7 +1824,7 @@
         <v>18.1</v>
       </c>
       <c r="K8" t="n">
-        <v>56.4</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -1876,7 +1878,7 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1961,7 +1963,7 @@
         <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>75.3</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="14">
@@ -1990,7 +1992,7 @@
         <v>14.8</v>
       </c>
       <c r="K14" t="n">
-        <v>16.3</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="15">
@@ -2022,7 +2024,9 @@
       <c r="J15" t="n">
         <v>44.3</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2328,16 +2332,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>849.8</v>
+        <v>839.3</v>
       </c>
       <c r="D11" t="n">
-        <v>82.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="E11" t="n">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F11" t="n">
         <v>910</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -685,13 +685,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="E8" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F8" t="n">
         <v>90.90000000000001</v>
@@ -700,10 +700,10 @@
         <v>18.1</v>
       </c>
       <c r="H8" t="n">
-        <v>475.8</v>
+        <v>525.8</v>
       </c>
       <c r="I8" t="n">
-        <v>809.3</v>
+        <v>798.3</v>
       </c>
       <c r="J8" t="n">
         <v>928</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,6 +1051,11 @@
           <t>9/11/26</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>9/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1088,6 +1093,7 @@
       <c r="K2" t="n">
         <v>899</v>
       </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1125,6 +1131,7 @@
       <c r="K3" t="n">
         <v>890</v>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1156,6 +1163,7 @@
       <c r="K4" t="n">
         <v>896</v>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1185,6 +1193,7 @@
       <c r="K5" t="n">
         <v>910</v>
       </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1220,6 +1229,7 @@
       <c r="K6" t="n">
         <v>813</v>
       </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1257,6 +1267,7 @@
       <c r="K7" t="n">
         <v>910</v>
       </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1291,6 +1302,9 @@
       </c>
       <c r="K8" t="n">
         <v>863</v>
+      </c>
+      <c r="L8" t="n">
+        <v>699</v>
       </c>
     </row>
     <row r="9">
@@ -1311,6 +1325,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1346,6 +1361,7 @@
       <c r="K10" t="n">
         <v>642</v>
       </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1371,6 +1387,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1396,6 +1413,7 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1431,6 +1449,7 @@
       <c r="K13" t="n">
         <v>906</v>
       </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1460,6 +1479,7 @@
       <c r="K14" t="n">
         <v>769</v>
       </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1493,6 +1513,7 @@
       <c r="K15" t="n">
         <v>734</v>
       </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1514,6 +1535,7 @@
         <v>845</v>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1526,7 +1548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1585,6 +1607,11 @@
           <t>9/11/26</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>9/12/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1622,6 +1649,7 @@
       <c r="K2" t="n">
         <v>75.8</v>
       </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1659,6 +1687,7 @@
       <c r="K3" t="n">
         <v>72.40000000000001</v>
       </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1690,6 +1719,7 @@
       <c r="K4" t="n">
         <v>74.7</v>
       </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1719,6 +1749,7 @@
       <c r="K5" t="n">
         <v>79.7</v>
       </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1754,6 +1785,7 @@
       <c r="K6" t="n">
         <v>37.9</v>
       </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1791,6 +1823,7 @@
       <c r="K7" t="n">
         <v>79.7</v>
       </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1825,6 +1858,9 @@
       </c>
       <c r="K8" t="n">
         <v>61</v>
+      </c>
+      <c r="L8" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1845,6 +1881,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1880,6 +1917,7 @@
       <c r="K10" t="n">
         <v>1</v>
       </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1905,6 +1943,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1930,6 +1969,7 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1965,6 +2005,7 @@
       <c r="K13" t="n">
         <v>78.3</v>
       </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1994,6 +2035,7 @@
       <c r="K14" t="n">
         <v>20.5</v>
       </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2027,6 +2069,7 @@
       <c r="K15" t="n">
         <v>10.9</v>
       </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2048,6 +2091,7 @@
         <v>91.59999999999999</v>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2060,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2350,6 +2394,31 @@
         <v>642</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9/12/26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>699</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>699</v>
+      </c>
+      <c r="F12" t="n">
+        <v>699</v>
+      </c>
+      <c r="G12" t="n">
+        <v>699</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>54.1</v>
+        <v>56.3</v>
       </c>
       <c r="E6" t="n">
-        <v>54.5</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>22.2</v>
+        <v>15.5</v>
       </c>
       <c r="H6" t="n">
-        <v>378.4</v>
+        <v>563</v>
       </c>
       <c r="I6" t="n">
-        <v>827.6</v>
+        <v>816.4</v>
       </c>
       <c r="J6" t="n">
-        <v>930</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>53.2</v>
+        <v>54.1</v>
       </c>
       <c r="E7" t="n">
-        <v>56.2</v>
+        <v>54.5</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H7" t="n">
-        <v>478.9</v>
+        <v>378.4</v>
       </c>
       <c r="I7" t="n">
-        <v>814</v>
+        <v>827.6</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ZZ</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>52.6</v>
+        <v>51.6</v>
       </c>
       <c r="E8" t="n">
-        <v>50.4</v>
+        <v>54.4</v>
       </c>
       <c r="F8" t="n">
-        <v>90.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G8" t="n">
-        <v>18.1</v>
+        <v>5.7</v>
       </c>
       <c r="H8" t="n">
-        <v>525.8</v>
+        <v>309.6</v>
       </c>
       <c r="I8" t="n">
-        <v>798.3</v>
+        <v>828.3</v>
       </c>
       <c r="J8" t="n">
-        <v>928</v>
+        <v>953</v>
       </c>
     </row>
     <row r="9">
@@ -715,32 +715,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>ZZ</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>51.6</v>
+        <v>49.2</v>
       </c>
       <c r="E9" t="n">
-        <v>54.4</v>
+        <v>44.8</v>
       </c>
       <c r="F9" t="n">
-        <v>79.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>5.7</v>
+        <v>15.9</v>
       </c>
       <c r="H9" t="n">
-        <v>309.6</v>
+        <v>491.7</v>
       </c>
       <c r="I9" t="n">
-        <v>828.3</v>
+        <v>798.3</v>
       </c>
       <c r="J9" t="n">
-        <v>953</v>
+        <v>928</v>
       </c>
     </row>
     <row r="10">
@@ -1229,7 +1229,9 @@
       <c r="K6" t="n">
         <v>813</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>838</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1785,7 +1787,9 @@
       <c r="K6" t="n">
         <v>37.9</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>84.09999999999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1860,7 +1864,7 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>50</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="9">
@@ -2401,19 +2405,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>699</v>
+        <v>768.5</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>69.5</v>
       </c>
       <c r="E12" t="n">
-        <v>699</v>
+        <v>768.5</v>
       </c>
       <c r="F12" t="n">
-        <v>699</v>
+        <v>838</v>
       </c>
       <c r="G12" t="n">
         <v>699</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>79.40000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>86.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="F2" t="n">
         <v>94.2</v>
@@ -496,10 +496,10 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>794.2</v>
+        <v>884.2</v>
       </c>
       <c r="I2" t="n">
-        <v>887.5</v>
+        <v>893.7</v>
       </c>
       <c r="J2" t="n">
         <v>997</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>56.3</v>
+        <v>54.1</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="F6" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H6" t="n">
-        <v>563</v>
+        <v>378.4</v>
       </c>
       <c r="I6" t="n">
-        <v>816.4</v>
+        <v>827.6</v>
       </c>
       <c r="J6" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>54.1</v>
+        <v>52.9</v>
       </c>
       <c r="E7" t="n">
-        <v>54.5</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>80.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>22.2</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>378.4</v>
+        <v>528.8</v>
       </c>
       <c r="I7" t="n">
-        <v>827.6</v>
+        <v>816.4</v>
       </c>
       <c r="J7" t="n">
-        <v>930</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>49.2</v>
+        <v>48.2</v>
       </c>
       <c r="E9" t="n">
         <v>44.8</v>
@@ -731,10 +731,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>15.9</v>
+        <v>6.5</v>
       </c>
       <c r="H9" t="n">
-        <v>491.7</v>
+        <v>482.3</v>
       </c>
       <c r="I9" t="n">
         <v>798.3</v>
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>138.9</v>
+        <v>348.1</v>
       </c>
       <c r="I12" t="n">
-        <v>765.2</v>
+        <v>765.4</v>
       </c>
       <c r="J12" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>32.1</v>
+        <v>34.7</v>
       </c>
       <c r="E13" t="n">
-        <v>33</v>
+        <v>36.6</v>
       </c>
       <c r="F13" t="n">
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>288.7</v>
+        <v>138.9</v>
       </c>
       <c r="I13" t="n">
-        <v>754.9</v>
+        <v>765.2</v>
       </c>
       <c r="J13" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
     </row>
     <row r="14">
@@ -1131,7 +1131,9 @@
       <c r="K3" t="n">
         <v>890</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>956</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1363,7 +1365,9 @@
       <c r="K10" t="n">
         <v>642</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>860</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1689,7 +1693,9 @@
       <c r="K3" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1788,7 +1794,7 @@
         <v>37.9</v>
       </c>
       <c r="L6" t="n">
-        <v>84.09999999999999</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="7">
@@ -1864,7 +1870,7 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>15.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="9">
@@ -1921,7 +1927,9 @@
       <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>59.4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2405,19 +2413,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>768.5</v>
+        <v>838.2</v>
       </c>
       <c r="D12" t="n">
-        <v>69.5</v>
+        <v>91.8</v>
       </c>
       <c r="E12" t="n">
-        <v>768.5</v>
+        <v>849</v>
       </c>
       <c r="F12" t="n">
-        <v>838</v>
+        <v>956</v>
       </c>
       <c r="G12" t="n">
         <v>699</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,7 +484,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>80.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>884.2</v>
+        <v>887.3</v>
       </c>
       <c r="I2" t="n">
         <v>893.7</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>79.7</v>
       </c>
       <c r="F3" t="n">
         <v>97.7</v>
@@ -530,10 +530,10 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>748</v>
+        <v>824.1</v>
       </c>
       <c r="I3" t="n">
-        <v>875.8</v>
+        <v>877.8</v>
       </c>
       <c r="J3" t="n">
         <v>991</v>
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>62.6</v>
+        <v>59.2</v>
       </c>
       <c r="E5" t="n">
-        <v>66.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>89.09999999999999</v>
@@ -598,10 +598,10 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>625.8</v>
+        <v>651.3</v>
       </c>
       <c r="I5" t="n">
-        <v>834.4</v>
+        <v>830.8</v>
       </c>
       <c r="J5" t="n">
         <v>975</v>
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>61.2</v>
       </c>
       <c r="F7" t="n">
-        <v>87.90000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>528.8</v>
+        <v>370.8</v>
       </c>
       <c r="I7" t="n">
-        <v>816.4</v>
+        <v>833.7</v>
       </c>
       <c r="J7" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>51.6</v>
+        <v>52.5</v>
       </c>
       <c r="E8" t="n">
-        <v>54.4</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>79.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="H8" t="n">
-        <v>309.6</v>
+        <v>525.4</v>
       </c>
       <c r="I8" t="n">
-        <v>828.3</v>
+        <v>816.4</v>
       </c>
       <c r="J8" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>48.2</v>
+        <v>47.9</v>
       </c>
       <c r="E9" t="n">
         <v>44.8</v>
@@ -731,10 +731,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="n">
-        <v>482.3</v>
+        <v>478.5</v>
       </c>
       <c r="I9" t="n">
         <v>798.3</v>
@@ -824,7 +824,7 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>348.1</v>
+        <v>346.8</v>
       </c>
       <c r="I12" t="n">
         <v>765.4</v>
@@ -1093,7 +1093,9 @@
       <c r="K2" t="n">
         <v>899</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>898</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1195,7 +1197,9 @@
       <c r="K5" t="n">
         <v>910</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>866</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1271,7 +1275,9 @@
       <c r="K7" t="n">
         <v>910</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>795</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1655,7 +1661,9 @@
       <c r="K2" t="n">
         <v>75.8</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>76.09999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1694,7 +1702,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1757,7 +1765,9 @@
       <c r="K5" t="n">
         <v>79.7</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>61.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1794,7 +1804,7 @@
         <v>37.9</v>
       </c>
       <c r="L6" t="n">
-        <v>49.9</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="7">
@@ -1833,7 +1843,9 @@
       <c r="K7" t="n">
         <v>79.7</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1870,7 +1882,7 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -1928,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>59.4</v>
+        <v>58.1</v>
       </c>
     </row>
     <row r="11">
@@ -2413,16 +2425,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>838.2</v>
+        <v>844.6</v>
       </c>
       <c r="D12" t="n">
-        <v>91.8</v>
+        <v>75.3</v>
       </c>
       <c r="E12" t="n">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="F12" t="n">
         <v>956</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,19 +484,19 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
       </c>
       <c r="F2" t="n">
-        <v>94.2</v>
+        <v>94.8</v>
       </c>
       <c r="G2" t="n">
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>887.3</v>
+        <v>889</v>
       </c>
       <c r="I2" t="n">
         <v>893.7</v>
@@ -518,7 +518,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>74.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="E3" t="n">
         <v>79.7</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>824.1</v>
+        <v>827.4</v>
       </c>
       <c r="I3" t="n">
         <v>877.8</v>
@@ -586,7 +586,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="E5" t="n">
         <v>65.40000000000001</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>651.3</v>
+        <v>653</v>
       </c>
       <c r="I5" t="n">
         <v>830.8</v>
@@ -613,32 +613,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tomh</t>
+          <t>kadrids</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>54.1</v>
+        <v>53.5</v>
       </c>
       <c r="E6" t="n">
-        <v>54.5</v>
+        <v>64.7</v>
       </c>
       <c r="F6" t="n">
-        <v>80.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="G6" t="n">
-        <v>22.2</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>378.4</v>
+        <v>374.3</v>
       </c>
       <c r="I6" t="n">
-        <v>827.6</v>
+        <v>833.7</v>
       </c>
       <c r="J6" t="n">
-        <v>930</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -647,32 +647,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>kadrids</t>
+          <t>JonahL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52.8</v>
       </c>
       <c r="E7" t="n">
-        <v>61.2</v>
+        <v>52.9</v>
       </c>
       <c r="F7" t="n">
-        <v>79.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>370.8</v>
+        <v>528.5</v>
       </c>
       <c r="I7" t="n">
-        <v>833.7</v>
+        <v>816.4</v>
       </c>
       <c r="J7" t="n">
-        <v>953</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8">
@@ -681,32 +681,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JonahL</t>
+          <t>Tomh</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>52.5</v>
+        <v>50.9</v>
       </c>
       <c r="E8" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="F8" t="n">
-        <v>87.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>15.5</v>
+        <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>525.4</v>
+        <v>407</v>
       </c>
       <c r="I8" t="n">
-        <v>816.4</v>
+        <v>823.9</v>
       </c>
       <c r="J8" t="n">
-        <v>960</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9">
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E9" t="n">
         <v>44.8</v>
@@ -731,10 +731,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="n">
-        <v>478.5</v>
+        <v>478.4</v>
       </c>
       <c r="I9" t="n">
         <v>798.3</v>
@@ -824,7 +824,7 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>34.7</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>346.8</v>
+        <v>350.3</v>
       </c>
       <c r="I12" t="n">
         <v>765.4</v>
@@ -1167,7 +1167,9 @@
       <c r="K4" t="n">
         <v>896</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>798</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1662,7 +1664,7 @@
         <v>75.8</v>
       </c>
       <c r="L2" t="n">
-        <v>76.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1702,7 +1704,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>93.09999999999999</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="4">
@@ -1735,7 +1737,9 @@
       <c r="K4" t="n">
         <v>74.7</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>28.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1766,7 +1770,7 @@
         <v>79.7</v>
       </c>
       <c r="L5" t="n">
-        <v>61.2</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="6">
@@ -1804,7 +1808,7 @@
         <v>37.9</v>
       </c>
       <c r="L6" t="n">
-        <v>46.5</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="7">
@@ -1844,7 +1848,7 @@
         <v>79.7</v>
       </c>
       <c r="L7" t="n">
-        <v>25.5</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="8">
@@ -1882,7 +1886,7 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -1940,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>58.1</v>
+        <v>61.6</v>
       </c>
     </row>
     <row r="11">
@@ -2425,16 +2429,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>844.6</v>
+        <v>838.8</v>
       </c>
       <c r="D12" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="F12" t="n">
         <v>956</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -484,19 +484,19 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>86.7</v>
       </c>
       <c r="F2" t="n">
-        <v>94.8</v>
+        <v>94.2</v>
       </c>
       <c r="G2" t="n">
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>889</v>
+        <v>886.2</v>
       </c>
       <c r="I2" t="n">
         <v>893.7</v>
@@ -518,7 +518,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>75.2</v>
+        <v>74.7</v>
       </c>
       <c r="E3" t="n">
         <v>79.7</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>827.4</v>
+        <v>821.7</v>
       </c>
       <c r="I3" t="n">
         <v>877.8</v>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>64.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>79.8</v>
       </c>
       <c r="F4" t="n">
         <v>93.59999999999999</v>
@@ -564,10 +564,10 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>581.1</v>
+        <v>670</v>
       </c>
       <c r="I4" t="n">
-        <v>831.4</v>
+        <v>842.5</v>
       </c>
       <c r="J4" t="n">
         <v>991</v>
@@ -586,7 +586,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>59.4</v>
+        <v>59</v>
       </c>
       <c r="E5" t="n">
         <v>65.40000000000001</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="I5" t="n">
         <v>830.8</v>
@@ -620,10 +620,10 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="E6" t="n">
-        <v>64.7</v>
+        <v>58.3</v>
       </c>
       <c r="F6" t="n">
         <v>79.7</v>
@@ -632,7 +632,7 @@
         <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>374.3</v>
+        <v>367.9</v>
       </c>
       <c r="I6" t="n">
         <v>833.7</v>
@@ -654,10 +654,10 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>52.8</v>
+        <v>52.2</v>
       </c>
       <c r="E7" t="n">
-        <v>52.9</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
         <v>87.90000000000001</v>
@@ -666,7 +666,7 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>528.5</v>
+        <v>522.5</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -688,7 +688,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
       <c r="E8" t="n">
         <v>51.8</v>
@@ -700,7 +700,7 @@
         <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>407</v>
+        <v>402.8</v>
       </c>
       <c r="I8" t="n">
         <v>823.9</v>
@@ -731,10 +731,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>478.4</v>
+        <v>478</v>
       </c>
       <c r="I9" t="n">
         <v>798.3</v>
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>350.3</v>
+        <v>138.9</v>
       </c>
       <c r="I12" t="n">
-        <v>765.4</v>
+        <v>765.2</v>
       </c>
       <c r="J12" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>34.7</v>
+        <v>34.4</v>
       </c>
       <c r="E13" t="n">
         <v>36.6</v>
       </c>
       <c r="F13" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>138.9</v>
+        <v>343.9</v>
       </c>
       <c r="I13" t="n">
-        <v>765.2</v>
+        <v>765.4</v>
       </c>
       <c r="J13" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="14">
@@ -1463,7 +1463,9 @@
       <c r="K13" t="n">
         <v>906</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>942</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1664,7 +1666,7 @@
         <v>75.8</v>
       </c>
       <c r="L2" t="n">
-        <v>79.40000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="3">
@@ -1704,7 +1706,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>94.8</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -1738,7 +1740,7 @@
         <v>74.7</v>
       </c>
       <c r="L4" t="n">
-        <v>28.6</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="5">
@@ -1770,7 +1772,7 @@
         <v>79.7</v>
       </c>
       <c r="L5" t="n">
-        <v>64.7</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="6">
@@ -1808,7 +1810,7 @@
         <v>37.9</v>
       </c>
       <c r="L6" t="n">
-        <v>49.6</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="7">
@@ -1848,7 +1850,7 @@
         <v>79.7</v>
       </c>
       <c r="L7" t="n">
-        <v>27.2</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="8">
@@ -1886,7 +1888,7 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -1944,7 +1946,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>61.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="11">
@@ -2033,7 +2035,9 @@
       <c r="K13" t="n">
         <v>78.3</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>88.90000000000001</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2429,16 +2433,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>838.8</v>
+        <v>850.2</v>
       </c>
       <c r="D12" t="n">
-        <v>72.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E12" t="n">
-        <v>849</v>
+        <v>860</v>
       </c>
       <c r="F12" t="n">
         <v>956</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -496,7 +496,7 @@
         <v>40.5</v>
       </c>
       <c r="H2" t="n">
-        <v>886.2</v>
+        <v>887.1</v>
       </c>
       <c r="I2" t="n">
         <v>893.7</v>
@@ -518,7 +518,7 @@
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>74.7</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
         <v>79.7</v>
@@ -530,7 +530,7 @@
         <v>30.5</v>
       </c>
       <c r="H3" t="n">
-        <v>821.7</v>
+        <v>825.3</v>
       </c>
       <c r="I3" t="n">
         <v>877.8</v>
@@ -552,7 +552,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>67</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>79.8</v>
@@ -564,7 +564,7 @@
         <v>11.4</v>
       </c>
       <c r="H4" t="n">
-        <v>670</v>
+        <v>671.3</v>
       </c>
       <c r="I4" t="n">
         <v>842.5</v>
@@ -586,7 +586,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>59.6</v>
       </c>
       <c r="E5" t="n">
         <v>65.40000000000001</v>
@@ -598,7 +598,7 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>649</v>
+        <v>655.4</v>
       </c>
       <c r="I5" t="n">
         <v>830.8</v>
@@ -620,10 +620,10 @@
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>52.6</v>
+        <v>53.3</v>
       </c>
       <c r="E6" t="n">
-        <v>58.3</v>
+        <v>63.6</v>
       </c>
       <c r="F6" t="n">
         <v>79.7</v>
@@ -632,7 +632,7 @@
         <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>367.9</v>
+        <v>373.2</v>
       </c>
       <c r="I6" t="n">
         <v>833.7</v>
@@ -654,10 +654,10 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>53.1</v>
       </c>
       <c r="F7" t="n">
         <v>87.90000000000001</v>
@@ -666,7 +666,7 @@
         <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>522.5</v>
+        <v>528.9</v>
       </c>
       <c r="I7" t="n">
         <v>816.4</v>
@@ -688,7 +688,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>50.3</v>
+        <v>51.2</v>
       </c>
       <c r="E8" t="n">
         <v>51.8</v>
@@ -700,7 +700,7 @@
         <v>22.2</v>
       </c>
       <c r="H8" t="n">
-        <v>402.8</v>
+        <v>409.3</v>
       </c>
       <c r="I8" t="n">
         <v>823.9</v>
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
         <v>44.8</v>
@@ -731,10 +731,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="H9" t="n">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I9" t="n">
         <v>798.3</v>
@@ -817,32 +817,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>johnson6</t>
+          <t>Jules</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>34.7</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
         <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>62.8</v>
+        <v>67.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>138.9</v>
+        <v>349.5</v>
       </c>
       <c r="I12" t="n">
-        <v>765.2</v>
+        <v>765.4</v>
       </c>
       <c r="J12" t="n">
-        <v>849</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13">
@@ -851,32 +851,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jules</t>
+          <t>johnson6</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>34.4</v>
+        <v>34.7</v>
       </c>
       <c r="E13" t="n">
         <v>36.6</v>
       </c>
       <c r="F13" t="n">
-        <v>67.5</v>
+        <v>62.8</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>343.9</v>
+        <v>138.9</v>
       </c>
       <c r="I13" t="n">
-        <v>765.4</v>
+        <v>765.2</v>
       </c>
       <c r="J13" t="n">
-        <v>924</v>
+        <v>849</v>
       </c>
     </row>
     <row r="14">
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="E14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="F14" t="n">
         <v>44.3</v>
@@ -904,10 +904,10 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>119.8</v>
+        <v>128.3</v>
       </c>
       <c r="I14" t="n">
-        <v>679.1</v>
+        <v>684.6</v>
       </c>
       <c r="J14" t="n">
         <v>832</v>
@@ -1529,7 +1529,9 @@
       <c r="K15" t="n">
         <v>734</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1666,7 +1668,7 @@
         <v>75.8</v>
       </c>
       <c r="L2" t="n">
-        <v>73.7</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="3">
@@ -1706,7 +1708,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>92</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1740,7 +1742,7 @@
         <v>74.7</v>
       </c>
       <c r="L4" t="n">
-        <v>24.4</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="5">
@@ -1772,7 +1774,7 @@
         <v>79.7</v>
       </c>
       <c r="L5" t="n">
-        <v>58.3</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="6">
@@ -1810,7 +1812,7 @@
         <v>37.9</v>
       </c>
       <c r="L6" t="n">
-        <v>43.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -1850,7 +1852,7 @@
         <v>79.7</v>
       </c>
       <c r="L7" t="n">
-        <v>23.2</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="8">
@@ -1888,7 +1890,7 @@
         <v>61</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="9">
@@ -1946,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>55.2</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="11">
@@ -2036,7 +2038,7 @@
         <v>78.3</v>
       </c>
       <c r="L13" t="n">
-        <v>88.90000000000001</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="14">
@@ -2101,7 +2103,9 @@
       <c r="K15" t="n">
         <v>10.9</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2433,16 +2437,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>850.2</v>
+        <v>838</v>
       </c>
       <c r="D12" t="n">
-        <v>75.3</v>
+        <v>80.3</v>
       </c>
       <c r="E12" t="n">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="F12" t="n">
         <v>956</v>

--- a/geosports_history.xlsx
+++ b/geosports_history.xlsx
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>59.6</v>
+        <v>58.8</v>
       </c>
       <c r="E5" t="n">
-        <v>65.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="F5" t="n">
         <v>89.09999999999999</v>
@@ -598,10 +598,10 @@
         <v>17.6</v>
       </c>
       <c r="H5" t="n">
-        <v>655.4</v>
+        <v>705.4</v>
       </c>
       <c r="I5" t="n">
-        <v>830.8</v>
+        <v>826</v>
       </c>
       <c r="J5" t="n">
         <v>975</v>
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,6 +1056,11 @@
           <t>9/12/26</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>9/13/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1096,6 +1101,7 @@
       <c r="L2" t="n">
         <v>898</v>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1136,6 +1142,7 @@
       <c r="L3" t="n">
         <v>956</v>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1170,6 +1177,7 @@
       <c r="L4" t="n">
         <v>798</v>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1202,6 +1210,7 @@
       <c r="L5" t="n">
         <v>866</v>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1240,6 +1249,7 @@
       <c r="L6" t="n">
         <v>838</v>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1279,6 +1289,9 @@
       </c>
       <c r="L7" t="n">
         <v>795</v>
+      </c>
+      <c r="M7" t="n">
+        <v>773</v>
       </c>
     </row>
     <row r="8">
@@ -1318,6 +1331,7 @@
       <c r="L8" t="n">
         <v>699</v>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1338,6 +1352,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1376,6 +1391,7 @@
       <c r="L10" t="n">
         <v>860</v>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1402,6 +1418,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1428,6 +1445,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1466,6 +1484,7 @@
       <c r="L13" t="n">
         <v>942</v>
       </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1496,6 +1515,7 @@
         <v>769</v>
       </c>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1532,6 +1552,7 @@
       <c r="L15" t="n">
         <v>728</v>
       </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1554,6 +1575,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1566,7 +1588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,6 +1652,11 @@
           <t>9/12/26</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>9/13/26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1670,6 +1697,7 @@
       <c r="L2" t="n">
         <v>77.3</v>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1710,6 +1738,7 @@
       <c r="L3" t="n">
         <v>92.90000000000001</v>
       </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1744,6 +1773,7 @@
       <c r="L4" t="n">
         <v>30.9</v>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1776,6 +1806,7 @@
       <c r="L5" t="n">
         <v>63.6</v>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1814,6 +1845,7 @@
       <c r="L6" t="n">
         <v>50</v>
       </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1853,6 +1885,9 @@
       </c>
       <c r="L7" t="n">
         <v>29.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1892,6 +1927,7 @@
       <c r="L8" t="n">
         <v>4.2</v>
       </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1912,6 +1948,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1950,6 +1987,7 @@
       <c r="L10" t="n">
         <v>60.8</v>
       </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1976,6 +2014,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2002,6 +2041,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2040,6 +2080,7 @@
       <c r="L13" t="n">
         <v>90.2</v>
       </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2070,6 +2111,7 @@
         <v>20.5</v>
       </c>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2106,6 +2148,7 @@
       <c r="L15" t="n">
         <v>8.5</v>
       </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2128,6 +2171,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2140,7 +2184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2455,6 +2499,31 @@
         <v>699</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>9/13/26</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>773</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>773</v>
+      </c>
+      <c r="F13" t="n">
+        <v>773</v>
+      </c>
+      <c r="G13" t="n">
+        <v>773</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
